--- a/data/stock.xlsx
+++ b/data/stock.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\blocks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADED94A-30DC-4A02-A9FC-3FD412D899A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FBBDF2C-1FA9-45F8-A6F1-80A6DF5CE096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3525" yWindow="1845" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
+    <workbookView xWindow="495" yWindow="1890" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2099" uniqueCount="1397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="1429">
   <si>
     <t>Product</t>
   </si>
@@ -3381,9 +3381,6 @@
     <t>Batman [Affleck]</t>
   </si>
   <si>
-    <t>Batman [Pattinson]</t>
-  </si>
-  <si>
     <t>muzan.jpg</t>
   </si>
   <si>
@@ -4225,6 +4222,105 @@
   </si>
   <si>
     <t>peter griffin.jpeg</t>
+  </si>
+  <si>
+    <t>Vecna v2</t>
+  </si>
+  <si>
+    <t>Eleven v2</t>
+  </si>
+  <si>
+    <t>Demogorgon</t>
+  </si>
+  <si>
+    <t>dustin v2.jpeg</t>
+  </si>
+  <si>
+    <t>mike v2.jpeg</t>
+  </si>
+  <si>
+    <t>will v2.jpeg</t>
+  </si>
+  <si>
+    <t>nancy v2.jpeg</t>
+  </si>
+  <si>
+    <t>vecna v2.jpeg</t>
+  </si>
+  <si>
+    <t>eleven v2.jpeg</t>
+  </si>
+  <si>
+    <t>demogorgon.jpeg</t>
+  </si>
+  <si>
+    <t>Dustin Henderson v2</t>
+  </si>
+  <si>
+    <t>Mike Wheeler v2</t>
+  </si>
+  <si>
+    <t>Will Byers v2</t>
+  </si>
+  <si>
+    <t>Nancy Wheeler v2</t>
+  </si>
+  <si>
+    <t>Steve Harrignton v2</t>
+  </si>
+  <si>
+    <t>steve v2.jpeg</t>
+  </si>
+  <si>
+    <t>Display Box [Small]</t>
+  </si>
+  <si>
+    <t>small box.jpeg</t>
+  </si>
+  <si>
+    <t>The Batman [Robert Pattinson]</t>
+  </si>
+  <si>
+    <t>Ash and Pikachu</t>
+  </si>
+  <si>
+    <t>Ash and Bulbasaur</t>
+  </si>
+  <si>
+    <t>Ash and Squirtle</t>
+  </si>
+  <si>
+    <t>Ash and Pidgey</t>
+  </si>
+  <si>
+    <t>Serena and Mewtwo</t>
+  </si>
+  <si>
+    <t>Calem and Gengar</t>
+  </si>
+  <si>
+    <t>Misty and Eevee</t>
+  </si>
+  <si>
+    <t>ash pika.jpeg</t>
+  </si>
+  <si>
+    <t>ash bulb.jpeg</t>
+  </si>
+  <si>
+    <t>ash pidgey.jpeg</t>
+  </si>
+  <si>
+    <t>serena mewtwo.jpeg</t>
+  </si>
+  <si>
+    <t>calem genger.jpeg</t>
+  </si>
+  <si>
+    <t>misty eevee.jpeg</t>
+  </si>
+  <si>
+    <t>ash squirtle.jpeg</t>
   </si>
 </sst>
 </file>
@@ -4777,7 +4873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCDC9875-9E8E-485C-910E-47B83A1F9902}">
-  <dimension ref="A1:E699"/>
+  <dimension ref="A1:E715"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -4805,7 +4901,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B2" s="3">
         <v>4</v>
@@ -4814,7 +4910,7 @@
         <v>260</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>6</v>
@@ -4822,7 +4918,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B3" s="3">
         <v>6</v>
@@ -4831,7 +4927,7 @@
         <v>260</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
@@ -4839,7 +4935,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="B4" s="3">
         <v>2</v>
@@ -4848,7 +4944,7 @@
         <v>260</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>6</v>
@@ -4856,7 +4952,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -4865,7 +4961,7 @@
         <v>300</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>6</v>
@@ -4873,7 +4969,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -4882,7 +4978,7 @@
         <v>260</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>6</v>
@@ -4890,7 +4986,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -4899,7 +4995,7 @@
         <v>260</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>6</v>
@@ -4907,7 +5003,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -4916,7 +5012,7 @@
         <v>260</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>6</v>
@@ -4924,7 +5020,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -4933,7 +5029,7 @@
         <v>260</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>6</v>
@@ -4941,7 +5037,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -4950,7 +5046,7 @@
         <v>260</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>6</v>
@@ -5060,7 +5156,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B17" s="3">
         <v>2</v>
@@ -5069,7 +5165,7 @@
         <v>550</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>6</v>
@@ -5077,7 +5173,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B18" s="3">
         <v>0</v>
@@ -5086,7 +5182,7 @@
         <v>260</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>6</v>
@@ -5094,7 +5190,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B19" s="3">
         <v>1</v>
@@ -5103,7 +5199,7 @@
         <v>300</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>6</v>
@@ -5111,7 +5207,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B20" s="3">
         <v>1</v>
@@ -5120,7 +5216,7 @@
         <v>260</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>6</v>
@@ -5128,7 +5224,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B21" s="3">
         <v>1</v>
@@ -5137,7 +5233,7 @@
         <v>320</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>6</v>
@@ -5157,7 +5253,7 @@
         <v>783</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -5174,7 +5270,7 @@
         <v>785</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -5191,7 +5287,7 @@
         <v>784</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -5208,7 +5304,7 @@
         <v>786</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -5225,7 +5321,7 @@
         <v>788</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -5242,7 +5338,7 @@
         <v>570</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -5284,7 +5380,7 @@
         <v>790</v>
       </c>
       <c r="B30" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="3">
         <v>220</v>
@@ -5409,10 +5505,10 @@
         <v>200</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -5426,7 +5522,7 @@
         <v>200</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>6</v>
@@ -5437,7 +5533,7 @@
         <v>504</v>
       </c>
       <c r="B39" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" s="3">
         <v>260</v>
@@ -5471,7 +5567,7 @@
         <v>244</v>
       </c>
       <c r="B41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" s="3">
         <v>260</v>
@@ -5522,7 +5618,7 @@
         <v>245</v>
       </c>
       <c r="B44" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44" s="3">
         <v>260</v>
@@ -5641,7 +5737,7 @@
         <v>369</v>
       </c>
       <c r="B51" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" s="3">
         <v>260</v>
@@ -5859,10 +5955,10 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B64" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64" s="3">
         <v>180</v>
@@ -5944,16 +6040,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B69" s="3">
+        <v>1</v>
+      </c>
+      <c r="C69" s="3">
+        <v>260</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>1125</v>
-      </c>
-      <c r="B69" s="3">
-        <v>1</v>
-      </c>
-      <c r="C69" s="3">
-        <v>260</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>1126</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>6</v>
@@ -6185,7 +6281,7 @@
         <v>31</v>
       </c>
       <c r="B83" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83" s="3">
         <v>850</v>
@@ -6199,7 +6295,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B84" s="3">
         <v>3</v>
@@ -6216,7 +6312,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B85" s="3">
         <v>5</v>
@@ -6284,7 +6380,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B89" s="3">
         <v>3</v>
@@ -6301,7 +6397,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B90" s="3">
         <v>2</v>
@@ -6474,7 +6570,7 @@
         <v>382</v>
       </c>
       <c r="B100" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C100" s="3">
         <v>260</v>
@@ -6913,7 +7009,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B126" s="3">
         <v>0</v>
@@ -7041,7 +7137,7 @@
         <v>320</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>6</v>
@@ -7168,7 +7264,7 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B141" s="3">
         <v>2</v>
@@ -7185,7 +7281,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="B142" s="3">
         <v>4</v>
@@ -7347,7 +7443,7 @@
         <v>260</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>6</v>
@@ -7372,7 +7468,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B153" s="3">
         <v>1</v>
@@ -7381,7 +7477,7 @@
         <v>260</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>6</v>
@@ -7389,7 +7485,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B154" s="3">
         <v>2</v>
@@ -7406,7 +7502,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="B155" s="3">
         <v>0</v>
@@ -7644,7 +7740,7 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B169" s="3">
         <v>3</v>
@@ -7653,7 +7749,7 @@
         <v>400</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>6</v>
@@ -7661,7 +7757,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B170" s="3">
         <v>2</v>
@@ -7670,7 +7766,7 @@
         <v>280</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="E170" s="3" t="s">
         <v>6</v>
@@ -7678,7 +7774,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B171" s="3">
         <v>2</v>
@@ -7687,7 +7783,7 @@
         <v>280</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>6</v>
@@ -7695,7 +7791,7 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B172" s="3">
         <v>3</v>
@@ -7704,7 +7800,7 @@
         <v>280</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>6</v>
@@ -7712,7 +7808,7 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B173" s="3">
         <v>1</v>
@@ -7721,7 +7817,7 @@
         <v>280</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>6</v>
@@ -7729,7 +7825,7 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B174" s="3">
         <v>2</v>
@@ -7738,7 +7834,7 @@
         <v>280</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>6</v>
@@ -7746,16 +7842,16 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B175" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C175" s="3">
         <v>280</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>6</v>
@@ -7763,7 +7859,7 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B176" s="3">
         <v>3</v>
@@ -7772,7 +7868,7 @@
         <v>400</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>6</v>
@@ -7780,7 +7876,7 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B177" s="3">
         <v>1</v>
@@ -7789,7 +7885,7 @@
         <v>260</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>6</v>
@@ -7797,7 +7893,7 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B178" s="3">
         <v>1</v>
@@ -7806,7 +7902,7 @@
         <v>260</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>6</v>
@@ -7814,7 +7910,7 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B179" s="3">
         <v>1</v>
@@ -7823,7 +7919,7 @@
         <v>260</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>6</v>
@@ -7831,7 +7927,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B180" s="3">
         <v>3</v>
@@ -7840,7 +7936,7 @@
         <v>260</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>6</v>
@@ -7848,7 +7944,7 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B181" s="3">
         <v>3</v>
@@ -7857,7 +7953,7 @@
         <v>260</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>6</v>
@@ -7865,7 +7961,7 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="B182" s="3">
         <v>3</v>
@@ -7874,7 +7970,7 @@
         <v>260</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>6</v>
@@ -7882,7 +7978,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="B183" s="3">
         <v>3</v>
@@ -7891,7 +7987,7 @@
         <v>300</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>6</v>
@@ -7899,7 +7995,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="B184" s="3">
         <v>1</v>
@@ -7908,7 +8004,7 @@
         <v>260</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>6</v>
@@ -7916,7 +8012,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="B185" s="3">
         <v>2</v>
@@ -7925,7 +8021,7 @@
         <v>260</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>6</v>
@@ -7933,7 +8029,7 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="B186" s="3">
         <v>2</v>
@@ -7942,7 +8038,7 @@
         <v>260</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>6</v>
@@ -7950,7 +8046,7 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="B187" s="3">
         <v>2</v>
@@ -7959,7 +8055,7 @@
         <v>260</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>6</v>
@@ -7967,7 +8063,7 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="B188" s="3">
         <v>2</v>
@@ -7976,7 +8072,7 @@
         <v>260</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>6</v>
@@ -7984,7 +8080,7 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="B189" s="3">
         <v>5</v>
@@ -7993,7 +8089,7 @@
         <v>400</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>6</v>
@@ -8001,7 +8097,7 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="B190" s="3">
         <v>9</v>
@@ -8010,7 +8106,7 @@
         <v>300</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>6</v>
@@ -8018,7 +8114,7 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B191" s="3">
         <v>2</v>
@@ -8027,7 +8123,7 @@
         <v>300</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>6</v>
@@ -8035,7 +8131,7 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="B192" s="3">
         <v>1</v>
@@ -8044,7 +8140,7 @@
         <v>260</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>6</v>
@@ -8052,7 +8148,7 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B193" s="3">
         <v>2</v>
@@ -8061,7 +8157,7 @@
         <v>260</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>6</v>
@@ -8078,7 +8174,7 @@
         <v>260</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>6</v>
@@ -8086,7 +8182,7 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="B195" s="3">
         <v>2</v>
@@ -8095,7 +8191,7 @@
         <v>260</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>6</v>
@@ -8103,7 +8199,7 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B196" s="3">
         <v>2</v>
@@ -8112,7 +8208,7 @@
         <v>260</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>6</v>
@@ -8120,7 +8216,7 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="B197" s="3">
         <v>2</v>
@@ -8129,7 +8225,7 @@
         <v>260</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>6</v>
@@ -8137,7 +8233,7 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="B198" s="3">
         <v>2</v>
@@ -8146,7 +8242,7 @@
         <v>260</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>6</v>
@@ -8154,7 +8250,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="B199" s="3">
         <v>2</v>
@@ -8163,7 +8259,7 @@
         <v>260</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>6</v>
@@ -8171,10 +8267,10 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="13" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B200" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C200" s="14">
         <v>280</v>
@@ -8375,7 +8471,7 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="7" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="B212" s="3">
         <v>1</v>
@@ -8392,7 +8488,7 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="B213" s="3">
         <v>6</v>
@@ -8486,7 +8582,7 @@
         <v>220</v>
       </c>
       <c r="D218" s="8" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="E218" s="3" t="s">
         <v>35</v>
@@ -8503,7 +8599,7 @@
         <v>220</v>
       </c>
       <c r="D219" s="8" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="E219" s="3" t="s">
         <v>35</v>
@@ -8622,7 +8718,7 @@
         <v>220</v>
       </c>
       <c r="D226" s="8" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>35</v>
@@ -9021,10 +9117,10 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="7" t="s">
-        <v>1115</v>
+        <v>1414</v>
       </c>
       <c r="B250" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C250" s="3">
         <v>260</v>
@@ -9072,16 +9168,16 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B253" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C253" s="3">
         <v>300</v>
       </c>
       <c r="D253" s="8" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>35</v>
@@ -9089,7 +9185,7 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="7" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B254" s="3">
         <v>3</v>
@@ -9098,7 +9194,7 @@
         <v>300</v>
       </c>
       <c r="D254" s="8" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>35</v>
@@ -9106,7 +9202,7 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B255" s="3">
         <v>2</v>
@@ -9115,7 +9211,7 @@
         <v>260</v>
       </c>
       <c r="D255" s="8" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E255" s="3" t="s">
         <v>35</v>
@@ -9123,7 +9219,7 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="7" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B256" s="3">
         <v>2</v>
@@ -9132,7 +9228,7 @@
         <v>260</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E256" s="3" t="s">
         <v>35</v>
@@ -9140,7 +9236,7 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B257" s="3">
         <v>4</v>
@@ -9149,7 +9245,7 @@
         <v>260</v>
       </c>
       <c r="D257" s="8" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E257" s="3" t="s">
         <v>35</v>
@@ -9157,7 +9253,7 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B258" s="3">
         <v>2</v>
@@ -9166,7 +9262,7 @@
         <v>260</v>
       </c>
       <c r="D258" s="8" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E258" s="3" t="s">
         <v>35</v>
@@ -9174,7 +9270,7 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B259" s="3">
         <v>1</v>
@@ -9183,7 +9279,7 @@
         <v>260</v>
       </c>
       <c r="D259" s="8" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>35</v>
@@ -9191,7 +9287,7 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="7" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="B260" s="3">
         <v>5</v>
@@ -9200,7 +9296,7 @@
         <v>260</v>
       </c>
       <c r="D260" s="8" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>35</v>
@@ -9208,7 +9304,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B261" s="3">
         <v>3</v>
@@ -9217,7 +9313,7 @@
         <v>280</v>
       </c>
       <c r="D261" s="8" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>35</v>
@@ -9225,7 +9321,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="7" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="B262" s="3">
         <v>2</v>
@@ -9234,7 +9330,7 @@
         <v>280</v>
       </c>
       <c r="D262" s="8" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E262" s="3" t="s">
         <v>35</v>
@@ -9242,7 +9338,7 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="B263" s="3">
         <v>2</v>
@@ -9251,7 +9347,7 @@
         <v>280</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>35</v>
@@ -9259,7 +9355,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="B264" s="3">
         <v>2</v>
@@ -9268,7 +9364,7 @@
         <v>260</v>
       </c>
       <c r="D264" s="8" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>35</v>
@@ -9412,7 +9508,7 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B273" s="3">
         <v>1</v>
@@ -9591,7 +9687,7 @@
         <v>300</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="E283" s="3" t="s">
         <v>44</v>
@@ -10755,7 +10851,7 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B352" s="3">
         <v>1</v>
@@ -10764,7 +10860,7 @@
         <v>300</v>
       </c>
       <c r="D352" s="8" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="E352" s="3" t="s">
         <v>44</v>
@@ -10772,7 +10868,7 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="7" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B353" s="3">
         <v>1</v>
@@ -10781,7 +10877,7 @@
         <v>320</v>
       </c>
       <c r="D353" s="8" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="E353" s="3" t="s">
         <v>44</v>
@@ -10789,7 +10885,7 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B354" s="3">
         <v>1</v>
@@ -10798,7 +10894,7 @@
         <v>300</v>
       </c>
       <c r="D354" s="8" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="E354" s="3" t="s">
         <v>44</v>
@@ -10806,7 +10902,7 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B355" s="3">
         <v>1</v>
@@ -10815,7 +10911,7 @@
         <v>320</v>
       </c>
       <c r="D355" s="8" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>44</v>
@@ -10849,7 +10945,7 @@
         <v>260</v>
       </c>
       <c r="D357" s="8" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="E357" s="3" t="s">
         <v>100</v>
@@ -11163,7 +11259,7 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="7" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B376" s="3">
         <v>1</v>
@@ -11172,7 +11268,7 @@
         <v>500</v>
       </c>
       <c r="D376" s="8" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E376" s="3" t="s">
         <v>100</v>
@@ -11197,7 +11293,7 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B378" s="3">
         <v>1</v>
@@ -11325,7 +11421,7 @@
         <v>260</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E385" s="3" t="s">
         <v>100</v>
@@ -11376,7 +11472,7 @@
         <v>260</v>
       </c>
       <c r="D388" s="8" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="E388" s="3" t="s">
         <v>100</v>
@@ -11520,7 +11616,7 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" s="7" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B397" s="3">
         <v>0</v>
@@ -11537,7 +11633,7 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="7" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B398" s="3">
         <v>1</v>
@@ -11554,7 +11650,7 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="7" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B399" s="3">
         <v>1</v>
@@ -11571,7 +11667,7 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B400" s="3">
         <v>1</v>
@@ -11588,7 +11684,7 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="7" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B401" s="3">
         <v>0</v>
@@ -11605,7 +11701,7 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="7" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B402" s="3">
         <v>1</v>
@@ -11954,7 +12050,7 @@
         <v>260</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="E422" s="3" t="s">
         <v>116</v>
@@ -12319,7 +12415,7 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="7" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B444" s="3">
         <v>1</v>
@@ -12345,7 +12441,7 @@
         <v>300</v>
       </c>
       <c r="D445" s="8" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E445" s="3" t="s">
         <v>116</v>
@@ -12421,7 +12517,7 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B450" s="3">
         <v>1</v>
@@ -12430,7 +12526,7 @@
         <v>280</v>
       </c>
       <c r="D450" s="8" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="E450" s="3" t="s">
         <v>116</v>
@@ -12438,7 +12534,7 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B451" s="3">
         <v>1</v>
@@ -12447,7 +12543,7 @@
         <v>280</v>
       </c>
       <c r="D451" s="8" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="E451" s="3" t="s">
         <v>116</v>
@@ -12455,7 +12551,7 @@
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B452" s="3">
         <v>1</v>
@@ -12464,7 +12560,7 @@
         <v>280</v>
       </c>
       <c r="D452" s="8" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="E452" s="3" t="s">
         <v>116</v>
@@ -12472,7 +12568,7 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B453" s="3">
         <v>2</v>
@@ -12481,7 +12577,7 @@
         <v>320</v>
       </c>
       <c r="D453" s="8" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="E453" s="3" t="s">
         <v>116</v>
@@ -12489,7 +12585,7 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B454" s="3">
         <v>1</v>
@@ -12498,7 +12594,7 @@
         <v>320</v>
       </c>
       <c r="D454" s="8" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="E454" s="3" t="s">
         <v>116</v>
@@ -12506,7 +12602,7 @@
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B455" s="3">
         <v>2</v>
@@ -12515,7 +12611,7 @@
         <v>320</v>
       </c>
       <c r="D455" s="8" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="E455" s="3" t="s">
         <v>116</v>
@@ -12685,7 +12781,7 @@
         <v>270</v>
       </c>
       <c r="D465" s="8" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="E465" s="3" t="s">
         <v>120</v>
@@ -12804,7 +12900,7 @@
         <v>270</v>
       </c>
       <c r="D472" s="8" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="E472" s="3" t="s">
         <v>120</v>
@@ -12999,7 +13095,7 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B484" s="3">
         <v>3</v>
@@ -13008,7 +13104,7 @@
         <v>360</v>
       </c>
       <c r="D484" s="8" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="E484" s="3" t="s">
         <v>120</v>
@@ -13016,7 +13112,7 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B485" s="3">
         <v>4</v>
@@ -13025,7 +13121,7 @@
         <v>360</v>
       </c>
       <c r="D485" s="8" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="E485" s="3" t="s">
         <v>120</v>
@@ -13033,7 +13129,7 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B486" s="3">
         <v>1</v>
@@ -13042,7 +13138,7 @@
         <v>270</v>
       </c>
       <c r="D486" s="8" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="E486" s="3" t="s">
         <v>120</v>
@@ -13050,7 +13146,7 @@
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B487" s="3">
         <v>1</v>
@@ -13059,7 +13155,7 @@
         <v>270</v>
       </c>
       <c r="D487" s="8" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="E487" s="3" t="s">
         <v>120</v>
@@ -13067,7 +13163,7 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B488" s="3">
         <v>1</v>
@@ -13076,7 +13172,7 @@
         <v>270</v>
       </c>
       <c r="D488" s="8" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="E488" s="3" t="s">
         <v>120</v>
@@ -13543,7 +13639,7 @@
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" s="7" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B516" s="3">
         <v>1</v>
@@ -13552,7 +13648,7 @@
         <v>260</v>
       </c>
       <c r="D516" s="8" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="E516" s="6" t="s">
         <v>416</v>
@@ -13560,7 +13656,7 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" s="7" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B517" s="3">
         <v>0</v>
@@ -13569,7 +13665,7 @@
         <v>260</v>
       </c>
       <c r="D517" s="8" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="E517" s="6" t="s">
         <v>416</v>
@@ -13577,7 +13673,7 @@
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" s="7" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B518" s="3">
         <v>5</v>
@@ -13586,7 +13682,7 @@
         <v>220</v>
       </c>
       <c r="D518" s="8" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="E518" s="6" t="s">
         <v>416</v>
@@ -13606,7 +13702,7 @@
         <v>222</v>
       </c>
       <c r="E519" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
@@ -13623,7 +13719,7 @@
         <v>279</v>
       </c>
       <c r="E520" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
@@ -13637,7 +13733,7 @@
         <v>260</v>
       </c>
       <c r="D521" s="2" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E521" s="6" t="s">
         <v>361</v>
@@ -13654,7 +13750,7 @@
         <v>280</v>
       </c>
       <c r="D522" s="8" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="E522" s="6" t="s">
         <v>361</v>
@@ -13832,7 +13928,7 @@
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B533" s="5">
         <v>2</v>
@@ -13841,7 +13937,7 @@
         <v>260</v>
       </c>
       <c r="D533" s="8" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="E533" s="6" t="s">
         <v>361</v>
@@ -13849,7 +13945,7 @@
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B534" s="5">
         <v>1</v>
@@ -13858,7 +13954,7 @@
         <v>260</v>
       </c>
       <c r="D534" s="8" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="E534" s="6" t="s">
         <v>361</v>
@@ -13866,7 +13962,7 @@
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B535" s="5">
         <v>1</v>
@@ -13875,7 +13971,7 @@
         <v>260</v>
       </c>
       <c r="D535" s="8" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="E535" s="6" t="s">
         <v>361</v>
@@ -13883,7 +13979,7 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B536" s="5">
         <v>2</v>
@@ -13892,7 +13988,7 @@
         <v>260</v>
       </c>
       <c r="D536" s="8" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E536" s="6" t="s">
         <v>361</v>
@@ -13900,7 +13996,7 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B537" s="5">
         <v>2</v>
@@ -13909,7 +14005,7 @@
         <v>260</v>
       </c>
       <c r="D537" s="8" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="E537" s="6" t="s">
         <v>361</v>
@@ -13917,7 +14013,7 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B538" s="5">
         <v>1</v>
@@ -13926,7 +14022,7 @@
         <v>320</v>
       </c>
       <c r="D538" s="8" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="E538" s="6" t="s">
         <v>361</v>
@@ -13934,7 +14030,7 @@
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B539" s="5">
         <v>1</v>
@@ -13943,7 +14039,7 @@
         <v>320</v>
       </c>
       <c r="D539" s="8" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="E539" s="6" t="s">
         <v>361</v>
@@ -13951,7 +14047,7 @@
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B540" s="5">
         <v>1</v>
@@ -13960,7 +14056,7 @@
         <v>320</v>
       </c>
       <c r="D540" s="8" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="E540" s="6" t="s">
         <v>361</v>
@@ -13980,7 +14076,7 @@
         <v>223</v>
       </c>
       <c r="E541" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
@@ -14580,7 +14676,7 @@
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B577" s="5">
         <v>11</v>
@@ -15765,7 +15861,7 @@
         <v>1059</v>
       </c>
       <c r="E646" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
@@ -15782,7 +15878,7 @@
         <v>1060</v>
       </c>
       <c r="E647" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
@@ -15799,7 +15895,7 @@
         <v>1061</v>
       </c>
       <c r="E648" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
@@ -15816,7 +15912,7 @@
         <v>1062</v>
       </c>
       <c r="E649" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
@@ -15833,7 +15929,7 @@
         <v>1063</v>
       </c>
       <c r="E650" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
@@ -15850,7 +15946,7 @@
         <v>1064</v>
       </c>
       <c r="E651" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.25">
@@ -15867,7 +15963,7 @@
         <v>1065</v>
       </c>
       <c r="E652" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
@@ -15918,7 +16014,7 @@
         <v>1068</v>
       </c>
       <c r="E655" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
@@ -15935,7 +16031,7 @@
         <v>1069</v>
       </c>
       <c r="E656" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
@@ -15952,7 +16048,7 @@
         <v>1070</v>
       </c>
       <c r="E657" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.25">
@@ -15969,7 +16065,7 @@
         <v>1071</v>
       </c>
       <c r="E658" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
@@ -15986,7 +16082,7 @@
         <v>1072</v>
       </c>
       <c r="E659" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
@@ -16003,7 +16099,7 @@
         <v>1073</v>
       </c>
       <c r="E660" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
@@ -16020,12 +16116,12 @@
         <v>1074</v>
       </c>
       <c r="E661" s="6" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B662" s="5">
         <v>20</v>
@@ -16034,7 +16130,7 @@
         <v>100</v>
       </c>
       <c r="D662" s="8" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="E662" s="6" t="s">
         <v>176</v>
@@ -16042,7 +16138,7 @@
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B663" s="5">
         <v>40</v>
@@ -16051,7 +16147,7 @@
         <v>200</v>
       </c>
       <c r="D663" s="8" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="E663" s="6" t="s">
         <v>176</v>
@@ -16071,7 +16167,7 @@
         <v>1075</v>
       </c>
       <c r="E664" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
@@ -16088,7 +16184,7 @@
         <v>1080</v>
       </c>
       <c r="E665" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
@@ -16105,7 +16201,7 @@
         <v>1082</v>
       </c>
       <c r="E666" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
@@ -16122,12 +16218,12 @@
         <v>1100</v>
       </c>
       <c r="E667" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B668" s="5">
         <v>5</v>
@@ -16136,15 +16232,15 @@
         <v>280</v>
       </c>
       <c r="D668" s="4" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="E668" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B669" s="5">
         <v>1</v>
@@ -16153,15 +16249,15 @@
         <v>1300</v>
       </c>
       <c r="D669" s="4" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="E669" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B670" s="5">
         <v>1</v>
@@ -16170,15 +16266,15 @@
         <v>560</v>
       </c>
       <c r="D670" s="4" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="E670" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="B671" s="5">
         <v>1</v>
@@ -16187,15 +16283,15 @@
         <v>280</v>
       </c>
       <c r="D671" s="4" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E671" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="B672" s="5">
         <v>1</v>
@@ -16204,15 +16300,15 @@
         <v>350</v>
       </c>
       <c r="D672" s="4" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E672" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B673" s="5">
         <v>5</v>
@@ -16221,15 +16317,15 @@
         <v>280</v>
       </c>
       <c r="D673" s="4" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="E673" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="B674" s="5">
         <v>2</v>
@@ -16238,15 +16334,15 @@
         <v>280</v>
       </c>
       <c r="D674" s="4" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="E674" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B675" s="5">
         <v>0</v>
@@ -16255,15 +16351,15 @@
         <v>280</v>
       </c>
       <c r="D675" s="4" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="E675" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B676" s="5">
         <v>1</v>
@@ -16272,15 +16368,15 @@
         <v>280</v>
       </c>
       <c r="D676" s="4" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="E676" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B677" s="5">
         <v>1</v>
@@ -16289,15 +16385,15 @@
         <v>260</v>
       </c>
       <c r="D677" s="4" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="E677" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B678" s="5">
         <v>1</v>
@@ -16306,15 +16402,15 @@
         <v>260</v>
       </c>
       <c r="D678" s="4" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="E678" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B679" s="5">
         <v>1</v>
@@ -16323,15 +16419,15 @@
         <v>260</v>
       </c>
       <c r="D679" s="4" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="E679" s="6" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B680" s="5">
         <v>0</v>
@@ -16343,12 +16439,12 @@
         <v>134</v>
       </c>
       <c r="E680" s="6" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B681" s="5">
         <v>1</v>
@@ -16357,15 +16453,15 @@
         <v>460</v>
       </c>
       <c r="D681" s="4" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E681" s="6" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B682" s="5">
         <v>1</v>
@@ -16374,15 +16470,15 @@
         <v>400</v>
       </c>
       <c r="D682" s="4" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="E682" s="6" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B683" s="5">
         <v>1</v>
@@ -16391,15 +16487,15 @@
         <v>460</v>
       </c>
       <c r="D683" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E683" s="6" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B684" s="5">
         <v>2</v>
@@ -16408,15 +16504,15 @@
         <v>460</v>
       </c>
       <c r="D684" s="4" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="E684" s="6" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B685" s="5">
         <v>0</v>
@@ -16428,12 +16524,12 @@
         <v>134</v>
       </c>
       <c r="E685" s="6" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="B686" s="5">
         <v>0</v>
@@ -16442,15 +16538,15 @@
         <v>460</v>
       </c>
       <c r="D686" s="4" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="E686" s="6" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B687" s="5">
         <v>0</v>
@@ -16459,15 +16555,15 @@
         <v>460</v>
       </c>
       <c r="D687" s="4" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="E687" s="6" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B688" s="5">
         <v>0</v>
@@ -16479,12 +16575,12 @@
         <v>134</v>
       </c>
       <c r="E688" s="6" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B689" s="5">
         <v>1</v>
@@ -16493,15 +16589,15 @@
         <v>460</v>
       </c>
       <c r="D689" s="4" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="E689" s="6" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="B690" s="5">
         <v>1</v>
@@ -16510,15 +16606,15 @@
         <v>420</v>
       </c>
       <c r="D690" s="4" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="E690" s="6" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B691" s="5">
         <v>1</v>
@@ -16527,15 +16623,15 @@
         <v>420</v>
       </c>
       <c r="D691" s="4" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="E691" s="6" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B692" s="5">
         <v>1</v>
@@ -16544,15 +16640,15 @@
         <v>420</v>
       </c>
       <c r="D692" s="4" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="E692" s="6" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B693" s="5">
         <v>0</v>
@@ -16561,15 +16657,15 @@
         <v>420</v>
       </c>
       <c r="D693" s="4" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E693" s="6" t="s">
         <v>1274</v>
-      </c>
-      <c r="E693" s="6" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="B694" s="5">
         <v>1</v>
@@ -16578,7 +16674,7 @@
         <v>1600</v>
       </c>
       <c r="D694" s="4" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="E694" s="6" t="s">
         <v>176</v>
@@ -16586,7 +16682,7 @@
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B695" s="5">
         <v>1</v>
@@ -16595,15 +16691,15 @@
         <v>260</v>
       </c>
       <c r="D695" s="4" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E695" s="6" t="s">
         <v>1329</v>
-      </c>
-      <c r="E695" s="6" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B696" s="5">
         <v>1</v>
@@ -16612,32 +16708,32 @@
         <v>260</v>
       </c>
       <c r="D696" s="4" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="E696" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B697" s="5">
+        <v>1</v>
+      </c>
+      <c r="C697" s="5">
+        <v>260</v>
+      </c>
+      <c r="D697" s="4" t="s">
         <v>1326</v>
       </c>
-      <c r="B697" s="5">
-        <v>1</v>
-      </c>
-      <c r="C697" s="5">
-        <v>260</v>
-      </c>
-      <c r="D697" s="4" t="s">
-        <v>1327</v>
-      </c>
       <c r="E697" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="698" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B698" s="5">
         <v>2</v>
@@ -16646,15 +16742,15 @@
         <v>280</v>
       </c>
       <c r="D698" s="4" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="E698" s="6" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="699" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B699" s="5">
         <v>3</v>
@@ -16663,10 +16759,282 @@
         <v>300</v>
       </c>
       <c r="D699" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E699" s="6" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="700" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A700" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B700" s="5">
+        <v>1</v>
+      </c>
+      <c r="C700" s="5">
+        <v>260</v>
+      </c>
+      <c r="D700" s="4" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E700" s="6" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="701" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A701" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B701" s="5">
+        <v>1</v>
+      </c>
+      <c r="C701" s="5">
+        <v>260</v>
+      </c>
+      <c r="D701" s="4" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E701" s="6" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="702" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A702" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B702" s="5">
+        <v>1</v>
+      </c>
+      <c r="C702" s="5">
+        <v>260</v>
+      </c>
+      <c r="D702" s="4" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E702" s="6" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="703" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A703" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B703" s="5">
+        <v>1</v>
+      </c>
+      <c r="C703" s="5">
+        <v>260</v>
+      </c>
+      <c r="D703" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E703" s="6" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="704" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A704" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B704" s="5">
+        <v>1</v>
+      </c>
+      <c r="C704" s="5">
+        <v>260</v>
+      </c>
+      <c r="D704" s="4" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E704" s="6" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="705" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A705" t="s">
         <v>1396</v>
       </c>
-      <c r="E699" s="6" t="s">
-        <v>1330</v>
+      <c r="B705" s="5">
+        <v>1</v>
+      </c>
+      <c r="C705" s="5">
+        <v>260</v>
+      </c>
+      <c r="D705" s="4" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E705" s="6" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="706" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A706" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B706" s="5">
+        <v>1</v>
+      </c>
+      <c r="C706" s="5">
+        <v>260</v>
+      </c>
+      <c r="D706" s="4" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E706" s="6" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="707" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A707" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B707" s="5">
+        <v>1</v>
+      </c>
+      <c r="C707" s="5">
+        <v>260</v>
+      </c>
+      <c r="D707" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E707" s="6" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="708" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A708" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B708" s="5">
+        <v>10</v>
+      </c>
+      <c r="C708" s="5">
+        <v>250</v>
+      </c>
+      <c r="D708" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E708" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="709" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A709" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B709" s="5">
+        <v>1</v>
+      </c>
+      <c r="C709" s="5">
+        <v>280</v>
+      </c>
+      <c r="D709" s="4" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E709" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="710" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A710" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B710" s="5">
+        <v>1</v>
+      </c>
+      <c r="C710" s="5">
+        <v>280</v>
+      </c>
+      <c r="D710" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E710" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="711" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A711" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B711" s="5">
+        <v>1</v>
+      </c>
+      <c r="C711" s="5">
+        <v>280</v>
+      </c>
+      <c r="D711" s="4" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E711" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="712" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A712" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B712" s="5">
+        <v>1</v>
+      </c>
+      <c r="C712" s="5">
+        <v>280</v>
+      </c>
+      <c r="D712" s="4" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E712" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="713" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A713" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B713" s="5">
+        <v>1</v>
+      </c>
+      <c r="C713" s="5">
+        <v>280</v>
+      </c>
+      <c r="D713" s="4" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E713" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="714" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A714" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B714" s="5">
+        <v>1</v>
+      </c>
+      <c r="C714" s="5">
+        <v>280</v>
+      </c>
+      <c r="D714" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E714" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="715" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A715" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B715" s="5">
+        <v>1</v>
+      </c>
+      <c r="C715" s="5">
+        <v>280</v>
+      </c>
+      <c r="D715" s="4" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E715" s="6" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/data/stock.xlsx
+++ b/data/stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\blocks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0A1116-40F4-4C07-BB63-9C2E73B52ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E62042-4E6D-4026-A999-F1912C1F5E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4500" yWindow="2040" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
   </bookViews>
@@ -5464,7 +5464,7 @@
         <v>592</v>
       </c>
       <c r="B30" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" s="11">
         <v>280</v>
@@ -6178,7 +6178,7 @@
         <v>497</v>
       </c>
       <c r="B72" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" s="3">
         <v>270</v>
@@ -6195,7 +6195,7 @@
         <v>498</v>
       </c>
       <c r="B73" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73" s="3">
         <v>270</v>
@@ -7538,7 +7538,7 @@
         <v>892</v>
       </c>
       <c r="B152" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C152" s="3">
         <v>260</v>
@@ -7555,7 +7555,7 @@
         <v>893</v>
       </c>
       <c r="B153" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C153" s="3">
         <v>260</v>
@@ -7572,7 +7572,7 @@
         <v>894</v>
       </c>
       <c r="B154" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C154" s="3">
         <v>260</v>
@@ -7589,7 +7589,7 @@
         <v>1117</v>
       </c>
       <c r="B155" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C155" s="3">
         <v>260</v>
@@ -7776,7 +7776,7 @@
         <v>902</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C166" s="3">
         <v>260</v>
@@ -8609,7 +8609,7 @@
         <v>1377</v>
       </c>
       <c r="B215" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C215" s="3">
         <v>300</v>
@@ -9085,7 +9085,7 @@
         <v>913</v>
       </c>
       <c r="B243" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C243" s="3">
         <v>260</v>
@@ -11193,7 +11193,7 @@
         <v>1448</v>
       </c>
       <c r="B367" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C367" s="3">
         <v>320</v>
@@ -16208,7 +16208,7 @@
         <v>952</v>
       </c>
       <c r="B662" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C662" s="5">
         <v>260</v>

--- a/data/stock.xlsx
+++ b/data/stock.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\blocks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E62042-4E6D-4026-A999-F1912C1F5E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927184FD-EA62-4BAA-B0C7-CF0396A0F767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4500" yWindow="2040" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
+    <workbookView xWindow="4080" yWindow="1740" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -9510,7 +9510,7 @@
         <v>544</v>
       </c>
       <c r="B268" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C268" s="3">
         <v>360</v>
@@ -9578,7 +9578,7 @@
         <v>545</v>
       </c>
       <c r="B272" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C272" s="3">
         <v>400</v>
@@ -9731,7 +9731,7 @@
         <v>658</v>
       </c>
       <c r="B281" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C281" s="3">
         <v>360</v>
@@ -10054,7 +10054,7 @@
         <v>240</v>
       </c>
       <c r="B300" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C300" s="3">
         <v>360</v>
@@ -10173,7 +10173,7 @@
         <v>66</v>
       </c>
       <c r="B307" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C307" s="3">
         <v>320</v>
@@ -10275,7 +10275,7 @@
         <v>72</v>
       </c>
       <c r="B313" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C313" s="3">
         <v>320</v>
@@ -10394,7 +10394,7 @@
         <v>78</v>
       </c>
       <c r="B320" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C320" s="3">
         <v>300</v>
@@ -10445,7 +10445,7 @@
         <v>80</v>
       </c>
       <c r="B323" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C323" s="3">
         <v>300</v>
@@ -10632,7 +10632,7 @@
         <v>321</v>
       </c>
       <c r="B334" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C334" s="3">
         <v>300</v>
@@ -10955,7 +10955,7 @@
         <v>98</v>
       </c>
       <c r="B353" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C353" s="3">
         <v>300</v>

--- a/data/stock.xlsx
+++ b/data/stock.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\blocks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927184FD-EA62-4BAA-B0C7-CF0396A0F767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C0E394-5061-49A3-BDB8-41A4DAE4ECDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="1740" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
+    <workbookView xWindow="3120" yWindow="2220" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1239,12 +1239,6 @@
     <t>Harley (Lego Movie)</t>
   </si>
   <si>
-    <t>Batman (Batman Begins)</t>
-  </si>
-  <si>
-    <t>Batman (Dark Knight Rises)</t>
-  </si>
-  <si>
     <t>alfred.jpg</t>
   </si>
   <si>
@@ -1701,9 +1695,6 @@
     <t>vegeta unleashed.jpg</t>
   </si>
   <si>
-    <t>Mister Fanstastic</t>
-  </si>
-  <si>
     <t>Invisible woman</t>
   </si>
   <si>
@@ -4405,6 +4396,15 @@
   </si>
   <si>
     <t>sanji wholecake dy.jpeg</t>
+  </si>
+  <si>
+    <t>Batman [Dark Knight Rises]</t>
+  </si>
+  <si>
+    <t>Batman [Batman Begins]</t>
+  </si>
+  <si>
+    <t>Mister Fantastic</t>
   </si>
 </sst>
 </file>
@@ -4985,7 +4985,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="B2" s="3">
         <v>4</v>
@@ -4994,7 +4994,7 @@
         <v>260</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>6</v>
@@ -5002,16 +5002,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="B3" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3">
         <v>260</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
@@ -5019,7 +5019,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="B4" s="3">
         <v>2</v>
@@ -5028,7 +5028,7 @@
         <v>260</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>6</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -5045,7 +5045,7 @@
         <v>300</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>6</v>
@@ -5053,7 +5053,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5062,7 +5062,7 @@
         <v>260</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>6</v>
@@ -5070,7 +5070,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5079,7 +5079,7 @@
         <v>260</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>6</v>
@@ -5087,7 +5087,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5096,7 +5096,7 @@
         <v>260</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>6</v>
@@ -5104,7 +5104,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5113,7 +5113,7 @@
         <v>260</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>6</v>
@@ -5121,7 +5121,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -5130,7 +5130,7 @@
         <v>260</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>6</v>
@@ -5138,7 +5138,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
@@ -5147,7 +5147,7 @@
         <v>400</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>6</v>
@@ -5155,7 +5155,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
@@ -5164,7 +5164,7 @@
         <v>400</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>6</v>
@@ -5172,16 +5172,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>555</v>
+        <v>1456</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="3">
         <v>260</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>6</v>
@@ -5189,7 +5189,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -5198,7 +5198,7 @@
         <v>260</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>6</v>
@@ -5206,7 +5206,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -5215,7 +5215,7 @@
         <v>260</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>6</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B16" s="3">
         <v>0</v>
@@ -5232,7 +5232,7 @@
         <v>260</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>6</v>
@@ -5240,7 +5240,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B17" s="3">
         <v>0</v>
@@ -5249,7 +5249,7 @@
         <v>260</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>6</v>
@@ -5257,7 +5257,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B18" s="3">
         <v>2</v>
@@ -5266,7 +5266,7 @@
         <v>260</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>6</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="B19" s="3">
         <v>2</v>
@@ -5283,7 +5283,7 @@
         <v>550</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>6</v>
@@ -5291,7 +5291,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="B20" s="3">
         <v>0</v>
@@ -5300,7 +5300,7 @@
         <v>260</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>6</v>
@@ -5308,7 +5308,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="B21" s="3">
         <v>1</v>
@@ -5317,7 +5317,7 @@
         <v>300</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>6</v>
@@ -5325,7 +5325,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="B22" s="3">
         <v>1</v>
@@ -5334,7 +5334,7 @@
         <v>260</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>6</v>
@@ -5342,7 +5342,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
@@ -5351,7 +5351,7 @@
         <v>320</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>6</v>
@@ -5359,7 +5359,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
@@ -5368,15 +5368,15 @@
         <v>300</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
@@ -5385,15 +5385,15 @@
         <v>300</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
@@ -5402,15 +5402,15 @@
         <v>300</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B27" s="3">
         <v>2</v>
@@ -5419,15 +5419,15 @@
         <v>300</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B28" s="3">
         <v>2</v>
@@ -5436,15 +5436,15 @@
         <v>300</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B29" s="10">
         <v>4</v>
@@ -5453,15 +5453,15 @@
         <v>660</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B30" s="10">
         <v>0</v>
@@ -5470,7 +5470,7 @@
         <v>280</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>6</v>
@@ -5495,7 +5495,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B32" s="3">
         <v>5</v>
@@ -5504,7 +5504,7 @@
         <v>220</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>6</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B33" s="3">
         <v>0</v>
@@ -5529,7 +5529,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B34" s="3">
         <v>0</v>
@@ -5538,7 +5538,7 @@
         <v>560</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>6</v>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B37" s="3">
         <v>3</v>
@@ -5617,16 +5617,16 @@
         <v>10</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39" s="3">
         <v>200</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -5640,7 +5640,7 @@
         <v>200</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>6</v>
@@ -5648,7 +5648,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B41" s="3">
         <v>4</v>
@@ -5665,7 +5665,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B42" s="3">
         <v>0</v>
@@ -5674,7 +5674,7 @@
         <v>260</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>6</v>
@@ -5699,7 +5699,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B44" s="3">
         <v>0</v>
@@ -5708,7 +5708,7 @@
         <v>260</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>6</v>
@@ -5818,7 +5818,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B51" s="3">
         <v>2</v>
@@ -5827,7 +5827,7 @@
         <v>260</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>6</v>
@@ -5835,7 +5835,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B52" s="3">
         <v>1</v>
@@ -5844,7 +5844,7 @@
         <v>260</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>6</v>
@@ -5895,7 +5895,7 @@
         <v>220</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>6</v>
@@ -6031,7 +6031,7 @@
         <v>180</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>6</v>
@@ -6042,13 +6042,13 @@
         <v>22</v>
       </c>
       <c r="B64" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64" s="3">
         <v>180</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>6</v>
@@ -6065,7 +6065,7 @@
         <v>180</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>6</v>
@@ -6073,7 +6073,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="B66" s="3">
         <v>1</v>
@@ -6082,7 +6082,7 @@
         <v>180</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>6</v>
@@ -6090,7 +6090,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B67" s="3">
         <v>1</v>
@@ -6099,7 +6099,7 @@
         <v>180</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>6</v>
@@ -6107,16 +6107,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B68" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" s="3">
         <v>180</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>6</v>
@@ -6133,7 +6133,7 @@
         <v>180</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>6</v>
@@ -6141,7 +6141,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B70" s="3">
         <v>3</v>
@@ -6150,7 +6150,7 @@
         <v>180</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>6</v>
@@ -6158,7 +6158,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="B71" s="3">
         <v>1</v>
@@ -6167,7 +6167,7 @@
         <v>260</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>6</v>
@@ -6175,7 +6175,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B72" s="3">
         <v>1</v>
@@ -6192,7 +6192,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B73" s="3">
         <v>2</v>
@@ -6209,7 +6209,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B74" s="3">
         <v>0</v>
@@ -6243,7 +6243,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B76" s="3">
         <v>3</v>
@@ -6252,7 +6252,7 @@
         <v>460</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>6</v>
@@ -6260,7 +6260,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B77" s="3">
         <v>2</v>
@@ -6269,7 +6269,7 @@
         <v>260</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>6</v>
@@ -6277,7 +6277,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="B78" s="3">
         <v>2</v>
@@ -6286,7 +6286,7 @@
         <v>260</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>6</v>
@@ -6379,7 +6379,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B84" s="3">
         <v>0</v>
@@ -6413,10 +6413,10 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="B86" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C86" s="3">
         <v>260</v>
@@ -6430,7 +6430,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="B87" s="3">
         <v>5</v>
@@ -6498,7 +6498,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="B91" s="3">
         <v>3</v>
@@ -6515,7 +6515,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="B92" s="3">
         <v>2</v>
@@ -6583,7 +6583,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B96" s="3">
         <v>2</v>
@@ -6600,7 +6600,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B97" s="3">
         <v>2</v>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B103" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C103" s="3">
         <v>260</v>
@@ -6736,10 +6736,10 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B105" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C105" s="3">
         <v>260</v>
@@ -6770,7 +6770,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B107" s="3">
         <v>0</v>
@@ -6779,7 +6779,7 @@
         <v>360</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>6</v>
@@ -6787,7 +6787,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B108" s="3">
         <v>0</v>
@@ -6796,7 +6796,7 @@
         <v>360</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>6</v>
@@ -6804,7 +6804,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B109" s="3">
         <v>0</v>
@@ -6813,7 +6813,7 @@
         <v>360</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>6</v>
@@ -6821,7 +6821,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B110" s="3">
         <v>0</v>
@@ -6830,7 +6830,7 @@
         <v>360</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>6</v>
@@ -6838,7 +6838,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B111" s="3">
         <v>0</v>
@@ -6847,7 +6847,7 @@
         <v>360</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>6</v>
@@ -6855,7 +6855,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B112" s="3">
         <v>1</v>
@@ -6864,7 +6864,7 @@
         <v>360</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>6</v>
@@ -6872,7 +6872,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B113" s="3">
         <v>2</v>
@@ -6881,7 +6881,7 @@
         <v>260</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>6</v>
@@ -6889,7 +6889,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="B114" s="3">
         <v>2</v>
@@ -6898,7 +6898,7 @@
         <v>260</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>6</v>
@@ -6906,7 +6906,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B115" s="3">
         <v>1</v>
@@ -6915,7 +6915,7 @@
         <v>260</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>6</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="B116" s="3">
         <v>1</v>
@@ -6932,7 +6932,7 @@
         <v>260</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>6</v>
@@ -6940,7 +6940,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="B117" s="3">
         <v>0</v>
@@ -6949,7 +6949,7 @@
         <v>260</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>6</v>
@@ -6957,7 +6957,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B118" s="3">
         <v>2</v>
@@ -6966,7 +6966,7 @@
         <v>260</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>6</v>
@@ -6974,7 +6974,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="B119" s="3">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>260</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>6</v>
@@ -6991,7 +6991,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B120" s="3">
         <v>0</v>
@@ -7000,7 +7000,7 @@
         <v>260</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>6</v>
@@ -7008,7 +7008,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="B121" s="3">
         <v>1</v>
@@ -7017,7 +7017,7 @@
         <v>260</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>6</v>
@@ -7025,7 +7025,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B122" s="3">
         <v>1</v>
@@ -7034,7 +7034,7 @@
         <v>260</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>6</v>
@@ -7042,7 +7042,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="B123" s="3">
         <v>1</v>
@@ -7051,7 +7051,7 @@
         <v>280</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>6</v>
@@ -7059,7 +7059,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="B124" s="3">
         <v>1</v>
@@ -7068,7 +7068,7 @@
         <v>280</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>6</v>
@@ -7076,7 +7076,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="B125" s="3">
         <v>1</v>
@@ -7085,7 +7085,7 @@
         <v>280</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>6</v>
@@ -7093,7 +7093,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="B126" s="3">
         <v>1</v>
@@ -7102,7 +7102,7 @@
         <v>260</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>6</v>
@@ -7110,7 +7110,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="B127" s="3">
         <v>3</v>
@@ -7119,7 +7119,7 @@
         <v>260</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>6</v>
@@ -7127,7 +7127,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="B128" s="3">
         <v>0</v>
@@ -7136,7 +7136,7 @@
         <v>260</v>
       </c>
       <c r="D128" s="8" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>6</v>
@@ -7144,7 +7144,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B129" s="3">
         <v>1</v>
@@ -7153,7 +7153,7 @@
         <v>260</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>6</v>
@@ -7161,7 +7161,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="B130" s="3">
         <v>2</v>
@@ -7170,7 +7170,7 @@
         <v>260</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>6</v>
@@ -7178,7 +7178,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="B131" s="3">
         <v>4</v>
@@ -7187,7 +7187,7 @@
         <v>150</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>6</v>
@@ -7195,16 +7195,16 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="B132" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C132" s="3">
         <v>150</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>6</v>
@@ -7212,7 +7212,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="B133" s="3">
         <v>0</v>
@@ -7221,7 +7221,7 @@
         <v>360</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>6</v>
@@ -7229,7 +7229,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="B134" s="3">
         <v>1</v>
@@ -7238,7 +7238,7 @@
         <v>260</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>6</v>
@@ -7246,7 +7246,7 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="B135" s="3">
         <v>1</v>
@@ -7255,7 +7255,7 @@
         <v>320</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>6</v>
@@ -7263,7 +7263,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B136" s="3">
         <v>1</v>
@@ -7272,7 +7272,7 @@
         <v>280</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>6</v>
@@ -7280,7 +7280,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="B137" s="3">
         <v>1</v>
@@ -7289,7 +7289,7 @@
         <v>280</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>6</v>
@@ -7297,7 +7297,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B138" s="3">
         <v>1</v>
@@ -7306,7 +7306,7 @@
         <v>280</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>6</v>
@@ -7314,7 +7314,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="B139" s="3">
         <v>1</v>
@@ -7323,7 +7323,7 @@
         <v>280</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>6</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B140" s="3">
         <v>1</v>
@@ -7340,7 +7340,7 @@
         <v>280</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>6</v>
@@ -7348,7 +7348,7 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="B141" s="3">
         <v>1</v>
@@ -7357,7 +7357,7 @@
         <v>320</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>6</v>
@@ -7365,7 +7365,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="B142" s="3">
         <v>1</v>
@@ -7374,7 +7374,7 @@
         <v>280</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>6</v>
@@ -7382,7 +7382,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="B143" s="3">
         <v>2</v>
@@ -7391,7 +7391,7 @@
         <v>300</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>6</v>
@@ -7399,7 +7399,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="B144" s="3">
         <v>4</v>
@@ -7408,7 +7408,7 @@
         <v>300</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>6</v>
@@ -7416,7 +7416,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="B145" s="3">
         <v>2</v>
@@ -7425,7 +7425,7 @@
         <v>260</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>6</v>
@@ -7433,7 +7433,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="B146" s="3">
         <v>0</v>
@@ -7442,7 +7442,7 @@
         <v>280</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>6</v>
@@ -7450,7 +7450,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="B147" s="3">
         <v>5</v>
@@ -7459,7 +7459,7 @@
         <v>280</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>6</v>
@@ -7467,7 +7467,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="B148" s="3">
         <v>1</v>
@@ -7476,7 +7476,7 @@
         <v>280</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>6</v>
@@ -7484,7 +7484,7 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="B149" s="3">
         <v>2</v>
@@ -7493,7 +7493,7 @@
         <v>280</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>6</v>
@@ -7501,7 +7501,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B150" s="3">
         <v>2</v>
@@ -7510,7 +7510,7 @@
         <v>280</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>6</v>
@@ -7518,7 +7518,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="B151" s="3">
         <v>1</v>
@@ -7527,7 +7527,7 @@
         <v>280</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>6</v>
@@ -7535,7 +7535,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="B152" s="3">
         <v>5</v>
@@ -7544,7 +7544,7 @@
         <v>260</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>6</v>
@@ -7552,16 +7552,16 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B153" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C153" s="3">
         <v>260</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>6</v>
@@ -7569,7 +7569,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="B154" s="3">
         <v>0</v>
@@ -7578,7 +7578,7 @@
         <v>260</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>6</v>
@@ -7586,7 +7586,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="B155" s="3">
         <v>0</v>
@@ -7595,7 +7595,7 @@
         <v>260</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>6</v>
@@ -7603,7 +7603,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="B156" s="3">
         <v>2</v>
@@ -7612,7 +7612,7 @@
         <v>260</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>6</v>
@@ -7620,7 +7620,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="B157" s="3">
         <v>0</v>
@@ -7629,7 +7629,7 @@
         <v>260</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>6</v>
@@ -7637,7 +7637,7 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="B158" s="3">
         <v>1</v>
@@ -7646,7 +7646,7 @@
         <v>260</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>6</v>
@@ -7654,7 +7654,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="B159" s="3">
         <v>1</v>
@@ -7663,7 +7663,7 @@
         <v>260</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>6</v>
@@ -7671,7 +7671,7 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="B160" s="3">
         <v>2</v>
@@ -7680,7 +7680,7 @@
         <v>260</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>6</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B161" s="3">
         <v>0</v>
@@ -7697,7 +7697,7 @@
         <v>260</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>6</v>
@@ -7705,7 +7705,7 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="B162" s="3">
         <v>4</v>
@@ -7714,7 +7714,7 @@
         <v>280</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>6</v>
@@ -7722,7 +7722,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="B163" s="3">
         <v>1</v>
@@ -7731,7 +7731,7 @@
         <v>360</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>6</v>
@@ -7739,7 +7739,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="B164" s="3">
         <v>3</v>
@@ -7748,7 +7748,7 @@
         <v>260</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>6</v>
@@ -7756,7 +7756,7 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="B165" s="3">
         <v>0</v>
@@ -7765,7 +7765,7 @@
         <v>260</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>6</v>
@@ -7773,7 +7773,7 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="B166" s="3">
         <v>0</v>
@@ -7782,7 +7782,7 @@
         <v>260</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>6</v>
@@ -7790,7 +7790,7 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="B167" s="3">
         <v>2</v>
@@ -7799,7 +7799,7 @@
         <v>260</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>6</v>
@@ -7807,7 +7807,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="B168" s="3">
         <v>2</v>
@@ -7816,7 +7816,7 @@
         <v>260</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>6</v>
@@ -7824,7 +7824,7 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B169" s="3">
         <v>2</v>
@@ -7833,7 +7833,7 @@
         <v>260</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>6</v>
@@ -7841,16 +7841,16 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="B170" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C170" s="3">
         <v>260</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="E170" s="3" t="s">
         <v>6</v>
@@ -7858,7 +7858,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="B171" s="3">
         <v>3</v>
@@ -7867,7 +7867,7 @@
         <v>400</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>6</v>
@@ -7875,16 +7875,16 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="B172" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C172" s="3">
         <v>280</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>6</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="B173" s="3">
         <v>2</v>
@@ -7901,7 +7901,7 @@
         <v>280</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>6</v>
@@ -7909,7 +7909,7 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="B174" s="3">
         <v>3</v>
@@ -7918,7 +7918,7 @@
         <v>280</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>6</v>
@@ -7926,7 +7926,7 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B175" s="3">
         <v>1</v>
@@ -7935,7 +7935,7 @@
         <v>280</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>6</v>
@@ -7943,7 +7943,7 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="B176" s="3">
         <v>2</v>
@@ -7952,7 +7952,7 @@
         <v>280</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>6</v>
@@ -7960,7 +7960,7 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="B177" s="3">
         <v>2</v>
@@ -7969,7 +7969,7 @@
         <v>280</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>6</v>
@@ -7977,7 +7977,7 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="B178" s="3">
         <v>3</v>
@@ -7986,7 +7986,7 @@
         <v>400</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>6</v>
@@ -7994,7 +7994,7 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="B179" s="3">
         <v>1</v>
@@ -8003,7 +8003,7 @@
         <v>260</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>6</v>
@@ -8011,7 +8011,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="B180" s="3">
         <v>1</v>
@@ -8020,7 +8020,7 @@
         <v>260</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>6</v>
@@ -8028,7 +8028,7 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="B181" s="3">
         <v>1</v>
@@ -8037,7 +8037,7 @@
         <v>260</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>6</v>
@@ -8045,7 +8045,7 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="B182" s="3">
         <v>3</v>
@@ -8054,7 +8054,7 @@
         <v>260</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>6</v>
@@ -8062,7 +8062,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B183" s="3">
         <v>3</v>
@@ -8071,7 +8071,7 @@
         <v>260</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>6</v>
@@ -8079,7 +8079,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="B184" s="3">
         <v>3</v>
@@ -8088,7 +8088,7 @@
         <v>260</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>6</v>
@@ -8096,7 +8096,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="B185" s="3">
         <v>3</v>
@@ -8105,7 +8105,7 @@
         <v>300</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>6</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="B186" s="3">
         <v>1</v>
@@ -8122,7 +8122,7 @@
         <v>260</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>6</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="B187" s="3">
         <v>2</v>
@@ -8139,7 +8139,7 @@
         <v>260</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>6</v>
@@ -8147,7 +8147,7 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="B188" s="3">
         <v>2</v>
@@ -8156,7 +8156,7 @@
         <v>260</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>6</v>
@@ -8164,7 +8164,7 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
       <c r="B189" s="3">
         <v>2</v>
@@ -8173,7 +8173,7 @@
         <v>260</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>6</v>
@@ -8181,7 +8181,7 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="B190" s="3">
         <v>2</v>
@@ -8190,7 +8190,7 @@
         <v>260</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>6</v>
@@ -8198,7 +8198,7 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="B191" s="3">
         <v>5</v>
@@ -8207,7 +8207,7 @@
         <v>400</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>6</v>
@@ -8215,7 +8215,7 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="B192" s="3">
         <v>9</v>
@@ -8224,7 +8224,7 @@
         <v>300</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>6</v>
@@ -8232,7 +8232,7 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="B193" s="3">
         <v>2</v>
@@ -8241,7 +8241,7 @@
         <v>300</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>6</v>
@@ -8249,7 +8249,7 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="B194" s="3">
         <v>1</v>
@@ -8258,7 +8258,7 @@
         <v>260</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>6</v>
@@ -8266,7 +8266,7 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="B195" s="3">
         <v>2</v>
@@ -8275,7 +8275,7 @@
         <v>260</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>6</v>
@@ -8283,7 +8283,7 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B196" s="3">
         <v>1</v>
@@ -8292,7 +8292,7 @@
         <v>260</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>6</v>
@@ -8300,7 +8300,7 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="B197" s="3">
         <v>2</v>
@@ -8309,7 +8309,7 @@
         <v>260</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>6</v>
@@ -8317,7 +8317,7 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="B198" s="3">
         <v>2</v>
@@ -8326,7 +8326,7 @@
         <v>260</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>6</v>
@@ -8334,7 +8334,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="B199" s="3">
         <v>2</v>
@@ -8343,7 +8343,7 @@
         <v>260</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>6</v>
@@ -8351,7 +8351,7 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="B200" s="3">
         <v>2</v>
@@ -8360,7 +8360,7 @@
         <v>260</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>6</v>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="B201" s="3">
         <v>2</v>
@@ -8377,7 +8377,7 @@
         <v>260</v>
       </c>
       <c r="D201" s="8" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>6</v>
@@ -8385,7 +8385,7 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="13" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="B202" s="14">
         <v>0</v>
@@ -8394,7 +8394,7 @@
         <v>280</v>
       </c>
       <c r="D202" s="15" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E202" s="14" t="s">
         <v>35</v>
@@ -8487,7 +8487,7 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B208" s="3">
         <v>2</v>
@@ -8504,7 +8504,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="B209" s="3">
         <v>0</v>
@@ -8513,7 +8513,7 @@
         <v>260</v>
       </c>
       <c r="D209" s="8" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="E209" s="3" t="s">
         <v>35</v>
@@ -8572,7 +8572,7 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B213" s="3">
         <v>5</v>
@@ -8581,7 +8581,7 @@
         <v>400</v>
       </c>
       <c r="D213" s="8" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="E213" s="3" t="s">
         <v>35</v>
@@ -8589,7 +8589,7 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="7" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="B214" s="3">
         <v>1</v>
@@ -8606,7 +8606,7 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
       <c r="B215" s="3">
         <v>4</v>
@@ -8623,7 +8623,7 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B216" s="3">
         <v>3</v>
@@ -8632,7 +8632,7 @@
         <v>1000</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E216" s="3" t="s">
         <v>35</v>
@@ -8640,10 +8640,10 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="B217" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C217" s="3">
         <v>360</v>
@@ -8657,7 +8657,7 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="7" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="B218" s="3">
         <v>6</v>
@@ -8700,7 +8700,7 @@
         <v>220</v>
       </c>
       <c r="D220" s="8" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="E220" s="3" t="s">
         <v>35</v>
@@ -8717,7 +8717,7 @@
         <v>220</v>
       </c>
       <c r="D221" s="8" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="E221" s="3" t="s">
         <v>35</v>
@@ -8734,7 +8734,7 @@
         <v>200</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E222" s="3" t="s">
         <v>35</v>
@@ -8742,7 +8742,7 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="B223" s="6">
         <v>0</v>
@@ -8751,7 +8751,7 @@
         <v>260</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="E223" s="3" t="s">
         <v>35</v>
@@ -8759,16 +8759,16 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="7" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B224" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C224" s="6">
         <v>220</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="E224" s="3" t="s">
         <v>35</v>
@@ -8776,7 +8776,7 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B225" s="6">
         <v>2</v>
@@ -8785,7 +8785,7 @@
         <v>220</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="E225" s="3" t="s">
         <v>35</v>
@@ -8793,7 +8793,7 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="7" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B226" s="6">
         <v>1</v>
@@ -8802,7 +8802,7 @@
         <v>220</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>35</v>
@@ -8810,7 +8810,7 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B227" s="6">
         <v>3</v>
@@ -8819,7 +8819,7 @@
         <v>220</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>35</v>
@@ -8836,7 +8836,7 @@
         <v>220</v>
       </c>
       <c r="D228" s="8" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>35</v>
@@ -8844,7 +8844,7 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
-        <v>401</v>
+        <v>1455</v>
       </c>
       <c r="B229" s="3">
         <v>4</v>
@@ -8853,7 +8853,7 @@
         <v>260</v>
       </c>
       <c r="D229" s="8" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>35</v>
@@ -8861,16 +8861,16 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="7" t="s">
-        <v>402</v>
+        <v>1454</v>
       </c>
       <c r="B230" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C230" s="3">
         <v>260</v>
       </c>
       <c r="D230" s="8" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E230" s="3" t="s">
         <v>35</v>
@@ -8887,7 +8887,7 @@
         <v>220</v>
       </c>
       <c r="D231" s="8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>35</v>
@@ -8963,7 +8963,7 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B236" s="3">
         <v>5</v>
@@ -8980,7 +8980,7 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B237" s="3">
         <v>2</v>
@@ -8989,7 +8989,7 @@
         <v>260</v>
       </c>
       <c r="D237" s="8" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>35</v>
@@ -8997,7 +8997,7 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="7" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B238" s="3">
         <v>3</v>
@@ -9006,7 +9006,7 @@
         <v>260</v>
       </c>
       <c r="D238" s="8" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="E238" s="3" t="s">
         <v>35</v>
@@ -9014,7 +9014,7 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B239" s="3">
         <v>3</v>
@@ -9023,7 +9023,7 @@
         <v>260</v>
       </c>
       <c r="D239" s="8" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E239" s="3" t="s">
         <v>35</v>
@@ -9031,7 +9031,7 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B240" s="3">
         <v>3</v>
@@ -9040,7 +9040,7 @@
         <v>260</v>
       </c>
       <c r="D240" s="8" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="E240" s="3" t="s">
         <v>35</v>
@@ -9048,7 +9048,7 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B241" s="3">
         <v>1</v>
@@ -9057,7 +9057,7 @@
         <v>270</v>
       </c>
       <c r="D241" s="8" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>35</v>
@@ -9065,7 +9065,7 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="7" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B242" s="3">
         <v>2</v>
@@ -9074,7 +9074,7 @@
         <v>260</v>
       </c>
       <c r="D242" s="8" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="E242" s="3" t="s">
         <v>35</v>
@@ -9082,7 +9082,7 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="B243" s="3">
         <v>0</v>
@@ -9091,7 +9091,7 @@
         <v>260</v>
       </c>
       <c r="D243" s="8" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="E243" s="3" t="s">
         <v>35</v>
@@ -9099,7 +9099,7 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="7" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="B244" s="3">
         <v>1</v>
@@ -9108,7 +9108,7 @@
         <v>220</v>
       </c>
       <c r="D244" s="8" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="E244" s="3" t="s">
         <v>35</v>
@@ -9116,7 +9116,7 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="B245" s="3">
         <v>5</v>
@@ -9125,7 +9125,7 @@
         <v>220</v>
       </c>
       <c r="D245" s="8" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="E245" s="3" t="s">
         <v>35</v>
@@ -9133,7 +9133,7 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="7" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="B246" s="3">
         <v>1</v>
@@ -9142,7 +9142,7 @@
         <v>260</v>
       </c>
       <c r="D246" s="8" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="E246" s="3" t="s">
         <v>35</v>
@@ -9150,7 +9150,7 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="B247" s="3">
         <v>1</v>
@@ -9159,7 +9159,7 @@
         <v>220</v>
       </c>
       <c r="D247" s="8" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="E247" s="3" t="s">
         <v>35</v>
@@ -9167,7 +9167,7 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="7" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="B248" s="3">
         <v>1</v>
@@ -9176,7 +9176,7 @@
         <v>260</v>
       </c>
       <c r="D248" s="8" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="E248" s="3" t="s">
         <v>35</v>
@@ -9184,7 +9184,7 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="B249" s="3">
         <v>3</v>
@@ -9193,7 +9193,7 @@
         <v>220</v>
       </c>
       <c r="D249" s="8" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="E249" s="3" t="s">
         <v>35</v>
@@ -9201,7 +9201,7 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="7" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="B250" s="3">
         <v>1</v>
@@ -9210,7 +9210,7 @@
         <v>260</v>
       </c>
       <c r="D250" s="8" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="E250" s="3" t="s">
         <v>35</v>
@@ -9218,7 +9218,7 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="7" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="B251" s="3">
         <v>2</v>
@@ -9227,7 +9227,7 @@
         <v>220</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>35</v>
@@ -9235,16 +9235,16 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="7" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="B252" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C252" s="3">
         <v>260</v>
       </c>
       <c r="D252" s="8" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>35</v>
@@ -9252,7 +9252,7 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="B253" s="3">
         <v>1</v>
@@ -9261,7 +9261,7 @@
         <v>220</v>
       </c>
       <c r="D253" s="8" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>35</v>
@@ -9269,7 +9269,7 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="7" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B254" s="3">
         <v>1</v>
@@ -9278,7 +9278,7 @@
         <v>260</v>
       </c>
       <c r="D254" s="8" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>35</v>
@@ -9286,7 +9286,7 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="B255" s="3">
         <v>3</v>
@@ -9295,7 +9295,7 @@
         <v>300</v>
       </c>
       <c r="D255" s="8" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="E255" s="3" t="s">
         <v>35</v>
@@ -9303,7 +9303,7 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="7" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="B256" s="3">
         <v>3</v>
@@ -9312,7 +9312,7 @@
         <v>300</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="E256" s="3" t="s">
         <v>35</v>
@@ -9320,7 +9320,7 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="B257" s="3">
         <v>2</v>
@@ -9329,7 +9329,7 @@
         <v>260</v>
       </c>
       <c r="D257" s="8" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="E257" s="3" t="s">
         <v>35</v>
@@ -9337,7 +9337,7 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="B258" s="3">
         <v>2</v>
@@ -9346,7 +9346,7 @@
         <v>260</v>
       </c>
       <c r="D258" s="8" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="E258" s="3" t="s">
         <v>35</v>
@@ -9354,7 +9354,7 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="B259" s="3">
         <v>4</v>
@@ -9363,7 +9363,7 @@
         <v>260</v>
       </c>
       <c r="D259" s="8" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>35</v>
@@ -9371,7 +9371,7 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="7" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="B260" s="3">
         <v>2</v>
@@ -9380,7 +9380,7 @@
         <v>260</v>
       </c>
       <c r="D260" s="8" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>35</v>
@@ -9388,7 +9388,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="B261" s="3">
         <v>1</v>
@@ -9397,7 +9397,7 @@
         <v>260</v>
       </c>
       <c r="D261" s="8" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>35</v>
@@ -9405,7 +9405,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="7" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="B262" s="3">
         <v>5</v>
@@ -9414,7 +9414,7 @@
         <v>260</v>
       </c>
       <c r="D262" s="8" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="E262" s="3" t="s">
         <v>35</v>
@@ -9422,7 +9422,7 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="B263" s="3">
         <v>3</v>
@@ -9431,7 +9431,7 @@
         <v>280</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>35</v>
@@ -9439,7 +9439,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="B264" s="3">
         <v>2</v>
@@ -9448,7 +9448,7 @@
         <v>280</v>
       </c>
       <c r="D264" s="8" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>35</v>
@@ -9456,7 +9456,7 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="B265" s="3">
         <v>2</v>
@@ -9465,7 +9465,7 @@
         <v>280</v>
       </c>
       <c r="D265" s="8" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>35</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="7" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
       <c r="B266" s="3">
         <v>2</v>
@@ -9482,7 +9482,7 @@
         <v>260</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="E266" s="3" t="s">
         <v>35</v>
@@ -9507,7 +9507,7 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B268" s="3">
         <v>1</v>
@@ -9516,7 +9516,7 @@
         <v>360</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>44</v>
@@ -9524,7 +9524,7 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B269" s="3">
         <v>2</v>
@@ -9575,7 +9575,7 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B272" s="3">
         <v>0</v>
@@ -9584,7 +9584,7 @@
         <v>400</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E272" s="3" t="s">
         <v>44</v>
@@ -9592,7 +9592,7 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B273" s="3">
         <v>0</v>
@@ -9626,7 +9626,7 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="B275" s="3">
         <v>1</v>
@@ -9635,7 +9635,7 @@
         <v>300</v>
       </c>
       <c r="D275" s="8" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>44</v>
@@ -9669,7 +9669,7 @@
         <v>300</v>
       </c>
       <c r="D277" s="8" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="E277" s="3" t="s">
         <v>44</v>
@@ -9677,7 +9677,7 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="7" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B278" s="3">
         <v>2</v>
@@ -9686,7 +9686,7 @@
         <v>320</v>
       </c>
       <c r="D278" s="8" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E278" s="3" t="s">
         <v>44</v>
@@ -9694,7 +9694,7 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B279" s="3">
         <v>2</v>
@@ -9703,7 +9703,7 @@
         <v>320</v>
       </c>
       <c r="D279" s="8" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>44</v>
@@ -9711,7 +9711,7 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B280" s="3">
         <v>2</v>
@@ -9720,7 +9720,7 @@
         <v>360</v>
       </c>
       <c r="D280" s="8" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>44</v>
@@ -9728,7 +9728,7 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B281" s="3">
         <v>1</v>
@@ -9737,7 +9737,7 @@
         <v>360</v>
       </c>
       <c r="D281" s="8" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E281" s="3" t="s">
         <v>44</v>
@@ -9745,7 +9745,7 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B282" s="3">
         <v>2</v>
@@ -9754,7 +9754,7 @@
         <v>300</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E282" s="3" t="s">
         <v>44</v>
@@ -9799,13 +9799,13 @@
         <v>320</v>
       </c>
       <c r="B285" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C285" s="3">
         <v>300</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="E285" s="3" t="s">
         <v>44</v>
@@ -9822,7 +9822,7 @@
         <v>300</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="E286" s="3" t="s">
         <v>44</v>
@@ -9830,7 +9830,7 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="7" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B287" s="3">
         <v>0</v>
@@ -9847,7 +9847,7 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="7" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B288" s="3">
         <v>0</v>
@@ -9983,7 +9983,7 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B296" s="3">
         <v>1</v>
@@ -9992,7 +9992,7 @@
         <v>300</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="E296" s="3" t="s">
         <v>44</v>
@@ -10000,7 +10000,7 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="7" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B297" s="3">
         <v>1</v>
@@ -10009,7 +10009,7 @@
         <v>300</v>
       </c>
       <c r="D297" s="8" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="E297" s="3" t="s">
         <v>44</v>
@@ -10425,7 +10425,7 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B322" s="3">
         <v>2</v>
@@ -10434,7 +10434,7 @@
         <v>300</v>
       </c>
       <c r="D322" s="8" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="E322" s="3" t="s">
         <v>44</v>
@@ -10510,7 +10510,7 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B327" s="3">
         <v>1</v>
@@ -10519,7 +10519,7 @@
         <v>300</v>
       </c>
       <c r="D327" s="7" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="E327" s="3" t="s">
         <v>44</v>
@@ -10680,7 +10680,7 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B337" s="3">
         <v>2</v>
@@ -10689,7 +10689,7 @@
         <v>300</v>
       </c>
       <c r="D337" s="8" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="E337" s="3" t="s">
         <v>44</v>
@@ -10697,7 +10697,7 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B338" s="3">
         <v>1</v>
@@ -10706,7 +10706,7 @@
         <v>300</v>
       </c>
       <c r="D338" s="8" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E338" s="3" t="s">
         <v>44</v>
@@ -10714,7 +10714,7 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="7" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B339" s="3">
         <v>2</v>
@@ -10723,7 +10723,7 @@
         <v>300</v>
       </c>
       <c r="D339" s="8" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="E339" s="3" t="s">
         <v>44</v>
@@ -10731,16 +10731,16 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" s="7" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B340" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C340" s="3">
         <v>300</v>
       </c>
       <c r="D340" s="8" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E340" s="3" t="s">
         <v>44</v>
@@ -10748,7 +10748,7 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B341" s="3">
         <v>1</v>
@@ -10757,7 +10757,7 @@
         <v>300</v>
       </c>
       <c r="D341" s="8" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E341" s="3" t="s">
         <v>44</v>
@@ -10765,7 +10765,7 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="7" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B342" s="3">
         <v>2</v>
@@ -10774,7 +10774,7 @@
         <v>300</v>
       </c>
       <c r="D342" s="8" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E342" s="3" t="s">
         <v>44</v>
@@ -10782,7 +10782,7 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B343" s="3">
         <v>1</v>
@@ -10791,7 +10791,7 @@
         <v>300</v>
       </c>
       <c r="D343" s="8" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E343" s="3" t="s">
         <v>44</v>
@@ -10884,7 +10884,7 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B349" s="3">
         <v>1</v>
@@ -10893,7 +10893,7 @@
         <v>280</v>
       </c>
       <c r="D349" s="8" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E349" s="3" t="s">
         <v>44</v>
@@ -10901,7 +10901,7 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B350" s="3">
         <v>1</v>
@@ -10910,7 +10910,7 @@
         <v>280</v>
       </c>
       <c r="D350" s="8" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E350" s="3" t="s">
         <v>44</v>
@@ -10918,7 +10918,7 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="7" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B351" s="3">
         <v>1</v>
@@ -10927,7 +10927,7 @@
         <v>280</v>
       </c>
       <c r="D351" s="8" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E351" s="3" t="s">
         <v>44</v>
@@ -10969,7 +10969,7 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="B354" s="3">
         <v>1</v>
@@ -10978,7 +10978,7 @@
         <v>300</v>
       </c>
       <c r="D354" s="8" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="E354" s="3" t="s">
         <v>44</v>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="7" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="B355" s="3">
         <v>1</v>
@@ -10995,7 +10995,7 @@
         <v>320</v>
       </c>
       <c r="D355" s="8" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>44</v>
@@ -11003,7 +11003,7 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B356" s="3">
         <v>1</v>
@@ -11012,7 +11012,7 @@
         <v>300</v>
       </c>
       <c r="D356" s="8" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="E356" s="3" t="s">
         <v>44</v>
@@ -11020,7 +11020,7 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="B357" s="3">
         <v>1</v>
@@ -11029,7 +11029,7 @@
         <v>320</v>
       </c>
       <c r="D357" s="8" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="E357" s="3" t="s">
         <v>44</v>
@@ -11037,7 +11037,7 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="7" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B358" s="3">
         <v>1</v>
@@ -11046,7 +11046,7 @@
         <v>260</v>
       </c>
       <c r="D358" s="8" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="E358" s="3" t="s">
         <v>44</v>
@@ -11054,7 +11054,7 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" s="7" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="B359" s="3">
         <v>1</v>
@@ -11063,7 +11063,7 @@
         <v>360</v>
       </c>
       <c r="D359" s="8" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="E359" s="3" t="s">
         <v>44</v>
@@ -11071,7 +11071,7 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" s="7" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="B360" s="3">
         <v>1</v>
@@ -11080,7 +11080,7 @@
         <v>360</v>
       </c>
       <c r="D360" s="8" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="E360" s="3" t="s">
         <v>44</v>
@@ -11088,7 +11088,7 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" s="7" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="B361" s="3">
         <v>1</v>
@@ -11097,7 +11097,7 @@
         <v>360</v>
       </c>
       <c r="D361" s="8" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="E361" s="3" t="s">
         <v>44</v>
@@ -11105,7 +11105,7 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="7" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="B362" s="3">
         <v>1</v>
@@ -11114,7 +11114,7 @@
         <v>360</v>
       </c>
       <c r="D362" s="8" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="E362" s="3" t="s">
         <v>44</v>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="7" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="B363" s="3">
         <v>1</v>
@@ -11131,7 +11131,7 @@
         <v>360</v>
       </c>
       <c r="D363" s="8" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="E363" s="3" t="s">
         <v>44</v>
@@ -11139,7 +11139,7 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="7" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="B364" s="3">
         <v>2</v>
@@ -11148,7 +11148,7 @@
         <v>360</v>
       </c>
       <c r="D364" s="8" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="E364" s="3" t="s">
         <v>44</v>
@@ -11156,7 +11156,7 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" s="7" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="B365" s="3">
         <v>1</v>
@@ -11165,7 +11165,7 @@
         <v>360</v>
       </c>
       <c r="D365" s="8" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="E365" s="3" t="s">
         <v>44</v>
@@ -11173,7 +11173,7 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" s="7" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="B366" s="3">
         <v>1</v>
@@ -11182,7 +11182,7 @@
         <v>360</v>
       </c>
       <c r="D366" s="8" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="E366" s="3" t="s">
         <v>44</v>
@@ -11190,7 +11190,7 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="7" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="B367" s="3">
         <v>1</v>
@@ -11199,7 +11199,7 @@
         <v>320</v>
       </c>
       <c r="D367" s="8" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="E367" s="3" t="s">
         <v>44</v>
@@ -11207,7 +11207,7 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="7" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="B368" s="3">
         <v>3</v>
@@ -11216,7 +11216,7 @@
         <v>300</v>
       </c>
       <c r="D368" s="8" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="E368" s="3" t="s">
         <v>44</v>
@@ -11224,7 +11224,7 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" s="7" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="B369" s="3">
         <v>3</v>
@@ -11233,7 +11233,7 @@
         <v>320</v>
       </c>
       <c r="D369" s="8" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>44</v>
@@ -11241,7 +11241,7 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" s="7" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="B370" s="3">
         <v>3</v>
@@ -11250,7 +11250,7 @@
         <v>320</v>
       </c>
       <c r="D370" s="8" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="E370" s="3" t="s">
         <v>44</v>
@@ -11267,7 +11267,7 @@
         <v>260</v>
       </c>
       <c r="D371" s="8" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="E371" s="3" t="s">
         <v>100</v>
@@ -11292,7 +11292,7 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B373" s="3">
         <v>2</v>
@@ -11343,7 +11343,7 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="7" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B376" s="3">
         <v>2</v>
@@ -11352,7 +11352,7 @@
         <v>260</v>
       </c>
       <c r="D376" s="8" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="E376" s="3" t="s">
         <v>100</v>
@@ -11360,7 +11360,7 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B377" s="3">
         <v>3</v>
@@ -11369,7 +11369,7 @@
         <v>260</v>
       </c>
       <c r="D377" s="8" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E377" s="3" t="s">
         <v>100</v>
@@ -11377,7 +11377,7 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B378" s="3">
         <v>2</v>
@@ -11386,7 +11386,7 @@
         <v>260</v>
       </c>
       <c r="D378" s="8" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="E378" s="3" t="s">
         <v>100</v>
@@ -11394,7 +11394,7 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="B379" s="3">
         <v>2</v>
@@ -11403,7 +11403,7 @@
         <v>260</v>
       </c>
       <c r="D379" s="8" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="E379" s="3" t="s">
         <v>100</v>
@@ -11411,7 +11411,7 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B380" s="3">
         <v>1</v>
@@ -11420,7 +11420,7 @@
         <v>260</v>
       </c>
       <c r="D380" s="8" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E380" s="3" t="s">
         <v>100</v>
@@ -11428,7 +11428,7 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="7" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B381" s="3">
         <v>2</v>
@@ -11445,7 +11445,7 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B382" s="3">
         <v>1</v>
@@ -11454,7 +11454,7 @@
         <v>260</v>
       </c>
       <c r="D382" s="8" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E382" s="3" t="s">
         <v>100</v>
@@ -11462,7 +11462,7 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B383" s="3">
         <v>2</v>
@@ -11471,7 +11471,7 @@
         <v>260</v>
       </c>
       <c r="D383" s="8" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E383" s="3" t="s">
         <v>100</v>
@@ -11479,7 +11479,7 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B384" s="3">
         <v>1</v>
@@ -11488,7 +11488,7 @@
         <v>260</v>
       </c>
       <c r="D384" s="8" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="E384" s="3" t="s">
         <v>100</v>
@@ -11496,7 +11496,7 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="7" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B385" s="3">
         <v>0</v>
@@ -11505,7 +11505,7 @@
         <v>260</v>
       </c>
       <c r="D385" s="8" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E385" s="3" t="s">
         <v>100</v>
@@ -11513,7 +11513,7 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B386" s="3">
         <v>1</v>
@@ -11522,7 +11522,7 @@
         <v>260</v>
       </c>
       <c r="D386" s="8" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E386" s="3" t="s">
         <v>100</v>
@@ -11530,7 +11530,7 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B387" s="3">
         <v>1</v>
@@ -11539,7 +11539,7 @@
         <v>260</v>
       </c>
       <c r="D387" s="8" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E387" s="3" t="s">
         <v>100</v>
@@ -11547,7 +11547,7 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B388" s="3">
         <v>1</v>
@@ -11556,7 +11556,7 @@
         <v>260</v>
       </c>
       <c r="D388" s="8" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E388" s="3" t="s">
         <v>100</v>
@@ -11564,7 +11564,7 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B389" s="3">
         <v>1</v>
@@ -11573,7 +11573,7 @@
         <v>260</v>
       </c>
       <c r="D389" s="8" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="E389" s="3" t="s">
         <v>100</v>
@@ -11581,7 +11581,7 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="7" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="B390" s="3">
         <v>1</v>
@@ -11590,7 +11590,7 @@
         <v>500</v>
       </c>
       <c r="D390" s="8" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="E390" s="3" t="s">
         <v>100</v>
@@ -11615,7 +11615,7 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B392" s="3">
         <v>0</v>
@@ -11683,7 +11683,7 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B396" s="3">
         <v>0</v>
@@ -11743,7 +11743,7 @@
         <v>260</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="E399" s="3" t="s">
         <v>100</v>
@@ -11760,7 +11760,7 @@
         <v>260</v>
       </c>
       <c r="D400" s="8" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="E400" s="3" t="s">
         <v>100</v>
@@ -11785,7 +11785,7 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="7" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B402" s="3">
         <v>3</v>
@@ -11794,7 +11794,7 @@
         <v>260</v>
       </c>
       <c r="D402" s="8" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="E402" s="3" t="s">
         <v>100</v>
@@ -11802,7 +11802,7 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="7" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B403" s="3">
         <v>2</v>
@@ -11828,7 +11828,7 @@
         <v>260</v>
       </c>
       <c r="D404" s="8" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E404" s="3" t="s">
         <v>100</v>
@@ -11839,7 +11839,7 @@
         <v>108</v>
       </c>
       <c r="B405" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C405" s="3">
         <v>360</v>
@@ -11938,7 +11938,7 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" s="7" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="B411" s="3">
         <v>0</v>
@@ -11947,7 +11947,7 @@
         <v>800</v>
       </c>
       <c r="D411" s="8" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="E411" s="3" t="s">
         <v>100</v>
@@ -11955,7 +11955,7 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="7" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="B412" s="3">
         <v>1</v>
@@ -11964,7 +11964,7 @@
         <v>800</v>
       </c>
       <c r="D412" s="8" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E412" s="3" t="s">
         <v>100</v>
@@ -11972,7 +11972,7 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="7" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="B413" s="3">
         <v>1</v>
@@ -11981,7 +11981,7 @@
         <v>800</v>
       </c>
       <c r="D413" s="8" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="E413" s="3" t="s">
         <v>100</v>
@@ -11989,7 +11989,7 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="7" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="B414" s="3">
         <v>1</v>
@@ -11998,7 +11998,7 @@
         <v>800</v>
       </c>
       <c r="D414" s="8" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E414" s="3" t="s">
         <v>100</v>
@@ -12006,7 +12006,7 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="7" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="B415" s="3">
         <v>0</v>
@@ -12015,7 +12015,7 @@
         <v>800</v>
       </c>
       <c r="D415" s="8" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E415" s="3" t="s">
         <v>100</v>
@@ -12023,7 +12023,7 @@
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" s="7" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="B416" s="3">
         <v>1</v>
@@ -12032,7 +12032,7 @@
         <v>800</v>
       </c>
       <c r="D416" s="8" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="E416" s="3" t="s">
         <v>100</v>
@@ -12049,7 +12049,7 @@
         <v>260</v>
       </c>
       <c r="D417" s="8" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E417" s="3" t="s">
         <v>100</v>
@@ -12057,7 +12057,7 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="7" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B418" s="3">
         <v>0</v>
@@ -12066,7 +12066,7 @@
         <v>260</v>
       </c>
       <c r="D418" s="8" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E418" s="3" t="s">
         <v>100</v>
@@ -12074,7 +12074,7 @@
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" s="7" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B419" s="3">
         <v>0</v>
@@ -12083,7 +12083,7 @@
         <v>260</v>
       </c>
       <c r="D419" s="8" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E419" s="3" t="s">
         <v>100</v>
@@ -12091,7 +12091,7 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B420" s="3">
         <v>0</v>
@@ -12100,7 +12100,7 @@
         <v>260</v>
       </c>
       <c r="D420" s="8" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E420" s="3" t="s">
         <v>100</v>
@@ -12108,7 +12108,7 @@
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B421" s="3">
         <v>1</v>
@@ -12117,7 +12117,7 @@
         <v>260</v>
       </c>
       <c r="D421" s="8" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E421" s="3" t="s">
         <v>100</v>
@@ -12125,7 +12125,7 @@
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" s="7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B422" s="3">
         <v>0</v>
@@ -12134,7 +12134,7 @@
         <v>260</v>
       </c>
       <c r="D422" s="8" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E422" s="3" t="s">
         <v>100</v>
@@ -12151,7 +12151,7 @@
         <v>260</v>
       </c>
       <c r="D423" s="8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E423" s="3" t="s">
         <v>100</v>
@@ -12159,7 +12159,7 @@
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B424" s="3">
         <v>0</v>
@@ -12168,7 +12168,7 @@
         <v>260</v>
       </c>
       <c r="D424" s="8" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E424" s="3" t="s">
         <v>100</v>
@@ -12176,7 +12176,7 @@
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" s="7" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B425" s="3">
         <v>0</v>
@@ -12185,7 +12185,7 @@
         <v>260</v>
       </c>
       <c r="D425" s="8" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E425" s="3" t="s">
         <v>100</v>
@@ -12193,7 +12193,7 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="7" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B426" s="3">
         <v>0</v>
@@ -12202,7 +12202,7 @@
         <v>260</v>
       </c>
       <c r="D426" s="8" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E426" s="3" t="s">
         <v>100</v>
@@ -12210,7 +12210,7 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" s="7" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B427" s="3">
         <v>0</v>
@@ -12219,7 +12219,7 @@
         <v>260</v>
       </c>
       <c r="D427" s="8" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E427" s="3" t="s">
         <v>100</v>
@@ -12227,7 +12227,7 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" s="7" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B428" s="3">
         <v>1</v>
@@ -12236,7 +12236,7 @@
         <v>260</v>
       </c>
       <c r="D428" s="8" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E428" s="3" t="s">
         <v>100</v>
@@ -12244,7 +12244,7 @@
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" s="7" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B429" s="3">
         <v>0</v>
@@ -12253,7 +12253,7 @@
         <v>260</v>
       </c>
       <c r="D429" s="8" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="E429" s="3" t="s">
         <v>100</v>
@@ -12261,7 +12261,7 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" s="7" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B430" s="3">
         <v>1</v>
@@ -12270,7 +12270,7 @@
         <v>260</v>
       </c>
       <c r="D430" s="8" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E430" s="3" t="s">
         <v>100</v>
@@ -12278,7 +12278,7 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" s="7" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B431" s="3">
         <v>2</v>
@@ -12287,7 +12287,7 @@
         <v>260</v>
       </c>
       <c r="D431" s="8" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="E431" s="3" t="s">
         <v>100</v>
@@ -12295,7 +12295,7 @@
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" s="7" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B432" s="3">
         <v>1</v>
@@ -12304,7 +12304,7 @@
         <v>260</v>
       </c>
       <c r="D432" s="8" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="E432" s="3" t="s">
         <v>100</v>
@@ -12312,7 +12312,7 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="7" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B433" s="3">
         <v>2</v>
@@ -12321,7 +12321,7 @@
         <v>260</v>
       </c>
       <c r="D433" s="8" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E433" s="3" t="s">
         <v>100</v>
@@ -12329,7 +12329,7 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="7" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="B434" s="3">
         <v>0</v>
@@ -12338,7 +12338,7 @@
         <v>260</v>
       </c>
       <c r="D434" s="8" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="E434" s="3" t="s">
         <v>100</v>
@@ -12346,7 +12346,7 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="7" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B435" s="3">
         <v>2</v>
@@ -12355,7 +12355,7 @@
         <v>260</v>
       </c>
       <c r="D435" s="8" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E435" s="3" t="s">
         <v>100</v>
@@ -12372,7 +12372,7 @@
         <v>260</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="E436" s="3" t="s">
         <v>116</v>
@@ -12380,7 +12380,7 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="7" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="B437" s="3">
         <v>1</v>
@@ -12389,7 +12389,7 @@
         <v>260</v>
       </c>
       <c r="D437" s="8" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="E437" s="3" t="s">
         <v>116</v>
@@ -12397,7 +12397,7 @@
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" s="7" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B438" s="3">
         <v>1</v>
@@ -12406,7 +12406,7 @@
         <v>260</v>
       </c>
       <c r="D438" s="8" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="E438" s="3" t="s">
         <v>116</v>
@@ -12431,7 +12431,7 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="7" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B440" s="3">
         <v>3</v>
@@ -12457,7 +12457,7 @@
         <v>240</v>
       </c>
       <c r="D441" s="8" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="E441" s="3" t="s">
         <v>116</v>
@@ -12465,7 +12465,7 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B442" s="3">
         <v>1</v>
@@ -12474,7 +12474,7 @@
         <v>400</v>
       </c>
       <c r="D442" s="8" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E442" s="3" t="s">
         <v>116</v>
@@ -12482,7 +12482,7 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B443" s="3">
         <v>1</v>
@@ -12491,7 +12491,7 @@
         <v>400</v>
       </c>
       <c r="D443" s="8" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E443" s="3" t="s">
         <v>116</v>
@@ -12499,7 +12499,7 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B444" s="3">
         <v>0</v>
@@ -12508,7 +12508,7 @@
         <v>360</v>
       </c>
       <c r="D444" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E444" s="3" t="s">
         <v>116</v>
@@ -12516,7 +12516,7 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B445" s="3">
         <v>2</v>
@@ -12525,7 +12525,7 @@
         <v>400</v>
       </c>
       <c r="D445" s="8" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E445" s="3" t="s">
         <v>116</v>
@@ -12533,7 +12533,7 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B446" s="3">
         <v>0</v>
@@ -12542,7 +12542,7 @@
         <v>360</v>
       </c>
       <c r="D446" s="8" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E446" s="3" t="s">
         <v>116</v>
@@ -12550,7 +12550,7 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B447" s="3">
         <v>4</v>
@@ -12559,7 +12559,7 @@
         <v>360</v>
       </c>
       <c r="D447" s="8" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E447" s="3" t="s">
         <v>116</v>
@@ -12567,7 +12567,7 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B448" s="3">
         <v>2</v>
@@ -12576,7 +12576,7 @@
         <v>400</v>
       </c>
       <c r="D448" s="8" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E448" s="3" t="s">
         <v>116</v>
@@ -12584,7 +12584,7 @@
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B449" s="3">
         <v>1</v>
@@ -12593,7 +12593,7 @@
         <v>360</v>
       </c>
       <c r="D449" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E449" s="3" t="s">
         <v>116</v>
@@ -12601,7 +12601,7 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B450" s="3">
         <v>2</v>
@@ -12610,7 +12610,7 @@
         <v>360</v>
       </c>
       <c r="D450" s="8" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E450" s="3" t="s">
         <v>116</v>
@@ -12618,7 +12618,7 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B451" s="3">
         <v>3</v>
@@ -12627,7 +12627,7 @@
         <v>360</v>
       </c>
       <c r="D451" s="8" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E451" s="3" t="s">
         <v>116</v>
@@ -12635,7 +12635,7 @@
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B452" s="3">
         <v>2</v>
@@ -12644,7 +12644,7 @@
         <v>360</v>
       </c>
       <c r="D452" s="8" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E452" s="3" t="s">
         <v>116</v>
@@ -12652,7 +12652,7 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B453" s="3">
         <v>1</v>
@@ -12661,7 +12661,7 @@
         <v>260</v>
       </c>
       <c r="D453" s="8" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="E453" s="3" t="s">
         <v>116</v>
@@ -12669,7 +12669,7 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B454" s="3">
         <v>0</v>
@@ -12678,7 +12678,7 @@
         <v>260</v>
       </c>
       <c r="D454" s="8" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="E454" s="3" t="s">
         <v>116</v>
@@ -12686,7 +12686,7 @@
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" s="7" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B455" s="3">
         <v>1</v>
@@ -12695,7 +12695,7 @@
         <v>260</v>
       </c>
       <c r="D455" s="8" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E455" s="3" t="s">
         <v>116</v>
@@ -12703,7 +12703,7 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B456" s="3">
         <v>2</v>
@@ -12712,7 +12712,7 @@
         <v>260</v>
       </c>
       <c r="D456" s="8" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="E456" s="3" t="s">
         <v>116</v>
@@ -12720,7 +12720,7 @@
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B457" s="3">
         <v>1</v>
@@ -12729,7 +12729,7 @@
         <v>260</v>
       </c>
       <c r="D457" s="8" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="E457" s="6" t="s">
         <v>116</v>
@@ -12737,7 +12737,7 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="7" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="B458" s="3">
         <v>1</v>
@@ -12746,7 +12746,7 @@
         <v>300</v>
       </c>
       <c r="D458" s="8" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="E458" s="3" t="s">
         <v>116</v>
@@ -12754,7 +12754,7 @@
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" s="7" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="B459" s="3">
         <v>3</v>
@@ -12763,7 +12763,7 @@
         <v>300</v>
       </c>
       <c r="D459" s="8" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="E459" s="3" t="s">
         <v>116</v>
@@ -12771,7 +12771,7 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="B460" s="3">
         <v>3</v>
@@ -12780,7 +12780,7 @@
         <v>280</v>
       </c>
       <c r="D460" s="8" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="E460" s="3" t="s">
         <v>116</v>
@@ -12788,7 +12788,7 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="B461" s="3">
         <v>2</v>
@@ -12797,7 +12797,7 @@
         <v>280</v>
       </c>
       <c r="D461" s="8" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="E461" s="3" t="s">
         <v>116</v>
@@ -12805,7 +12805,7 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="B462" s="3">
         <v>1</v>
@@ -12814,7 +12814,7 @@
         <v>280</v>
       </c>
       <c r="D462" s="8" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="E462" s="3" t="s">
         <v>116</v>
@@ -12822,7 +12822,7 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B463" s="3">
         <v>1</v>
@@ -12831,7 +12831,7 @@
         <v>280</v>
       </c>
       <c r="D463" s="8" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="E463" s="3" t="s">
         <v>116</v>
@@ -12839,7 +12839,7 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="B464" s="3">
         <v>1</v>
@@ -12848,7 +12848,7 @@
         <v>280</v>
       </c>
       <c r="D464" s="8" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="E464" s="3" t="s">
         <v>116</v>
@@ -12856,7 +12856,7 @@
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="B465" s="3">
         <v>1</v>
@@ -12865,7 +12865,7 @@
         <v>280</v>
       </c>
       <c r="D465" s="8" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="E465" s="3" t="s">
         <v>116</v>
@@ -12873,7 +12873,7 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="B466" s="3">
         <v>1</v>
@@ -12882,7 +12882,7 @@
         <v>280</v>
       </c>
       <c r="D466" s="8" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="E466" s="3" t="s">
         <v>116</v>
@@ -12890,7 +12890,7 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="B467" s="3">
         <v>2</v>
@@ -12899,7 +12899,7 @@
         <v>320</v>
       </c>
       <c r="D467" s="8" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="E467" s="3" t="s">
         <v>116</v>
@@ -12907,7 +12907,7 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="B468" s="3">
         <v>1</v>
@@ -12916,7 +12916,7 @@
         <v>320</v>
       </c>
       <c r="D468" s="8" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="E468" s="3" t="s">
         <v>116</v>
@@ -12924,7 +12924,7 @@
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B469" s="3">
         <v>2</v>
@@ -12933,7 +12933,7 @@
         <v>320</v>
       </c>
       <c r="D469" s="8" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="E469" s="3" t="s">
         <v>116</v>
@@ -12975,7 +12975,7 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B472" s="3">
         <v>2</v>
@@ -13094,7 +13094,7 @@
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" s="7" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="B479" s="3">
         <v>1</v>
@@ -13103,7 +13103,7 @@
         <v>270</v>
       </c>
       <c r="D479" s="8" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="E479" s="3" t="s">
         <v>120</v>
@@ -13128,7 +13128,7 @@
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B481" s="3">
         <v>2</v>
@@ -13145,7 +13145,7 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B482" s="3">
         <v>1</v>
@@ -13162,7 +13162,7 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B483" s="3">
         <v>3</v>
@@ -13213,7 +13213,7 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B486" s="3">
         <v>3</v>
@@ -13222,7 +13222,7 @@
         <v>270</v>
       </c>
       <c r="D486" s="8" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="E486" s="3" t="s">
         <v>120</v>
@@ -13230,7 +13230,7 @@
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B487" s="3">
         <v>2</v>
@@ -13239,7 +13239,7 @@
         <v>270</v>
       </c>
       <c r="D487" s="8" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="E487" s="3" t="s">
         <v>120</v>
@@ -13247,7 +13247,7 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="B488" s="3">
         <v>1</v>
@@ -13256,7 +13256,7 @@
         <v>270</v>
       </c>
       <c r="D488" s="8" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="E488" s="3" t="s">
         <v>120</v>
@@ -13264,7 +13264,7 @@
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="B489" s="3">
         <v>2</v>
@@ -13273,7 +13273,7 @@
         <v>360</v>
       </c>
       <c r="D489" s="8" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="E489" s="3" t="s">
         <v>120</v>
@@ -13281,7 +13281,7 @@
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="B490" s="3">
         <v>2</v>
@@ -13290,7 +13290,7 @@
         <v>360</v>
       </c>
       <c r="D490" s="8" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="E490" s="3" t="s">
         <v>120</v>
@@ -13298,7 +13298,7 @@
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B491" s="3">
         <v>3</v>
@@ -13307,7 +13307,7 @@
         <v>360</v>
       </c>
       <c r="D491" s="8" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="E491" s="3" t="s">
         <v>120</v>
@@ -13315,7 +13315,7 @@
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B492" s="3">
         <v>1</v>
@@ -13324,7 +13324,7 @@
         <v>360</v>
       </c>
       <c r="D492" s="8" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="E492" s="3" t="s">
         <v>120</v>
@@ -13332,7 +13332,7 @@
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B493" s="3">
         <v>1</v>
@@ -13341,7 +13341,7 @@
         <v>360</v>
       </c>
       <c r="D493" s="8" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="E493" s="3" t="s">
         <v>120</v>
@@ -13349,7 +13349,7 @@
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="B494" s="3">
         <v>2</v>
@@ -13358,7 +13358,7 @@
         <v>360</v>
       </c>
       <c r="D494" s="8" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="E494" s="3" t="s">
         <v>120</v>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="B495" s="3">
         <v>2</v>
@@ -13375,7 +13375,7 @@
         <v>360</v>
       </c>
       <c r="D495" s="8" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="E495" s="3" t="s">
         <v>120</v>
@@ -13383,7 +13383,7 @@
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" s="7" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="B496" s="3">
         <v>2</v>
@@ -13392,7 +13392,7 @@
         <v>360</v>
       </c>
       <c r="D496" s="8" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="E496" s="3" t="s">
         <v>120</v>
@@ -13400,7 +13400,7 @@
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="B497" s="3">
         <v>0</v>
@@ -13409,7 +13409,7 @@
         <v>360</v>
       </c>
       <c r="D497" s="8" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="E497" s="3" t="s">
         <v>120</v>
@@ -13417,7 +13417,7 @@
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B498" s="3">
         <v>3</v>
@@ -13426,7 +13426,7 @@
         <v>360</v>
       </c>
       <c r="D498" s="8" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="E498" s="3" t="s">
         <v>120</v>
@@ -13434,7 +13434,7 @@
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="B499" s="3">
         <v>4</v>
@@ -13443,7 +13443,7 @@
         <v>360</v>
       </c>
       <c r="D499" s="8" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="E499" s="3" t="s">
         <v>120</v>
@@ -13451,7 +13451,7 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B500" s="3">
         <v>1</v>
@@ -13460,7 +13460,7 @@
         <v>270</v>
       </c>
       <c r="D500" s="8" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="E500" s="3" t="s">
         <v>120</v>
@@ -13468,7 +13468,7 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="B501" s="3">
         <v>1</v>
@@ -13477,7 +13477,7 @@
         <v>270</v>
       </c>
       <c r="D501" s="8" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="E501" s="3" t="s">
         <v>120</v>
@@ -13485,7 +13485,7 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="B502" s="3">
         <v>1</v>
@@ -13494,7 +13494,7 @@
         <v>270</v>
       </c>
       <c r="D502" s="8" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="E502" s="3" t="s">
         <v>120</v>
@@ -13502,7 +13502,7 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" s="7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B503" s="3">
         <v>0</v>
@@ -13511,32 +13511,32 @@
         <v>260</v>
       </c>
       <c r="D503" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E503" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B504" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C504" s="3">
         <v>260</v>
       </c>
       <c r="D504" s="8" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E504" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B505" s="3">
         <v>4</v>
@@ -13545,15 +13545,15 @@
         <v>220</v>
       </c>
       <c r="D505" s="8" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E505" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B506" s="3">
         <v>2</v>
@@ -13562,15 +13562,15 @@
         <v>220</v>
       </c>
       <c r="D506" s="8" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E506" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B507" s="3">
         <v>1</v>
@@ -13579,15 +13579,15 @@
         <v>220</v>
       </c>
       <c r="D507" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E507" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B508" s="3">
         <v>2</v>
@@ -13596,15 +13596,15 @@
         <v>220</v>
       </c>
       <c r="D508" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E508" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B509" s="3">
         <v>1</v>
@@ -13613,32 +13613,32 @@
         <v>160</v>
       </c>
       <c r="D509" s="8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E509" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" s="7" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B510" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C510" s="3">
         <v>260</v>
       </c>
       <c r="D510" s="8" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E510" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B511" s="3">
         <v>0</v>
@@ -13647,15 +13647,15 @@
         <v>260</v>
       </c>
       <c r="D511" s="8" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E511" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" s="7" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B512" s="3">
         <v>0</v>
@@ -13664,15 +13664,15 @@
         <v>220</v>
       </c>
       <c r="D512" s="8" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E512" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" s="7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B513" s="3">
         <v>0</v>
@@ -13681,15 +13681,15 @@
         <v>220</v>
       </c>
       <c r="D513" s="8" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E513" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" s="7" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B514" s="3">
         <v>0</v>
@@ -13698,15 +13698,15 @@
         <v>220</v>
       </c>
       <c r="D514" s="8" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E514" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B515" s="3">
         <v>0</v>
@@ -13715,15 +13715,15 @@
         <v>260</v>
       </c>
       <c r="D515" s="8" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E515" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" s="7" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B516" s="3">
         <v>1</v>
@@ -13732,15 +13732,15 @@
         <v>260</v>
       </c>
       <c r="D516" s="8" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E516" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517" s="7" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B517" s="3">
         <v>3</v>
@@ -13749,15 +13749,15 @@
         <v>220</v>
       </c>
       <c r="D517" s="8" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E517" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518" s="7" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B518" s="3">
         <v>2</v>
@@ -13766,15 +13766,15 @@
         <v>260</v>
       </c>
       <c r="D518" s="8" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E518" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519" s="7" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B519" s="3">
         <v>2</v>
@@ -13783,15 +13783,15 @@
         <v>260</v>
       </c>
       <c r="D519" s="8" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="E519" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520" s="7" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B520" s="3">
         <v>1</v>
@@ -13800,15 +13800,15 @@
         <v>260</v>
       </c>
       <c r="D520" s="8" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="E520" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521" s="7" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B521" s="3">
         <v>0</v>
@@ -13817,15 +13817,15 @@
         <v>50</v>
       </c>
       <c r="D521" s="8" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E521" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522" s="7" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="B522" s="3">
         <v>1</v>
@@ -13834,15 +13834,15 @@
         <v>260</v>
       </c>
       <c r="D522" s="8" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="E522" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523" s="7" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="B523" s="3">
         <v>1</v>
@@ -13851,15 +13851,15 @@
         <v>220</v>
       </c>
       <c r="D523" s="8" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="E523" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524" s="7" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="B524" s="3">
         <v>1</v>
@@ -13868,15 +13868,15 @@
         <v>220</v>
       </c>
       <c r="D524" s="8" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="E524" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525" s="7" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="B525" s="3">
         <v>1</v>
@@ -13885,15 +13885,15 @@
         <v>220</v>
       </c>
       <c r="D525" s="8" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="E525" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526" s="7" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="B526" s="3">
         <v>0</v>
@@ -13902,15 +13902,15 @@
         <v>220</v>
       </c>
       <c r="D526" s="8" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="E526" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527" s="7" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B527" s="3">
         <v>2</v>
@@ -13919,15 +13919,15 @@
         <v>260</v>
       </c>
       <c r="D527" s="8" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="E527" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528" s="7" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="B528" s="3">
         <v>2</v>
@@ -13936,49 +13936,49 @@
         <v>260</v>
       </c>
       <c r="D528" s="8" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="E528" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529" s="7" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="B529" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C529" s="3">
         <v>260</v>
       </c>
       <c r="D529" s="8" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="E529" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B530" s="3">
+        <v>1</v>
+      </c>
+      <c r="C530" s="3">
+        <v>260</v>
+      </c>
+      <c r="D530" s="8" t="s">
         <v>1204</v>
       </c>
-      <c r="B530" s="3">
-        <v>1</v>
-      </c>
-      <c r="C530" s="3">
-        <v>260</v>
-      </c>
-      <c r="D530" s="8" t="s">
-        <v>1207</v>
-      </c>
       <c r="E530" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531" s="7" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B531" s="3">
         <v>0</v>
@@ -13987,15 +13987,15 @@
         <v>260</v>
       </c>
       <c r="D531" s="8" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="E531" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532" s="7" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="B532" s="3">
         <v>5</v>
@@ -14004,10 +14004,10 @@
         <v>220</v>
       </c>
       <c r="D532" s="8" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="E532" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
@@ -14024,7 +14024,7 @@
         <v>220</v>
       </c>
       <c r="E533" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
@@ -14041,7 +14041,7 @@
         <v>277</v>
       </c>
       <c r="E534" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
@@ -14055,7 +14055,7 @@
         <v>260</v>
       </c>
       <c r="D535" s="2" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="E535" s="6" t="s">
         <v>359</v>
@@ -14063,7 +14063,7 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B536" s="5">
         <v>4</v>
@@ -14072,7 +14072,7 @@
         <v>280</v>
       </c>
       <c r="D536" s="8" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="E536" s="6" t="s">
         <v>359</v>
@@ -14080,7 +14080,7 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="B537" s="5">
         <v>3</v>
@@ -14089,7 +14089,7 @@
         <v>260</v>
       </c>
       <c r="D537" s="8" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="E537" s="6" t="s">
         <v>359</v>
@@ -14097,7 +14097,7 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="B538" s="5">
         <v>3</v>
@@ -14106,7 +14106,7 @@
         <v>280</v>
       </c>
       <c r="D538" s="8" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="E538" s="6" t="s">
         <v>359</v>
@@ -14165,7 +14165,7 @@
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="B542" s="5">
         <v>3</v>
@@ -14174,7 +14174,7 @@
         <v>320</v>
       </c>
       <c r="D542" s="8" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E542" s="6" t="s">
         <v>359</v>
@@ -14182,7 +14182,7 @@
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B543" s="5">
         <v>3</v>
@@ -14191,7 +14191,7 @@
         <v>320</v>
       </c>
       <c r="D543" s="8" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="E543" s="6" t="s">
         <v>359</v>
@@ -14199,7 +14199,7 @@
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B544" s="5">
         <v>4</v>
@@ -14208,7 +14208,7 @@
         <v>320</v>
       </c>
       <c r="D544" s="8" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E544" s="6" t="s">
         <v>359</v>
@@ -14216,7 +14216,7 @@
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B545" s="5">
         <v>3</v>
@@ -14225,7 +14225,7 @@
         <v>320</v>
       </c>
       <c r="D545" s="8" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="E545" s="6" t="s">
         <v>359</v>
@@ -14233,7 +14233,7 @@
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B546" s="5">
         <v>1</v>
@@ -14242,7 +14242,7 @@
         <v>320</v>
       </c>
       <c r="D546" s="8" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="E546" s="6" t="s">
         <v>359</v>
@@ -14250,7 +14250,7 @@
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="B547" s="5">
         <v>2</v>
@@ -14259,7 +14259,7 @@
         <v>260</v>
       </c>
       <c r="D547" s="8" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="E547" s="6" t="s">
         <v>359</v>
@@ -14267,7 +14267,7 @@
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="B548" s="5">
         <v>1</v>
@@ -14276,7 +14276,7 @@
         <v>260</v>
       </c>
       <c r="D548" s="8" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="E548" s="6" t="s">
         <v>359</v>
@@ -14284,7 +14284,7 @@
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="B549" s="5">
         <v>1</v>
@@ -14293,7 +14293,7 @@
         <v>260</v>
       </c>
       <c r="D549" s="8" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="E549" s="6" t="s">
         <v>359</v>
@@ -14301,7 +14301,7 @@
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="B550" s="5">
         <v>2</v>
@@ -14310,7 +14310,7 @@
         <v>260</v>
       </c>
       <c r="D550" s="8" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="E550" s="6" t="s">
         <v>359</v>
@@ -14318,7 +14318,7 @@
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="B551" s="5">
         <v>2</v>
@@ -14327,7 +14327,7 @@
         <v>260</v>
       </c>
       <c r="D551" s="8" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="E551" s="6" t="s">
         <v>359</v>
@@ -14335,7 +14335,7 @@
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="B552" s="5">
         <v>1</v>
@@ -14344,7 +14344,7 @@
         <v>320</v>
       </c>
       <c r="D552" s="8" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="E552" s="6" t="s">
         <v>359</v>
@@ -14352,7 +14352,7 @@
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="B553" s="5">
         <v>1</v>
@@ -14361,7 +14361,7 @@
         <v>320</v>
       </c>
       <c r="D553" s="8" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="E553" s="6" t="s">
         <v>359</v>
@@ -14369,7 +14369,7 @@
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="B554" s="5">
         <v>1</v>
@@ -14378,7 +14378,7 @@
         <v>320</v>
       </c>
       <c r="D554" s="8" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="E554" s="6" t="s">
         <v>359</v>
@@ -14398,7 +14398,7 @@
         <v>221</v>
       </c>
       <c r="E555" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
@@ -14539,7 +14539,7 @@
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B564" s="5">
         <v>1</v>
@@ -14548,7 +14548,7 @@
         <v>300</v>
       </c>
       <c r="D564" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E564" s="6" t="s">
         <v>308</v>
@@ -14556,7 +14556,7 @@
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B565" s="5">
         <v>1</v>
@@ -14565,7 +14565,7 @@
         <v>300</v>
       </c>
       <c r="D565" s="4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E565" s="6" t="s">
         <v>308</v>
@@ -14573,7 +14573,7 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B566" s="5">
         <v>1</v>
@@ -14582,7 +14582,7 @@
         <v>300</v>
       </c>
       <c r="D566" s="4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E566" s="6" t="s">
         <v>308</v>
@@ -14590,7 +14590,7 @@
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B567" s="5">
         <v>1</v>
@@ -14599,7 +14599,7 @@
         <v>300</v>
       </c>
       <c r="D567" s="4" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E567" s="6" t="s">
         <v>308</v>
@@ -14607,7 +14607,7 @@
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B568" s="5">
         <v>0</v>
@@ -14616,7 +14616,7 @@
         <v>300</v>
       </c>
       <c r="D568" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E568" s="6" t="s">
         <v>308</v>
@@ -14624,7 +14624,7 @@
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B569" s="5">
         <v>2</v>
@@ -14633,7 +14633,7 @@
         <v>300</v>
       </c>
       <c r="D569" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E569" s="6" t="s">
         <v>308</v>
@@ -14641,7 +14641,7 @@
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B570" s="5">
         <v>1</v>
@@ -14650,7 +14650,7 @@
         <v>300</v>
       </c>
       <c r="D570" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E570" s="6" t="s">
         <v>308</v>
@@ -14658,7 +14658,7 @@
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B571" s="5">
         <v>1</v>
@@ -14667,7 +14667,7 @@
         <v>300</v>
       </c>
       <c r="D571" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E571" s="6" t="s">
         <v>308</v>
@@ -14675,7 +14675,7 @@
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B572" s="5">
         <v>1</v>
@@ -14684,7 +14684,7 @@
         <v>300</v>
       </c>
       <c r="D572" s="4" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E572" s="6" t="s">
         <v>308</v>
@@ -14692,7 +14692,7 @@
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B573" s="5">
         <v>0</v>
@@ -14701,7 +14701,7 @@
         <v>300</v>
       </c>
       <c r="D573" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E573" s="6" t="s">
         <v>308</v>
@@ -14709,7 +14709,7 @@
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B574" s="5">
         <v>2</v>
@@ -14718,7 +14718,7 @@
         <v>300</v>
       </c>
       <c r="D574" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E574" s="6" t="s">
         <v>308</v>
@@ -14726,7 +14726,7 @@
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B575" s="5">
         <v>2</v>
@@ -14735,7 +14735,7 @@
         <v>300</v>
       </c>
       <c r="D575" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E575" s="6" t="s">
         <v>308</v>
@@ -14743,7 +14743,7 @@
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B576" s="5">
         <v>1</v>
@@ -14752,7 +14752,7 @@
         <v>300</v>
       </c>
       <c r="D576" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E576" s="6" t="s">
         <v>308</v>
@@ -14760,7 +14760,7 @@
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B577" s="5">
         <v>0</v>
@@ -14769,7 +14769,7 @@
         <v>300</v>
       </c>
       <c r="D577" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E577" s="6" t="s">
         <v>308</v>
@@ -14777,7 +14777,7 @@
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B578" s="5">
         <v>0</v>
@@ -14786,7 +14786,7 @@
         <v>300</v>
       </c>
       <c r="D578" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E578" s="6" t="s">
         <v>308</v>
@@ -14794,7 +14794,7 @@
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B579" s="5">
         <v>1</v>
@@ -14803,7 +14803,7 @@
         <v>320</v>
       </c>
       <c r="D579" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E579" s="6" t="s">
         <v>308</v>
@@ -14811,7 +14811,7 @@
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B580" s="5">
         <v>3</v>
@@ -14820,7 +14820,7 @@
         <v>320</v>
       </c>
       <c r="D580" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E580" s="6" t="s">
         <v>308</v>
@@ -14828,7 +14828,7 @@
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B581" s="5">
         <v>2</v>
@@ -14837,7 +14837,7 @@
         <v>320</v>
       </c>
       <c r="D581" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E581" s="6" t="s">
         <v>308</v>
@@ -14845,7 +14845,7 @@
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B582" s="5">
         <v>3</v>
@@ -14854,7 +14854,7 @@
         <v>320</v>
       </c>
       <c r="D582" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E582" s="6" t="s">
         <v>308</v>
@@ -14862,7 +14862,7 @@
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B583" s="5">
         <v>3</v>
@@ -14871,7 +14871,7 @@
         <v>320</v>
       </c>
       <c r="D583" s="4" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="E583" s="6" t="s">
         <v>308</v>
@@ -14879,7 +14879,7 @@
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B584" s="5">
         <v>1</v>
@@ -14888,7 +14888,7 @@
         <v>300</v>
       </c>
       <c r="D584" s="4" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E584" s="6" t="s">
         <v>308</v>
@@ -14896,7 +14896,7 @@
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B585" s="5">
         <v>3</v>
@@ -14905,7 +14905,7 @@
         <v>320</v>
       </c>
       <c r="D585" s="4" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E585" s="6" t="s">
         <v>308</v>
@@ -14913,7 +14913,7 @@
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B586" s="5">
         <v>1</v>
@@ -14922,7 +14922,7 @@
         <v>320</v>
       </c>
       <c r="D586" s="4" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E586" s="6" t="s">
         <v>308</v>
@@ -14930,7 +14930,7 @@
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B587" s="5">
         <v>2</v>
@@ -14939,7 +14939,7 @@
         <v>300</v>
       </c>
       <c r="D587" s="4" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="E587" s="6" t="s">
         <v>308</v>
@@ -14947,7 +14947,7 @@
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B588" s="5">
         <v>1</v>
@@ -14956,7 +14956,7 @@
         <v>300</v>
       </c>
       <c r="D588" s="8" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="E588" s="6" t="s">
         <v>308</v>
@@ -14964,7 +14964,7 @@
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="B589" s="5">
         <v>1</v>
@@ -14973,7 +14973,7 @@
         <v>300</v>
       </c>
       <c r="D589" s="8" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="E589" s="6" t="s">
         <v>308</v>
@@ -14981,7 +14981,7 @@
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="B590" s="5">
         <v>0</v>
@@ -14990,7 +14990,7 @@
         <v>320</v>
       </c>
       <c r="D590" s="8" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="E590" s="6" t="s">
         <v>308</v>
@@ -14998,7 +14998,7 @@
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="B591" s="5">
         <v>11</v>
@@ -15321,7 +15321,7 @@
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B610" s="5">
         <v>4</v>
@@ -15330,7 +15330,7 @@
         <v>220</v>
       </c>
       <c r="D610" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E610" s="6" t="s">
         <v>174</v>
@@ -15338,7 +15338,7 @@
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B611" s="5">
         <v>0</v>
@@ -15347,7 +15347,7 @@
         <v>1200</v>
       </c>
       <c r="D611" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E611" s="6" t="s">
         <v>174</v>
@@ -15355,7 +15355,7 @@
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B612" s="5">
         <v>0</v>
@@ -15364,7 +15364,7 @@
         <v>1200</v>
       </c>
       <c r="D612" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E612" s="6" t="s">
         <v>174</v>
@@ -15372,7 +15372,7 @@
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="B613" s="5">
         <v>0</v>
@@ -15381,7 +15381,7 @@
         <v>1000</v>
       </c>
       <c r="D613" s="4" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="E613" s="6" t="s">
         <v>174</v>
@@ -15389,7 +15389,7 @@
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B614" s="5">
         <v>1</v>
@@ -15398,7 +15398,7 @@
         <v>260</v>
       </c>
       <c r="D614" s="4" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="E614" s="6" t="s">
         <v>174</v>
@@ -15406,7 +15406,7 @@
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B615" s="5">
         <v>1</v>
@@ -15415,7 +15415,7 @@
         <v>260</v>
       </c>
       <c r="D615" s="4" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="E615" s="6" t="s">
         <v>174</v>
@@ -15423,7 +15423,7 @@
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B616" s="5">
         <v>2</v>
@@ -15432,7 +15432,7 @@
         <v>260</v>
       </c>
       <c r="D616" s="4" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="E616" s="6" t="s">
         <v>174</v>
@@ -15440,7 +15440,7 @@
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B617" s="5">
         <v>0</v>
@@ -15449,7 +15449,7 @@
         <v>260</v>
       </c>
       <c r="D617" s="4" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="E617" s="6" t="s">
         <v>174</v>
@@ -15457,7 +15457,7 @@
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B618" s="5">
         <v>1</v>
@@ -15466,7 +15466,7 @@
         <v>260</v>
       </c>
       <c r="D618" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="E618" s="6" t="s">
         <v>174</v>
@@ -15474,7 +15474,7 @@
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B619" s="5">
         <v>2</v>
@@ -15483,7 +15483,7 @@
         <v>260</v>
       </c>
       <c r="D619" s="4" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E619" s="6" t="s">
         <v>174</v>
@@ -15491,7 +15491,7 @@
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="B620" s="5">
         <v>2</v>
@@ -15500,7 +15500,7 @@
         <v>260</v>
       </c>
       <c r="D620" s="4" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="E620" s="6" t="s">
         <v>174</v>
@@ -15508,7 +15508,7 @@
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B621" s="5">
         <v>1</v>
@@ -15517,7 +15517,7 @@
         <v>260</v>
       </c>
       <c r="D621" s="4" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="E621" s="6" t="s">
         <v>174</v>
@@ -15525,7 +15525,7 @@
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="B622" s="5">
         <v>1</v>
@@ -15534,7 +15534,7 @@
         <v>260</v>
       </c>
       <c r="D622" s="4" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="E622" s="6" t="s">
         <v>174</v>
@@ -15542,7 +15542,7 @@
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B623" s="5">
         <v>1</v>
@@ -15551,7 +15551,7 @@
         <v>260</v>
       </c>
       <c r="D623" s="4" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="E623" s="6" t="s">
         <v>174</v>
@@ -15559,7 +15559,7 @@
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B624" s="5">
         <v>2</v>
@@ -15568,7 +15568,7 @@
         <v>260</v>
       </c>
       <c r="D624" s="4" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="E624" s="6" t="s">
         <v>174</v>
@@ -15576,7 +15576,7 @@
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B625" s="5">
         <v>1</v>
@@ -15585,7 +15585,7 @@
         <v>260</v>
       </c>
       <c r="D625" s="4" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="E625" s="6" t="s">
         <v>174</v>
@@ -15593,7 +15593,7 @@
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B626" s="5">
         <v>1</v>
@@ -15602,15 +15602,15 @@
         <v>200</v>
       </c>
       <c r="D626" s="4" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="E626" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B627" s="5">
         <v>0</v>
@@ -15619,15 +15619,15 @@
         <v>200</v>
       </c>
       <c r="D627" s="4" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="E627" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B628" s="5">
         <v>0</v>
@@ -15636,15 +15636,15 @@
         <v>200</v>
       </c>
       <c r="D628" s="4" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E628" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B629" s="5">
         <v>1</v>
@@ -15653,15 +15653,15 @@
         <v>200</v>
       </c>
       <c r="D629" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="E629" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B630" s="5">
         <v>1</v>
@@ -15670,15 +15670,15 @@
         <v>200</v>
       </c>
       <c r="D630" s="4" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="E630" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="B631" s="5">
         <v>0</v>
@@ -15687,15 +15687,15 @@
         <v>200</v>
       </c>
       <c r="D631" s="4" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="E631" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B632" s="5">
         <v>1</v>
@@ -15704,15 +15704,15 @@
         <v>200</v>
       </c>
       <c r="D632" s="4" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="E632" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B633" s="5">
         <v>1</v>
@@ -15721,15 +15721,15 @@
         <v>200</v>
       </c>
       <c r="D633" s="4" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="E633" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B634" s="5">
         <v>2</v>
@@ -15738,15 +15738,15 @@
         <v>200</v>
       </c>
       <c r="D634" s="4" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="E634" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B635" s="5">
         <v>2</v>
@@ -15755,15 +15755,15 @@
         <v>200</v>
       </c>
       <c r="D635" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="E635" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B636" s="5">
         <v>2</v>
@@ -15772,15 +15772,15 @@
         <v>200</v>
       </c>
       <c r="D636" s="4" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="E636" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B637" s="5">
         <v>1</v>
@@ -15789,15 +15789,15 @@
         <v>200</v>
       </c>
       <c r="D637" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="E637" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="B638" s="5">
         <v>1</v>
@@ -15806,15 +15806,15 @@
         <v>200</v>
       </c>
       <c r="D638" s="4" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="E638" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B639" s="5">
         <v>1</v>
@@ -15823,15 +15823,15 @@
         <v>200</v>
       </c>
       <c r="D639" s="4" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E639" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B640" s="5">
         <v>2</v>
@@ -15840,15 +15840,15 @@
         <v>200</v>
       </c>
       <c r="D640" s="4" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="E640" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B641" s="5">
         <v>2</v>
@@ -15857,15 +15857,15 @@
         <v>200</v>
       </c>
       <c r="D641" s="4" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E641" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B642" s="5">
         <v>2</v>
@@ -15874,15 +15874,15 @@
         <v>200</v>
       </c>
       <c r="D642" s="4" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="E642" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B643" s="5">
         <v>2</v>
@@ -15891,15 +15891,15 @@
         <v>200</v>
       </c>
       <c r="D643" s="4" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="E643" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="B644" s="5">
         <v>2</v>
@@ -15908,15 +15908,15 @@
         <v>200</v>
       </c>
       <c r="D644" s="4" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="E644" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="B645" s="5">
         <v>1</v>
@@ -15925,15 +15925,15 @@
         <v>200</v>
       </c>
       <c r="D645" s="4" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="E645" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="B646" s="5">
         <v>2</v>
@@ -15942,15 +15942,15 @@
         <v>200</v>
       </c>
       <c r="D646" s="4" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="E646" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="B647" s="5">
         <v>2</v>
@@ -15959,15 +15959,15 @@
         <v>200</v>
       </c>
       <c r="D647" s="4" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="E647" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="B648" s="5">
         <v>1</v>
@@ -15976,15 +15976,15 @@
         <v>200</v>
       </c>
       <c r="D648" s="4" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="E648" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="B649" s="5">
         <v>1</v>
@@ -15993,15 +15993,15 @@
         <v>200</v>
       </c>
       <c r="D649" s="4" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="E649" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B650" s="5">
         <v>1</v>
@@ -16010,15 +16010,15 @@
         <v>200</v>
       </c>
       <c r="D650" s="4" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E650" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B651" s="5">
         <v>1</v>
@@ -16027,15 +16027,15 @@
         <v>200</v>
       </c>
       <c r="D651" s="4" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="E651" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="B652" s="5">
         <v>1</v>
@@ -16044,15 +16044,15 @@
         <v>200</v>
       </c>
       <c r="D652" s="4" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="E652" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="B653" s="5">
         <v>1</v>
@@ -16061,7 +16061,7 @@
         <v>200</v>
       </c>
       <c r="D653" s="4" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="E653" s="6" t="s">
         <v>327</v>
@@ -16069,7 +16069,7 @@
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B654" s="5">
         <v>1</v>
@@ -16078,7 +16078,7 @@
         <v>200</v>
       </c>
       <c r="D654" s="4" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E654" s="6" t="s">
         <v>327</v>
@@ -16086,7 +16086,7 @@
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="B655" s="5">
         <v>3</v>
@@ -16095,7 +16095,7 @@
         <v>200</v>
       </c>
       <c r="D655" s="4" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="E655" s="6" t="s">
         <v>327</v>
@@ -16103,7 +16103,7 @@
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B656" s="5">
         <v>3</v>
@@ -16112,7 +16112,7 @@
         <v>200</v>
       </c>
       <c r="D656" s="4" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="E656" s="6" t="s">
         <v>327</v>
@@ -16120,7 +16120,7 @@
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="B657" s="5">
         <v>1</v>
@@ -16129,7 +16129,7 @@
         <v>160</v>
       </c>
       <c r="D657" s="4" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="E657" s="6" t="s">
         <v>327</v>
@@ -16137,7 +16137,7 @@
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="B658" s="5">
         <v>4</v>
@@ -16146,7 +16146,7 @@
         <v>160</v>
       </c>
       <c r="D658" s="4" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="E658" s="6" t="s">
         <v>327</v>
@@ -16154,7 +16154,7 @@
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B659" s="5">
         <v>2</v>
@@ -16163,7 +16163,7 @@
         <v>160</v>
       </c>
       <c r="D659" s="4" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E659" s="6" t="s">
         <v>327</v>
@@ -16171,7 +16171,7 @@
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="B660" s="5">
         <v>2</v>
@@ -16180,15 +16180,15 @@
         <v>260</v>
       </c>
       <c r="D660" s="8" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="E660" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="B661" s="5">
         <v>2</v>
@@ -16197,15 +16197,15 @@
         <v>260</v>
       </c>
       <c r="D661" s="8" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="E661" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="B662" s="5">
         <v>0</v>
@@ -16214,32 +16214,32 @@
         <v>260</v>
       </c>
       <c r="D662" s="8" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="E662" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="B663" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C663" s="5">
         <v>260</v>
       </c>
       <c r="D663" s="8" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="E663" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="B664" s="5">
         <v>2</v>
@@ -16248,15 +16248,15 @@
         <v>260</v>
       </c>
       <c r="D664" s="8" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="E664" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B665" s="5">
         <v>2</v>
@@ -16265,15 +16265,15 @@
         <v>260</v>
       </c>
       <c r="D665" s="8" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="E665" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="B666" s="5">
         <v>1</v>
@@ -16282,15 +16282,15 @@
         <v>260</v>
       </c>
       <c r="D666" s="8" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="E666" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B667" s="5">
         <v>0</v>
@@ -16299,7 +16299,7 @@
         <v>260</v>
       </c>
       <c r="D667" s="8" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="E667" s="6" t="s">
         <v>174</v>
@@ -16307,7 +16307,7 @@
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="B668" s="5">
         <v>0</v>
@@ -16316,7 +16316,7 @@
         <v>260</v>
       </c>
       <c r="D668" s="8" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="E668" s="6" t="s">
         <v>174</v>
@@ -16324,7 +16324,7 @@
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B669" s="5">
         <v>3</v>
@@ -16333,15 +16333,15 @@
         <v>300</v>
       </c>
       <c r="D669" s="8" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="E669" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="B670" s="5">
         <v>1</v>
@@ -16350,15 +16350,15 @@
         <v>300</v>
       </c>
       <c r="D670" s="8" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="E670" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B671" s="5">
         <v>1</v>
@@ -16367,15 +16367,15 @@
         <v>300</v>
       </c>
       <c r="D671" s="8" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="E671" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="B672" s="5">
         <v>3</v>
@@ -16384,15 +16384,15 @@
         <v>300</v>
       </c>
       <c r="D672" s="8" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="E672" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B673" s="5">
         <v>1</v>
@@ -16401,15 +16401,15 @@
         <v>300</v>
       </c>
       <c r="D673" s="8" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="E673" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B674" s="5">
         <v>2</v>
@@ -16418,15 +16418,15 @@
         <v>260</v>
       </c>
       <c r="D674" s="8" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="E674" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B675" s="5">
         <v>1</v>
@@ -16435,15 +16435,15 @@
         <v>260</v>
       </c>
       <c r="D675" s="8" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="E675" s="6" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="B676" s="5">
         <v>20</v>
@@ -16452,7 +16452,7 @@
         <v>100</v>
       </c>
       <c r="D676" s="8" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="E676" s="6" t="s">
         <v>174</v>
@@ -16460,7 +16460,7 @@
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="B677" s="5">
         <v>40</v>
@@ -16469,7 +16469,7 @@
         <v>200</v>
       </c>
       <c r="D677" s="8" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="E677" s="6" t="s">
         <v>174</v>
@@ -16477,7 +16477,7 @@
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B678" s="5">
         <v>1</v>
@@ -16486,32 +16486,32 @@
         <v>260</v>
       </c>
       <c r="D678" s="8" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="E678" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="B679" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C679" s="5">
         <v>260</v>
       </c>
       <c r="D679" s="8" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="E679" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="B680" s="5">
         <v>1</v>
@@ -16520,15 +16520,15 @@
         <v>260</v>
       </c>
       <c r="D680" s="8" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="E680" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="B681" s="5">
         <v>1</v>
@@ -16537,15 +16537,15 @@
         <v>260</v>
       </c>
       <c r="D681" s="8" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="E681" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B682" s="5">
         <v>5</v>
@@ -16554,15 +16554,15 @@
         <v>280</v>
       </c>
       <c r="D682" s="4" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="E682" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="B683" s="5">
         <v>0</v>
@@ -16571,15 +16571,15 @@
         <v>1300</v>
       </c>
       <c r="D683" s="4" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="E683" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="B684" s="5">
         <v>1</v>
@@ -16588,15 +16588,15 @@
         <v>560</v>
       </c>
       <c r="D684" s="4" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="E684" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="B685" s="5">
         <v>1</v>
@@ -16605,15 +16605,15 @@
         <v>280</v>
       </c>
       <c r="D685" s="4" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="E685" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="B686" s="5">
         <v>1</v>
@@ -16622,15 +16622,15 @@
         <v>350</v>
       </c>
       <c r="D686" s="4" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="E686" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="B687" s="5">
         <v>5</v>
@@ -16639,15 +16639,15 @@
         <v>280</v>
       </c>
       <c r="D687" s="4" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="E687" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="B688" s="5">
         <v>2</v>
@@ -16656,15 +16656,15 @@
         <v>280</v>
       </c>
       <c r="D688" s="4" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="E688" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="B689" s="5">
         <v>0</v>
@@ -16673,15 +16673,15 @@
         <v>280</v>
       </c>
       <c r="D689" s="4" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="E689" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="B690" s="5">
         <v>1</v>
@@ -16690,15 +16690,15 @@
         <v>280</v>
       </c>
       <c r="D690" s="4" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="E690" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="B691" s="5">
         <v>1</v>
@@ -16707,15 +16707,15 @@
         <v>260</v>
       </c>
       <c r="D691" s="4" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="E691" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="B692" s="5">
         <v>1</v>
@@ -16724,15 +16724,15 @@
         <v>260</v>
       </c>
       <c r="D692" s="4" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="E692" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="B693" s="5">
         <v>1</v>
@@ -16741,15 +16741,15 @@
         <v>260</v>
       </c>
       <c r="D693" s="4" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="E693" s="6" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="B694" s="5">
         <v>0</v>
@@ -16761,12 +16761,12 @@
         <v>134</v>
       </c>
       <c r="E694" s="6" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="B695" s="5">
         <v>1</v>
@@ -16775,15 +16775,15 @@
         <v>460</v>
       </c>
       <c r="D695" s="4" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="E695" s="6" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="B696" s="5">
         <v>1</v>
@@ -16792,15 +16792,15 @@
         <v>400</v>
       </c>
       <c r="D696" s="4" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="E696" s="6" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="B697" s="5">
         <v>1</v>
@@ -16809,15 +16809,15 @@
         <v>460</v>
       </c>
       <c r="D697" s="4" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="E697" s="6" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="698" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="B698" s="5">
         <v>2</v>
@@ -16826,15 +16826,15 @@
         <v>460</v>
       </c>
       <c r="D698" s="4" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="E698" s="6" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="699" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="B699" s="5">
         <v>0</v>
@@ -16846,12 +16846,12 @@
         <v>134</v>
       </c>
       <c r="E699" s="6" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="700" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="B700" s="5">
         <v>0</v>
@@ -16860,15 +16860,15 @@
         <v>460</v>
       </c>
       <c r="D700" s="4" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="E700" s="6" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="701" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="B701" s="5">
         <v>0</v>
@@ -16877,15 +16877,15 @@
         <v>460</v>
       </c>
       <c r="D701" s="4" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="E701" s="6" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="702" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="B702" s="5">
         <v>0</v>
@@ -16897,12 +16897,12 @@
         <v>134</v>
       </c>
       <c r="E702" s="6" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="703" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="B703" s="5">
         <v>1</v>
@@ -16911,15 +16911,15 @@
         <v>460</v>
       </c>
       <c r="D703" s="4" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="E703" s="6" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="704" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="B704" s="5">
         <v>1</v>
@@ -16928,15 +16928,15 @@
         <v>420</v>
       </c>
       <c r="D704" s="4" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="E704" s="6" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="B705" s="5">
         <v>1</v>
@@ -16945,15 +16945,15 @@
         <v>420</v>
       </c>
       <c r="D705" s="4" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E705" s="6" t="s">
         <v>1269</v>
-      </c>
-      <c r="E705" s="6" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="B706" s="5">
         <v>1</v>
@@ -16962,15 +16962,15 @@
         <v>420</v>
       </c>
       <c r="D706" s="4" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="E706" s="6" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="707" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="B707" s="5">
         <v>0</v>
@@ -16979,15 +16979,15 @@
         <v>420</v>
       </c>
       <c r="D707" s="4" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="E707" s="6" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="708" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="B708" s="5">
         <v>1</v>
@@ -16996,7 +16996,7 @@
         <v>1600</v>
       </c>
       <c r="D708" s="4" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="E708" s="6" t="s">
         <v>174</v>
@@ -17004,7 +17004,7 @@
     </row>
     <row r="709" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="B709" s="5">
         <v>1</v>
@@ -17013,32 +17013,32 @@
         <v>260</v>
       </c>
       <c r="D709" s="4" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="E709" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="710" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B710" s="5">
+        <v>1</v>
+      </c>
+      <c r="C710" s="5">
+        <v>260</v>
+      </c>
+      <c r="D710" s="4" t="s">
         <v>1322</v>
       </c>
-      <c r="B710" s="5">
-        <v>1</v>
-      </c>
-      <c r="C710" s="5">
-        <v>260</v>
-      </c>
-      <c r="D710" s="4" t="s">
-        <v>1325</v>
-      </c>
       <c r="E710" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="711" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="B711" s="5">
         <v>1</v>
@@ -17047,15 +17047,15 @@
         <v>260</v>
       </c>
       <c r="D711" s="4" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E711" s="6" t="s">
         <v>1324</v>
-      </c>
-      <c r="E711" s="6" t="s">
-        <v>1327</v>
       </c>
     </row>
     <row r="712" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="B712" s="5">
         <v>2</v>
@@ -17064,15 +17064,15 @@
         <v>280</v>
       </c>
       <c r="D712" s="4" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="E712" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="713" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B713" s="5">
         <v>3</v>
@@ -17081,15 +17081,15 @@
         <v>300</v>
       </c>
       <c r="D713" s="4" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="E713" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="714" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="B714" s="5">
         <v>1</v>
@@ -17098,15 +17098,15 @@
         <v>260</v>
       </c>
       <c r="D714" s="4" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="E714" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="715" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="B715" s="5">
         <v>1</v>
@@ -17115,15 +17115,15 @@
         <v>260</v>
       </c>
       <c r="D715" s="4" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="E715" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="716" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
       <c r="B716" s="5">
         <v>1</v>
@@ -17132,15 +17132,15 @@
         <v>260</v>
       </c>
       <c r="D716" s="4" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="E716" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="717" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="B717" s="5">
         <v>1</v>
@@ -17149,15 +17149,15 @@
         <v>260</v>
       </c>
       <c r="D717" s="4" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="E717" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="718" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
       <c r="B718" s="5">
         <v>1</v>
@@ -17166,15 +17166,15 @@
         <v>260</v>
       </c>
       <c r="D718" s="4" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="E718" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="719" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B719" s="5">
         <v>1</v>
@@ -17183,15 +17183,15 @@
         <v>260</v>
       </c>
       <c r="D719" s="4" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="E719" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="720" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B720" s="5">
         <v>1</v>
@@ -17200,15 +17200,15 @@
         <v>260</v>
       </c>
       <c r="D720" s="4" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="E720" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="721" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B721" s="5">
         <v>1</v>
@@ -17217,24 +17217,24 @@
         <v>260</v>
       </c>
       <c r="D721" s="4" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="E721" s="6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="B722" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C722" s="5">
         <v>250</v>
       </c>
       <c r="D722" s="4" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="E722" s="6" t="s">
         <v>174</v>
@@ -17242,7 +17242,7 @@
     </row>
     <row r="723" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="B723" s="5">
         <v>1</v>
@@ -17251,7 +17251,7 @@
         <v>280</v>
       </c>
       <c r="D723" s="4" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="E723" s="6" t="s">
         <v>327</v>
@@ -17259,7 +17259,7 @@
     </row>
     <row r="724" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="B724" s="5">
         <v>1</v>
@@ -17268,7 +17268,7 @@
         <v>280</v>
       </c>
       <c r="D724" s="4" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="E724" s="6" t="s">
         <v>327</v>
@@ -17276,7 +17276,7 @@
     </row>
     <row r="725" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="B725" s="5">
         <v>1</v>
@@ -17285,7 +17285,7 @@
         <v>280</v>
       </c>
       <c r="D725" s="4" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="E725" s="6" t="s">
         <v>327</v>
@@ -17293,7 +17293,7 @@
     </row>
     <row r="726" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="B726" s="5">
         <v>1</v>
@@ -17302,7 +17302,7 @@
         <v>280</v>
       </c>
       <c r="D726" s="4" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="E726" s="6" t="s">
         <v>327</v>
@@ -17310,7 +17310,7 @@
     </row>
     <row r="727" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="B727" s="5">
         <v>1</v>
@@ -17319,7 +17319,7 @@
         <v>280</v>
       </c>
       <c r="D727" s="4" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="E727" s="6" t="s">
         <v>327</v>
@@ -17327,7 +17327,7 @@
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="B728" s="5">
         <v>1</v>
@@ -17336,7 +17336,7 @@
         <v>280</v>
       </c>
       <c r="D728" s="4" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="E728" s="6" t="s">
         <v>327</v>
@@ -17344,7 +17344,7 @@
     </row>
     <row r="729" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="B729" s="5">
         <v>1</v>
@@ -17353,7 +17353,7 @@
         <v>280</v>
       </c>
       <c r="D729" s="4" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="E729" s="6" t="s">
         <v>327</v>

--- a/data/stock.xlsx
+++ b/data/stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\blocks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7CCB09-05D3-4908-8739-2F99A060ECD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06CC5F2-4140-4631-ACCE-095CEBA56303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4035" yWindow="825" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
   </bookViews>
@@ -4648,7 +4648,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -4686,9 +4686,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5182,7 +5179,7 @@
         <v>1305</v>
       </c>
       <c r="B3" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3">
         <v>260</v>
@@ -5199,7 +5196,7 @@
         <v>1457</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3">
         <v>450</v>
@@ -5250,7 +5247,7 @@
         <v>1372</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3">
         <v>260</v>
@@ -5542,7 +5539,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="3">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>1504</v>
@@ -6304,7 +6301,7 @@
         <v>22</v>
       </c>
       <c r="B69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69" s="3">
         <v>180</v>
@@ -6338,7 +6335,7 @@
         <v>1118</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71" s="3">
         <v>180</v>
@@ -6355,7 +6352,7 @@
         <v>493</v>
       </c>
       <c r="B72" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72" s="3">
         <v>180</v>
@@ -8225,7 +8222,7 @@
         <v>1142</v>
       </c>
       <c r="B182" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C182" s="3">
         <v>280</v>
@@ -8837,7 +8834,7 @@
         <v>34</v>
       </c>
       <c r="B218" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C218" s="3">
         <v>260</v>
@@ -8990,7 +8987,7 @@
         <v>1373</v>
       </c>
       <c r="B227" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C227" s="3">
         <v>300</v>
@@ -9109,7 +9106,7 @@
         <v>399</v>
       </c>
       <c r="B234" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C234" s="3">
         <v>220</v>
@@ -9262,7 +9259,7 @@
         <v>1454</v>
       </c>
       <c r="B243" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C243" s="3">
         <v>260</v>
@@ -9840,7 +9837,7 @@
         <v>1378</v>
       </c>
       <c r="B277" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C277" s="3">
         <v>280</v>
@@ -14413,7 +14410,7 @@
         <v>167</v>
       </c>
       <c r="B546" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C546" s="3">
         <v>260</v>
@@ -17770,7 +17767,7 @@
       <c r="D743" s="4" t="s">
         <v>1512</v>
       </c>
-      <c r="E743" s="16" t="s">
+      <c r="E743" s="6" t="s">
         <v>1332</v>
       </c>
     </row>
@@ -17787,7 +17784,7 @@
       <c r="D744" s="4" t="s">
         <v>1513</v>
       </c>
-      <c r="E744" s="16" t="s">
+      <c r="E744" s="6" t="s">
         <v>1332</v>
       </c>
     </row>
@@ -17804,7 +17801,7 @@
       <c r="D745" s="4" t="s">
         <v>1514</v>
       </c>
-      <c r="E745" s="16" t="s">
+      <c r="E745" s="6" t="s">
         <v>1332</v>
       </c>
     </row>
@@ -17821,7 +17818,7 @@
       <c r="D746" s="4" t="s">
         <v>1482</v>
       </c>
-      <c r="E746" s="16" t="s">
+      <c r="E746" s="6" t="s">
         <v>1324</v>
       </c>
     </row>
@@ -17838,7 +17835,7 @@
       <c r="D747" s="4" t="s">
         <v>1484</v>
       </c>
-      <c r="E747" s="16" t="s">
+      <c r="E747" s="6" t="s">
         <v>174</v>
       </c>
     </row>
@@ -17855,7 +17852,7 @@
       <c r="D748" s="4" t="s">
         <v>1486</v>
       </c>
-      <c r="E748" s="16" t="s">
+      <c r="E748" s="6" t="s">
         <v>174</v>
       </c>
     </row>
@@ -17872,7 +17869,7 @@
       <c r="D749" s="4" t="s">
         <v>1487</v>
       </c>
-      <c r="E749" s="16" t="s">
+      <c r="E749" s="6" t="s">
         <v>174</v>
       </c>
     </row>
@@ -17889,7 +17886,7 @@
       <c r="D750" s="4" t="s">
         <v>1488</v>
       </c>
-      <c r="E750" s="16" t="s">
+      <c r="E750" s="6" t="s">
         <v>174</v>
       </c>
     </row>
@@ -17906,7 +17903,7 @@
       <c r="D751" s="4" t="s">
         <v>1489</v>
       </c>
-      <c r="E751" s="16" t="s">
+      <c r="E751" s="6" t="s">
         <v>174</v>
       </c>
     </row>
@@ -17923,7 +17920,7 @@
       <c r="D752" s="4" t="s">
         <v>1490</v>
       </c>
-      <c r="E752" s="16" t="s">
+      <c r="E752" s="6" t="s">
         <v>174</v>
       </c>
     </row>
@@ -17940,7 +17937,7 @@
       <c r="D753" s="4" t="s">
         <v>1491</v>
       </c>
-      <c r="E753" s="16" t="s">
+      <c r="E753" s="6" t="s">
         <v>174</v>
       </c>
     </row>
@@ -17957,7 +17954,7 @@
       <c r="D754" s="4" t="s">
         <v>1492</v>
       </c>
-      <c r="E754" s="16" t="s">
+      <c r="E754" s="6" t="s">
         <v>174</v>
       </c>
     </row>
@@ -17974,7 +17971,7 @@
       <c r="D755" s="4" t="s">
         <v>1493</v>
       </c>
-      <c r="E755" s="16" t="s">
+      <c r="E755" s="6" t="s">
         <v>174</v>
       </c>
     </row>
@@ -17991,7 +17988,7 @@
       <c r="D756" s="4" t="s">
         <v>1483</v>
       </c>
-      <c r="E756" s="16" t="s">
+      <c r="E756" s="6" t="s">
         <v>174</v>
       </c>
     </row>
@@ -18008,7 +18005,7 @@
       <c r="D757" s="4" t="s">
         <v>1494</v>
       </c>
-      <c r="E757" s="16" t="s">
+      <c r="E757" s="6" t="s">
         <v>174</v>
       </c>
     </row>
@@ -18025,7 +18022,7 @@
       <c r="D758" s="4" t="s">
         <v>1495</v>
       </c>
-      <c r="E758" s="16" t="s">
+      <c r="E758" s="6" t="s">
         <v>174</v>
       </c>
     </row>

--- a/data/stock.xlsx
+++ b/data/stock.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\blocks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06CC5F2-4140-4631-ACCE-095CEBA56303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0659C60D-0A2B-4BC0-9396-163EF2F745D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4035" yWindow="825" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
+    <workbookView xWindow="4485" yWindow="1815" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4413,9 +4413,6 @@
     <t>Peter B Parker</t>
   </si>
   <si>
-    <t>Spiderman (Insomniac)</t>
-  </si>
-  <si>
     <t>Venom PS5 version</t>
   </si>
   <si>
@@ -4579,6 +4576,9 @@
   </si>
   <si>
     <t>armin.jpeg</t>
+  </si>
+  <si>
+    <t>Spiderman [Insomniac]</t>
   </si>
 </sst>
 </file>
@@ -5202,7 +5202,7 @@
         <v>450</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>6</v>
@@ -5366,13 +5366,13 @@
         <v>1458</v>
       </c>
       <c r="B14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="3">
         <v>260</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>6</v>
@@ -5380,7 +5380,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>1459</v>
+        <v>1514</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5389,7 +5389,7 @@
         <v>260</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>6</v>
@@ -5397,7 +5397,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5406,7 +5406,7 @@
         <v>360</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>6</v>
@@ -5533,7 +5533,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B24" s="3">
         <v>1</v>
@@ -5542,7 +5542,7 @@
         <v>2000</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>6</v>
@@ -5757,7 +5757,7 @@
         <v>785</v>
       </c>
       <c r="B37" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" s="3">
         <v>220</v>
@@ -6012,7 +6012,7 @@
         <v>244</v>
       </c>
       <c r="B52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="3">
         <v>260</v>
@@ -6386,7 +6386,7 @@
         <v>24</v>
       </c>
       <c r="B74" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74" s="3">
         <v>180</v>
@@ -6403,7 +6403,7 @@
         <v>622</v>
       </c>
       <c r="B75" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75" s="3">
         <v>180</v>
@@ -6437,7 +6437,7 @@
         <v>495</v>
       </c>
       <c r="B77" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C77" s="3">
         <v>270</v>
@@ -8644,7 +8644,7 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B207" s="3">
         <v>3</v>
@@ -8653,7 +8653,7 @@
         <v>160</v>
       </c>
       <c r="D207" s="8" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>6</v>
@@ -8661,7 +8661,7 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B208" s="3">
         <v>3</v>
@@ -8670,7 +8670,7 @@
         <v>160</v>
       </c>
       <c r="D208" s="8" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>6</v>
@@ -8678,7 +8678,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B209" s="3">
         <v>3</v>
@@ -8687,7 +8687,7 @@
         <v>160</v>
       </c>
       <c r="D209" s="8" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="E209" s="3" t="s">
         <v>6</v>
@@ -8695,7 +8695,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="7" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="B210" s="3">
         <v>3</v>
@@ -8704,7 +8704,7 @@
         <v>160</v>
       </c>
       <c r="D210" s="8" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>6</v>
@@ -8712,7 +8712,7 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B211" s="3">
         <v>4</v>
@@ -8721,7 +8721,7 @@
         <v>160</v>
       </c>
       <c r="D211" s="8" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>6</v>
@@ -8729,7 +8729,7 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="7" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="B212" s="3">
         <v>4</v>
@@ -8738,7 +8738,7 @@
         <v>160</v>
       </c>
       <c r="D212" s="8" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="E212" s="3" t="s">
         <v>6</v>
@@ -8746,7 +8746,7 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B213" s="3">
         <v>3</v>
@@ -8755,7 +8755,7 @@
         <v>200</v>
       </c>
       <c r="D213" s="8" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="E213" s="3" t="s">
         <v>6</v>
@@ -8763,7 +8763,7 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="7" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B214" s="3">
         <v>4</v>
@@ -8772,7 +8772,7 @@
         <v>160</v>
       </c>
       <c r="D214" s="8" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="E214" s="3" t="s">
         <v>6</v>
@@ -9599,7 +9599,7 @@
         <v>915</v>
       </c>
       <c r="B263" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C263" s="3">
         <v>260</v>
@@ -11673,7 +11673,7 @@
         <v>268</v>
       </c>
       <c r="B385" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C385" s="3">
         <v>280</v>
@@ -11690,7 +11690,7 @@
         <v>515</v>
       </c>
       <c r="B386" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C386" s="3">
         <v>280</v>
@@ -13985,7 +13985,7 @@
         <v>410</v>
       </c>
       <c r="B521" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C521" s="3">
         <v>220</v>
@@ -14325,7 +14325,7 @@
         <v>1088</v>
       </c>
       <c r="B541" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C541" s="3">
         <v>260</v>
@@ -14784,7 +14784,7 @@
         <v>173</v>
       </c>
       <c r="B568" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C568" s="6">
         <v>360</v>
@@ -15124,7 +15124,7 @@
         <v>473</v>
       </c>
       <c r="B588" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C588" s="6">
         <v>300</v>
@@ -17623,7 +17623,7 @@
         <v>1407</v>
       </c>
       <c r="B735" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C735" s="5">
         <v>250</v>
@@ -17756,7 +17756,7 @@
     </row>
     <row r="743" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B743" s="5">
         <v>3</v>
@@ -17765,7 +17765,7 @@
         <v>280</v>
       </c>
       <c r="D743" s="4" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="E743" s="6" t="s">
         <v>1332</v>
@@ -17773,16 +17773,16 @@
     </row>
     <row r="744" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B744" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C744" s="5">
         <v>280</v>
       </c>
       <c r="D744" s="4" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="E744" s="6" t="s">
         <v>1332</v>
@@ -17790,7 +17790,7 @@
     </row>
     <row r="745" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B745" s="5">
         <v>3</v>
@@ -17799,7 +17799,7 @@
         <v>280</v>
       </c>
       <c r="D745" s="4" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="E745" s="6" t="s">
         <v>1332</v>
@@ -17807,7 +17807,7 @@
     </row>
     <row r="746" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B746" s="5">
         <v>1</v>
@@ -17816,7 +17816,7 @@
         <v>960</v>
       </c>
       <c r="D746" s="4" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="E746" s="6" t="s">
         <v>1324</v>
@@ -17824,7 +17824,7 @@
     </row>
     <row r="747" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B747" s="5">
         <v>1</v>
@@ -17833,7 +17833,7 @@
         <v>580</v>
       </c>
       <c r="D747" s="4" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="E747" s="6" t="s">
         <v>174</v>
@@ -17841,7 +17841,7 @@
     </row>
     <row r="748" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B748" s="5">
         <v>1</v>
@@ -17850,7 +17850,7 @@
         <v>580</v>
       </c>
       <c r="D748" s="4" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="E748" s="6" t="s">
         <v>174</v>
@@ -17858,7 +17858,7 @@
     </row>
     <row r="749" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B749" s="5">
         <v>2</v>
@@ -17867,7 +17867,7 @@
         <v>180</v>
       </c>
       <c r="D749" s="4" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="E749" s="6" t="s">
         <v>174</v>
@@ -17875,7 +17875,7 @@
     </row>
     <row r="750" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B750" s="5">
         <v>1</v>
@@ -17884,7 +17884,7 @@
         <v>200</v>
       </c>
       <c r="D750" s="4" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="E750" s="6" t="s">
         <v>174</v>
@@ -17892,7 +17892,7 @@
     </row>
     <row r="751" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B751" s="5">
         <v>2</v>
@@ -17901,7 +17901,7 @@
         <v>160</v>
       </c>
       <c r="D751" s="4" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="E751" s="6" t="s">
         <v>174</v>
@@ -17909,7 +17909,7 @@
     </row>
     <row r="752" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B752" s="5">
         <v>2</v>
@@ -17918,7 +17918,7 @@
         <v>160</v>
       </c>
       <c r="D752" s="4" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="E752" s="6" t="s">
         <v>174</v>
@@ -17926,7 +17926,7 @@
     </row>
     <row r="753" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B753" s="5">
         <v>2</v>
@@ -17935,7 +17935,7 @@
         <v>200</v>
       </c>
       <c r="D753" s="4" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="E753" s="6" t="s">
         <v>174</v>
@@ -17943,7 +17943,7 @@
     </row>
     <row r="754" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="B754" s="5">
         <v>2</v>
@@ -17952,7 +17952,7 @@
         <v>120</v>
       </c>
       <c r="D754" s="4" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="E754" s="6" t="s">
         <v>174</v>
@@ -17960,7 +17960,7 @@
     </row>
     <row r="755" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B755" s="5">
         <v>2</v>
@@ -17969,7 +17969,7 @@
         <v>120</v>
       </c>
       <c r="D755" s="4" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="E755" s="6" t="s">
         <v>174</v>
@@ -17977,7 +17977,7 @@
     </row>
     <row r="756" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B756" s="5">
         <v>2</v>
@@ -17986,7 +17986,7 @@
         <v>120</v>
       </c>
       <c r="D756" s="4" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="E756" s="6" t="s">
         <v>174</v>
@@ -17994,7 +17994,7 @@
     </row>
     <row r="757" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B757" s="5">
         <v>8</v>
@@ -18003,7 +18003,7 @@
         <v>120</v>
       </c>
       <c r="D757" s="4" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="E757" s="6" t="s">
         <v>174</v>
@@ -18011,7 +18011,7 @@
     </row>
     <row r="758" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="B758" s="5">
         <v>2</v>
@@ -18020,7 +18020,7 @@
         <v>120</v>
       </c>
       <c r="D758" s="4" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="E758" s="6" t="s">
         <v>174</v>

--- a/data/stock.xlsx
+++ b/data/stock.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\blocks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0659C60D-0A2B-4BC0-9396-163EF2F745D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82323FC-7A40-45F1-A0A5-E9070AF9B191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4485" yWindow="1815" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
+    <workbookView xWindow="4320" yWindow="2340" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2361,9 +2361,6 @@
     <t>Frieren Happy</t>
   </si>
   <si>
-    <t>Frieren Angy</t>
-  </si>
-  <si>
     <t>Okarun</t>
   </si>
   <si>
@@ -4579,6 +4576,9 @@
   </si>
   <si>
     <t>Spiderman [Insomniac]</t>
+  </si>
+  <si>
+    <t>Frieren Angry</t>
   </si>
 </sst>
 </file>
@@ -5159,7 +5159,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B2" s="3">
         <v>4</v>
@@ -5168,7 +5168,7 @@
         <v>260</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>6</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B3" s="3">
         <v>4</v>
@@ -5185,7 +5185,7 @@
         <v>260</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
@@ -5193,7 +5193,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="B4" s="3">
         <v>6</v>
@@ -5202,7 +5202,7 @@
         <v>450</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>6</v>
@@ -5210,7 +5210,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -5219,7 +5219,7 @@
         <v>260</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>6</v>
@@ -5227,7 +5227,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5236,7 +5236,7 @@
         <v>300</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>6</v>
@@ -5244,7 +5244,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
@@ -5253,7 +5253,7 @@
         <v>260</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>6</v>
@@ -5261,7 +5261,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -5270,7 +5270,7 @@
         <v>260</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>6</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -5287,7 +5287,7 @@
         <v>260</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>6</v>
@@ -5295,7 +5295,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -5304,7 +5304,7 @@
         <v>260</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>6</v>
@@ -5312,7 +5312,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
@@ -5321,7 +5321,7 @@
         <v>260</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>6</v>
@@ -5329,7 +5329,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
@@ -5338,7 +5338,7 @@
         <v>400</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>6</v>
@@ -5346,7 +5346,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -5355,7 +5355,7 @@
         <v>400</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>6</v>
@@ -5363,7 +5363,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
@@ -5372,7 +5372,7 @@
         <v>260</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>6</v>
@@ -5380,7 +5380,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5389,7 +5389,7 @@
         <v>260</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>6</v>
@@ -5397,7 +5397,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5406,7 +5406,7 @@
         <v>360</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>6</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B17" s="3">
         <v>0</v>
@@ -5516,7 +5516,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B23" s="3">
         <v>2</v>
@@ -5525,7 +5525,7 @@
         <v>550</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>6</v>
@@ -5533,7 +5533,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B24" s="3">
         <v>1</v>
@@ -5542,7 +5542,7 @@
         <v>2000</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>6</v>
@@ -5550,7 +5550,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B25" s="3">
         <v>0</v>
@@ -5559,7 +5559,7 @@
         <v>260</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>6</v>
@@ -5567,7 +5567,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B26" s="3">
         <v>1</v>
@@ -5576,7 +5576,7 @@
         <v>300</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>6</v>
@@ -5584,7 +5584,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B27" s="3">
         <v>1</v>
@@ -5593,7 +5593,7 @@
         <v>260</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>6</v>
@@ -5601,7 +5601,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B28" s="3">
         <v>1</v>
@@ -5610,7 +5610,7 @@
         <v>320</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>6</v>
@@ -5621,21 +5621,21 @@
         <v>774</v>
       </c>
       <c r="B29" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" s="3">
         <v>300</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>775</v>
+        <v>1514</v>
       </c>
       <c r="B30" s="3">
         <v>4</v>
@@ -5644,15 +5644,15 @@
         <v>300</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B31" s="3">
         <v>4</v>
@@ -5661,15 +5661,15 @@
         <v>300</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B32" s="3">
         <v>2</v>
@@ -5678,15 +5678,15 @@
         <v>300</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B33" s="3">
         <v>2</v>
@@ -5695,10 +5695,10 @@
         <v>300</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -5715,7 +5715,7 @@
         <v>565</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -5754,7 +5754,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B37" s="3">
         <v>4</v>
@@ -5763,7 +5763,7 @@
         <v>220</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>6</v>
@@ -5808,7 +5808,7 @@
         <v>7</v>
       </c>
       <c r="B40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" s="3">
         <v>180</v>
@@ -5842,7 +5842,7 @@
         <v>492</v>
       </c>
       <c r="B42" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" s="3">
         <v>200</v>
@@ -5882,10 +5882,10 @@
         <v>200</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -5899,7 +5899,7 @@
         <v>200</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>6</v>
@@ -6154,7 +6154,7 @@
         <v>220</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>6</v>
@@ -6199,7 +6199,7 @@
         <v>15</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63" s="3">
         <v>220</v>
@@ -6332,7 +6332,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B71" s="3">
         <v>0</v>
@@ -6417,16 +6417,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B76" s="3">
+        <v>1</v>
+      </c>
+      <c r="C76" s="3">
+        <v>260</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>1119</v>
-      </c>
-      <c r="B76" s="3">
-        <v>1</v>
-      </c>
-      <c r="C76" s="3">
-        <v>260</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>1120</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>6</v>
@@ -6454,7 +6454,7 @@
         <v>496</v>
       </c>
       <c r="B78" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C78" s="3">
         <v>270</v>
@@ -6502,7 +6502,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B81" s="3">
         <v>3</v>
@@ -6511,7 +6511,7 @@
         <v>460</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>6</v>
@@ -6519,7 +6519,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B82" s="3">
         <v>2</v>
@@ -6528,7 +6528,7 @@
         <v>260</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>6</v>
@@ -6536,7 +6536,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B83" s="3">
         <v>2</v>
@@ -6545,7 +6545,7 @@
         <v>260</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>6</v>
@@ -6624,7 +6624,7 @@
         <v>30</v>
       </c>
       <c r="B88" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" s="3">
         <v>270</v>
@@ -6672,7 +6672,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B91" s="3">
         <v>2</v>
@@ -6689,7 +6689,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B92" s="3">
         <v>5</v>
@@ -6757,7 +6757,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B96" s="3">
         <v>3</v>
@@ -6774,7 +6774,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B97" s="3">
         <v>2</v>
@@ -6859,7 +6859,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B102" s="3">
         <v>2</v>
@@ -7131,7 +7131,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B118" s="3">
         <v>2</v>
@@ -7140,7 +7140,7 @@
         <v>260</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>6</v>
@@ -7148,7 +7148,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B119" s="3">
         <v>2</v>
@@ -7157,7 +7157,7 @@
         <v>260</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>6</v>
@@ -7165,7 +7165,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B120" s="3">
         <v>1</v>
@@ -7174,7 +7174,7 @@
         <v>260</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>6</v>
@@ -7182,7 +7182,7 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B121" s="3">
         <v>1</v>
@@ -7191,7 +7191,7 @@
         <v>260</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>6</v>
@@ -7199,7 +7199,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B122" s="3">
         <v>0</v>
@@ -7208,7 +7208,7 @@
         <v>260</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>6</v>
@@ -7216,7 +7216,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B123" s="3">
         <v>2</v>
@@ -7225,7 +7225,7 @@
         <v>260</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>6</v>
@@ -7233,7 +7233,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B124" s="3">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>260</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>6</v>
@@ -7250,7 +7250,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B125" s="3">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>260</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>6</v>
@@ -7267,7 +7267,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B126" s="3">
         <v>1</v>
@@ -7276,7 +7276,7 @@
         <v>260</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>6</v>
@@ -7284,7 +7284,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B127" s="3">
         <v>1</v>
@@ -7293,7 +7293,7 @@
         <v>260</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>6</v>
@@ -7301,7 +7301,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B128" s="3">
         <v>1</v>
@@ -7310,7 +7310,7 @@
         <v>280</v>
       </c>
       <c r="D128" s="8" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>6</v>
@@ -7318,7 +7318,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B129" s="3">
         <v>1</v>
@@ -7327,7 +7327,7 @@
         <v>280</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>6</v>
@@ -7335,7 +7335,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B130" s="3">
         <v>1</v>
@@ -7344,7 +7344,7 @@
         <v>280</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>6</v>
@@ -7352,7 +7352,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B131" s="3">
         <v>1</v>
@@ -7361,7 +7361,7 @@
         <v>260</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>6</v>
@@ -7369,16 +7369,16 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B132" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C132" s="3">
         <v>260</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>6</v>
@@ -7386,7 +7386,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B133" s="3">
         <v>0</v>
@@ -7395,7 +7395,7 @@
         <v>260</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>6</v>
@@ -7403,7 +7403,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B134" s="3">
         <v>1</v>
@@ -7412,7 +7412,7 @@
         <v>260</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>6</v>
@@ -7420,7 +7420,7 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B135" s="3">
         <v>2</v>
@@ -7429,7 +7429,7 @@
         <v>260</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>6</v>
@@ -7437,7 +7437,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B136" s="3">
         <v>4</v>
@@ -7446,7 +7446,7 @@
         <v>150</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>6</v>
@@ -7454,7 +7454,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B137" s="3">
         <v>3</v>
@@ -7463,7 +7463,7 @@
         <v>150</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>6</v>
@@ -7471,7 +7471,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B138" s="3">
         <v>0</v>
@@ -7480,7 +7480,7 @@
         <v>360</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>6</v>
@@ -7488,7 +7488,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B139" s="3">
         <v>1</v>
@@ -7497,7 +7497,7 @@
         <v>260</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>6</v>
@@ -7505,7 +7505,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B140" s="3">
         <v>1</v>
@@ -7514,7 +7514,7 @@
         <v>320</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>6</v>
@@ -7522,7 +7522,7 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B141" s="3">
         <v>1</v>
@@ -7531,7 +7531,7 @@
         <v>280</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>6</v>
@@ -7539,7 +7539,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B142" s="3">
         <v>1</v>
@@ -7548,7 +7548,7 @@
         <v>280</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>6</v>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B143" s="3">
         <v>1</v>
@@ -7565,7 +7565,7 @@
         <v>280</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>6</v>
@@ -7573,7 +7573,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B144" s="3">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         <v>280</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>6</v>
@@ -7590,7 +7590,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B145" s="3">
         <v>1</v>
@@ -7599,7 +7599,7 @@
         <v>280</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>6</v>
@@ -7607,7 +7607,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B146" s="3">
         <v>1</v>
@@ -7616,7 +7616,7 @@
         <v>320</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>6</v>
@@ -7624,7 +7624,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B147" s="3">
         <v>1</v>
@@ -7633,7 +7633,7 @@
         <v>280</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>6</v>
@@ -7641,7 +7641,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="B148" s="3">
         <v>2</v>
@@ -7650,7 +7650,7 @@
         <v>300</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>6</v>
@@ -7658,7 +7658,7 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="B149" s="3">
         <v>4</v>
@@ -7667,7 +7667,7 @@
         <v>300</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>6</v>
@@ -7675,7 +7675,7 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B150" s="3">
         <v>2</v>
@@ -7684,7 +7684,7 @@
         <v>260</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>6</v>
@@ -7692,7 +7692,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B151" s="3">
         <v>0</v>
@@ -7701,7 +7701,7 @@
         <v>280</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>6</v>
@@ -7709,7 +7709,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B152" s="3">
         <v>5</v>
@@ -7718,7 +7718,7 @@
         <v>280</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>6</v>
@@ -7726,7 +7726,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B153" s="3">
         <v>1</v>
@@ -7735,7 +7735,7 @@
         <v>280</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>6</v>
@@ -7743,7 +7743,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B154" s="3">
         <v>2</v>
@@ -7752,7 +7752,7 @@
         <v>280</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>6</v>
@@ -7760,7 +7760,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B155" s="3">
         <v>2</v>
@@ -7769,7 +7769,7 @@
         <v>280</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>6</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B156" s="3">
         <v>1</v>
@@ -7786,7 +7786,7 @@
         <v>280</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>6</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B157" s="3">
         <v>5</v>
@@ -7803,7 +7803,7 @@
         <v>260</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>6</v>
@@ -7811,7 +7811,7 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B158" s="3">
         <v>3</v>
@@ -7820,7 +7820,7 @@
         <v>260</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>6</v>
@@ -7828,7 +7828,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B159" s="3">
         <v>0</v>
@@ -7837,7 +7837,7 @@
         <v>260</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>6</v>
@@ -7845,7 +7845,7 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B160" s="3">
         <v>0</v>
@@ -7854,7 +7854,7 @@
         <v>260</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>6</v>
@@ -7862,7 +7862,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B161" s="3">
         <v>2</v>
@@ -7871,7 +7871,7 @@
         <v>260</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>6</v>
@@ -7879,7 +7879,7 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B162" s="3">
         <v>0</v>
@@ -7888,7 +7888,7 @@
         <v>260</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>6</v>
@@ -7896,7 +7896,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B163" s="3">
         <v>1</v>
@@ -7905,7 +7905,7 @@
         <v>260</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>6</v>
@@ -7913,7 +7913,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B164" s="3">
         <v>1</v>
@@ -7922,7 +7922,7 @@
         <v>260</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>6</v>
@@ -7930,7 +7930,7 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B165" s="3">
         <v>2</v>
@@ -7939,7 +7939,7 @@
         <v>260</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>6</v>
@@ -7947,7 +7947,7 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B166" s="3">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>260</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>6</v>
@@ -7964,7 +7964,7 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B167" s="3">
         <v>4</v>
@@ -7973,7 +7973,7 @@
         <v>280</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>6</v>
@@ -7981,7 +7981,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B168" s="3">
         <v>1</v>
@@ -7990,7 +7990,7 @@
         <v>360</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>6</v>
@@ -7998,7 +7998,7 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B169" s="3">
         <v>3</v>
@@ -8007,7 +8007,7 @@
         <v>260</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>6</v>
@@ -8015,7 +8015,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B170" s="3">
         <v>0</v>
@@ -8024,7 +8024,7 @@
         <v>260</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E170" s="3" t="s">
         <v>6</v>
@@ -8032,7 +8032,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B171" s="3">
         <v>0</v>
@@ -8041,7 +8041,7 @@
         <v>260</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>6</v>
@@ -8049,7 +8049,7 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B172" s="3">
         <v>2</v>
@@ -8058,7 +8058,7 @@
         <v>260</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>6</v>
@@ -8066,7 +8066,7 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B173" s="3">
         <v>2</v>
@@ -8075,7 +8075,7 @@
         <v>260</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>6</v>
@@ -8083,7 +8083,7 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B174" s="3">
         <v>2</v>
@@ -8092,7 +8092,7 @@
         <v>260</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>6</v>
@@ -8100,7 +8100,7 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B175" s="3">
         <v>0</v>
@@ -8109,7 +8109,7 @@
         <v>260</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>6</v>
@@ -8117,7 +8117,7 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B176" s="3">
         <v>3</v>
@@ -8126,7 +8126,7 @@
         <v>400</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>6</v>
@@ -8134,7 +8134,7 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B177" s="3">
         <v>1</v>
@@ -8143,7 +8143,7 @@
         <v>280</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>6</v>
@@ -8151,7 +8151,7 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B178" s="3">
         <v>2</v>
@@ -8160,7 +8160,7 @@
         <v>280</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>6</v>
@@ -8168,7 +8168,7 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="B179" s="3">
         <v>3</v>
@@ -8177,7 +8177,7 @@
         <v>280</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>6</v>
@@ -8185,7 +8185,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B180" s="3">
         <v>1</v>
@@ -8194,7 +8194,7 @@
         <v>280</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>6</v>
@@ -8202,7 +8202,7 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B181" s="3">
         <v>2</v>
@@ -8211,7 +8211,7 @@
         <v>280</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>6</v>
@@ -8219,7 +8219,7 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B182" s="3">
         <v>1</v>
@@ -8228,7 +8228,7 @@
         <v>280</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>6</v>
@@ -8236,7 +8236,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B183" s="3">
         <v>3</v>
@@ -8245,7 +8245,7 @@
         <v>400</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>6</v>
@@ -8253,7 +8253,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B184" s="3">
         <v>1</v>
@@ -8262,7 +8262,7 @@
         <v>260</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>6</v>
@@ -8270,7 +8270,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B185" s="3">
         <v>1</v>
@@ -8279,7 +8279,7 @@
         <v>260</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>6</v>
@@ -8287,7 +8287,7 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B186" s="3">
         <v>1</v>
@@ -8296,7 +8296,7 @@
         <v>260</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>6</v>
@@ -8304,7 +8304,7 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B187" s="3">
         <v>3</v>
@@ -8313,7 +8313,7 @@
         <v>260</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>6</v>
@@ -8321,7 +8321,7 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B188" s="3">
         <v>3</v>
@@ -8330,7 +8330,7 @@
         <v>260</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>6</v>
@@ -8338,7 +8338,7 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="B189" s="3">
         <v>3</v>
@@ -8347,7 +8347,7 @@
         <v>260</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>6</v>
@@ -8355,7 +8355,7 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="B190" s="3">
         <v>3</v>
@@ -8364,7 +8364,7 @@
         <v>300</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>6</v>
@@ -8372,7 +8372,7 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B191" s="3">
         <v>1</v>
@@ -8381,7 +8381,7 @@
         <v>260</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>6</v>
@@ -8389,7 +8389,7 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="B192" s="3">
         <v>2</v>
@@ -8398,7 +8398,7 @@
         <v>260</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>6</v>
@@ -8406,7 +8406,7 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B193" s="3">
         <v>2</v>
@@ -8415,7 +8415,7 @@
         <v>260</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>6</v>
@@ -8423,7 +8423,7 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="B194" s="3">
         <v>2</v>
@@ -8432,7 +8432,7 @@
         <v>260</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>6</v>
@@ -8440,7 +8440,7 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="B195" s="3">
         <v>2</v>
@@ -8449,7 +8449,7 @@
         <v>260</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>6</v>
@@ -8457,7 +8457,7 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="B196" s="3">
         <v>5</v>
@@ -8466,7 +8466,7 @@
         <v>400</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>6</v>
@@ -8474,7 +8474,7 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="B197" s="3">
         <v>9</v>
@@ -8483,7 +8483,7 @@
         <v>300</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>6</v>
@@ -8491,7 +8491,7 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="B198" s="3">
         <v>2</v>
@@ -8500,7 +8500,7 @@
         <v>300</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>6</v>
@@ -8508,7 +8508,7 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="B199" s="3">
         <v>1</v>
@@ -8517,7 +8517,7 @@
         <v>260</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>6</v>
@@ -8525,7 +8525,7 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="B200" s="3">
         <v>2</v>
@@ -8534,7 +8534,7 @@
         <v>260</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>6</v>
@@ -8542,7 +8542,7 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B201" s="3">
         <v>1</v>
@@ -8551,7 +8551,7 @@
         <v>260</v>
       </c>
       <c r="D201" s="8" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>6</v>
@@ -8559,7 +8559,7 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="B202" s="3">
         <v>2</v>
@@ -8568,7 +8568,7 @@
         <v>260</v>
       </c>
       <c r="D202" s="8" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>6</v>
@@ -8576,7 +8576,7 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="B203" s="3">
         <v>2</v>
@@ -8585,7 +8585,7 @@
         <v>260</v>
       </c>
       <c r="D203" s="8" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>6</v>
@@ -8593,7 +8593,7 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="B204" s="3">
         <v>2</v>
@@ -8602,7 +8602,7 @@
         <v>260</v>
       </c>
       <c r="D204" s="8" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>6</v>
@@ -8610,7 +8610,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B205" s="3">
         <v>2</v>
@@ -8619,7 +8619,7 @@
         <v>260</v>
       </c>
       <c r="D205" s="8" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>6</v>
@@ -8627,7 +8627,7 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="B206" s="3">
         <v>2</v>
@@ -8636,7 +8636,7 @@
         <v>260</v>
       </c>
       <c r="D206" s="8" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="E206" s="3" t="s">
         <v>6</v>
@@ -8644,7 +8644,7 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B207" s="3">
         <v>3</v>
@@ -8653,7 +8653,7 @@
         <v>160</v>
       </c>
       <c r="D207" s="8" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>6</v>
@@ -8661,7 +8661,7 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B208" s="3">
         <v>3</v>
@@ -8670,7 +8670,7 @@
         <v>160</v>
       </c>
       <c r="D208" s="8" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>6</v>
@@ -8678,7 +8678,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B209" s="3">
         <v>3</v>
@@ -8687,7 +8687,7 @@
         <v>160</v>
       </c>
       <c r="D209" s="8" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="E209" s="3" t="s">
         <v>6</v>
@@ -8695,7 +8695,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="7" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B210" s="3">
         <v>3</v>
@@ -8704,7 +8704,7 @@
         <v>160</v>
       </c>
       <c r="D210" s="8" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>6</v>
@@ -8712,7 +8712,7 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="B211" s="3">
         <v>4</v>
@@ -8721,7 +8721,7 @@
         <v>160</v>
       </c>
       <c r="D211" s="8" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>6</v>
@@ -8729,7 +8729,7 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="7" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B212" s="3">
         <v>4</v>
@@ -8738,7 +8738,7 @@
         <v>160</v>
       </c>
       <c r="D212" s="8" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="E212" s="3" t="s">
         <v>6</v>
@@ -8746,7 +8746,7 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="B213" s="3">
         <v>3</v>
@@ -8755,7 +8755,7 @@
         <v>200</v>
       </c>
       <c r="D213" s="8" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="E213" s="3" t="s">
         <v>6</v>
@@ -8763,16 +8763,16 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="7" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B214" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C214" s="3">
         <v>160</v>
       </c>
       <c r="D214" s="8" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="E214" s="3" t="s">
         <v>6</v>
@@ -8780,7 +8780,7 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="13" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="B215" s="14">
         <v>0</v>
@@ -8882,7 +8882,7 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B221" s="3">
         <v>2</v>
@@ -8899,16 +8899,16 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="B222" s="3">
+        <v>0</v>
+      </c>
+      <c r="C222" s="3">
+        <v>260</v>
+      </c>
+      <c r="D222" s="8" t="s">
         <v>908</v>
-      </c>
-      <c r="B222" s="3">
-        <v>0</v>
-      </c>
-      <c r="C222" s="3">
-        <v>260</v>
-      </c>
-      <c r="D222" s="8" t="s">
-        <v>909</v>
       </c>
       <c r="E222" s="3" t="s">
         <v>35</v>
@@ -8936,7 +8936,7 @@
         <v>275</v>
       </c>
       <c r="B224" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C224" s="3">
         <v>180</v>
@@ -8984,7 +8984,7 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="B227" s="3">
         <v>0</v>
@@ -9001,7 +9001,7 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="7" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="B228" s="3">
         <v>4</v>
@@ -9035,7 +9035,7 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="7" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B230" s="3">
         <v>3</v>
@@ -9052,7 +9052,7 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B231" s="3">
         <v>6</v>
@@ -9095,7 +9095,7 @@
         <v>220</v>
       </c>
       <c r="D233" s="8" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="E233" s="3" t="s">
         <v>35</v>
@@ -9112,7 +9112,7 @@
         <v>220</v>
       </c>
       <c r="D234" s="8" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="E234" s="3" t="s">
         <v>35</v>
@@ -9137,7 +9137,7 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="7" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B236" s="6">
         <v>0</v>
@@ -9231,7 +9231,7 @@
         <v>220</v>
       </c>
       <c r="D241" s="8" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>35</v>
@@ -9239,7 +9239,7 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="7" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B242" s="3">
         <v>4</v>
@@ -9256,10 +9256,10 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B243" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C243" s="3">
         <v>260</v>
@@ -9477,7 +9477,7 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="7" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B256" s="3">
         <v>0</v>
@@ -9486,7 +9486,7 @@
         <v>260</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E256" s="3" t="s">
         <v>35</v>
@@ -9494,7 +9494,7 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B257" s="3">
         <v>1</v>
@@ -9503,7 +9503,7 @@
         <v>220</v>
       </c>
       <c r="D257" s="8" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E257" s="3" t="s">
         <v>35</v>
@@ -9511,7 +9511,7 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B258" s="3">
         <v>5</v>
@@ -9520,7 +9520,7 @@
         <v>220</v>
       </c>
       <c r="D258" s="8" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E258" s="3" t="s">
         <v>35</v>
@@ -9528,7 +9528,7 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B259" s="3">
         <v>1</v>
@@ -9537,7 +9537,7 @@
         <v>260</v>
       </c>
       <c r="D259" s="8" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>35</v>
@@ -9545,7 +9545,7 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="7" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B260" s="3">
         <v>1</v>
@@ -9554,7 +9554,7 @@
         <v>220</v>
       </c>
       <c r="D260" s="8" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>35</v>
@@ -9562,7 +9562,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B261" s="3">
         <v>1</v>
@@ -9571,7 +9571,7 @@
         <v>260</v>
       </c>
       <c r="D261" s="8" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>35</v>
@@ -9579,7 +9579,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="7" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B262" s="3">
         <v>3</v>
@@ -9588,7 +9588,7 @@
         <v>220</v>
       </c>
       <c r="D262" s="8" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E262" s="3" t="s">
         <v>35</v>
@@ -9596,7 +9596,7 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B263" s="3">
         <v>0</v>
@@ -9605,7 +9605,7 @@
         <v>260</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>35</v>
@@ -9613,7 +9613,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B264" s="3">
         <v>2</v>
@@ -9622,7 +9622,7 @@
         <v>220</v>
       </c>
       <c r="D264" s="8" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>35</v>
@@ -9630,7 +9630,7 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B265" s="3">
         <v>4</v>
@@ -9639,7 +9639,7 @@
         <v>260</v>
       </c>
       <c r="D265" s="8" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>35</v>
@@ -9647,7 +9647,7 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="7" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B266" s="3">
         <v>1</v>
@@ -9656,7 +9656,7 @@
         <v>220</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="E266" s="3" t="s">
         <v>35</v>
@@ -9664,7 +9664,7 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B267" s="3">
         <v>1</v>
@@ -9673,7 +9673,7 @@
         <v>260</v>
       </c>
       <c r="D267" s="8" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>35</v>
@@ -9681,7 +9681,7 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B268" s="3">
         <v>2</v>
@@ -9690,7 +9690,7 @@
         <v>300</v>
       </c>
       <c r="D268" s="8" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>35</v>
@@ -9698,7 +9698,7 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B269" s="3">
         <v>2</v>
@@ -9707,7 +9707,7 @@
         <v>300</v>
       </c>
       <c r="D269" s="8" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="E269" s="3" t="s">
         <v>35</v>
@@ -9715,7 +9715,7 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="7" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B270" s="3">
         <v>2</v>
@@ -9724,7 +9724,7 @@
         <v>260</v>
       </c>
       <c r="D270" s="8" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E270" s="3" t="s">
         <v>35</v>
@@ -9732,7 +9732,7 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B271" s="3">
         <v>2</v>
@@ -9741,7 +9741,7 @@
         <v>260</v>
       </c>
       <c r="D271" s="8" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E271" s="3" t="s">
         <v>35</v>
@@ -9749,7 +9749,7 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="7" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B272" s="3">
         <v>4</v>
@@ -9758,7 +9758,7 @@
         <v>260</v>
       </c>
       <c r="D272" s="8" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E272" s="3" t="s">
         <v>35</v>
@@ -9766,7 +9766,7 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B273" s="3">
         <v>2</v>
@@ -9775,7 +9775,7 @@
         <v>260</v>
       </c>
       <c r="D273" s="8" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="E273" s="3" t="s">
         <v>35</v>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="7" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B274" s="3">
         <v>1</v>
@@ -9792,7 +9792,7 @@
         <v>260</v>
       </c>
       <c r="D274" s="8" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E274" s="3" t="s">
         <v>35</v>
@@ -9800,16 +9800,16 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="B275" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C275" s="3">
         <v>260</v>
       </c>
       <c r="D275" s="8" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>35</v>
@@ -9817,7 +9817,7 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="7" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="B276" s="3">
         <v>3</v>
@@ -9826,7 +9826,7 @@
         <v>280</v>
       </c>
       <c r="D276" s="8" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="E276" s="3" t="s">
         <v>35</v>
@@ -9834,7 +9834,7 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="B277" s="3">
         <v>0</v>
@@ -9843,7 +9843,7 @@
         <v>280</v>
       </c>
       <c r="D277" s="8" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="E277" s="3" t="s">
         <v>35</v>
@@ -9851,7 +9851,7 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="7" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="B278" s="3">
         <v>1</v>
@@ -9860,7 +9860,7 @@
         <v>280</v>
       </c>
       <c r="D278" s="8" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="E278" s="3" t="s">
         <v>35</v>
@@ -9868,7 +9868,7 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="B279" s="3">
         <v>2</v>
@@ -9877,7 +9877,7 @@
         <v>260</v>
       </c>
       <c r="D279" s="8" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>35</v>
@@ -10021,7 +10021,7 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="7" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B288" s="3">
         <v>1</v>
@@ -10064,7 +10064,7 @@
         <v>300</v>
       </c>
       <c r="D290" s="8" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="E290" s="3" t="s">
         <v>44</v>
@@ -10126,7 +10126,7 @@
         <v>655</v>
       </c>
       <c r="B294" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C294" s="3">
         <v>360</v>
@@ -10200,7 +10200,7 @@
         <v>300</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="E298" s="3" t="s">
         <v>44</v>
@@ -10217,7 +10217,7 @@
         <v>300</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="E299" s="3" t="s">
         <v>44</v>
@@ -11364,7 +11364,7 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B367" s="3">
         <v>1</v>
@@ -11373,7 +11373,7 @@
         <v>300</v>
       </c>
       <c r="D367" s="8" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="E367" s="3" t="s">
         <v>44</v>
@@ -11381,7 +11381,7 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="7" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B368" s="3">
         <v>1</v>
@@ -11390,7 +11390,7 @@
         <v>320</v>
       </c>
       <c r="D368" s="8" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="E368" s="3" t="s">
         <v>44</v>
@@ -11398,7 +11398,7 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B369" s="3">
         <v>1</v>
@@ -11407,7 +11407,7 @@
         <v>300</v>
       </c>
       <c r="D369" s="8" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>44</v>
@@ -11415,7 +11415,7 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B370" s="3">
         <v>1</v>
@@ -11424,7 +11424,7 @@
         <v>320</v>
       </c>
       <c r="D370" s="8" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="E370" s="3" t="s">
         <v>44</v>
@@ -11432,16 +11432,16 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" s="7" t="s">
+        <v>962</v>
+      </c>
+      <c r="B371" s="3">
+        <v>1</v>
+      </c>
+      <c r="C371" s="3">
+        <v>260</v>
+      </c>
+      <c r="D371" s="8" t="s">
         <v>963</v>
-      </c>
-      <c r="B371" s="3">
-        <v>1</v>
-      </c>
-      <c r="C371" s="3">
-        <v>260</v>
-      </c>
-      <c r="D371" s="8" t="s">
-        <v>964</v>
       </c>
       <c r="E371" s="3" t="s">
         <v>44</v>
@@ -11449,7 +11449,7 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" s="7" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="B372" s="3">
         <v>1</v>
@@ -11458,7 +11458,7 @@
         <v>360</v>
       </c>
       <c r="D372" s="8" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="E372" s="3" t="s">
         <v>44</v>
@@ -11466,7 +11466,7 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="7" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B373" s="3">
         <v>1</v>
@@ -11475,7 +11475,7 @@
         <v>360</v>
       </c>
       <c r="D373" s="8" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="E373" s="3" t="s">
         <v>44</v>
@@ -11483,7 +11483,7 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" s="7" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B374" s="3">
         <v>1</v>
@@ -11492,7 +11492,7 @@
         <v>360</v>
       </c>
       <c r="D374" s="8" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="E374" s="3" t="s">
         <v>44</v>
@@ -11500,7 +11500,7 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="7" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B375" s="3">
         <v>1</v>
@@ -11509,7 +11509,7 @@
         <v>360</v>
       </c>
       <c r="D375" s="8" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="E375" s="3" t="s">
         <v>44</v>
@@ -11517,7 +11517,7 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="7" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B376" s="3">
         <v>1</v>
@@ -11526,7 +11526,7 @@
         <v>360</v>
       </c>
       <c r="D376" s="8" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="E376" s="3" t="s">
         <v>44</v>
@@ -11534,7 +11534,7 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" s="7" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B377" s="3">
         <v>2</v>
@@ -11543,7 +11543,7 @@
         <v>360</v>
       </c>
       <c r="D377" s="8" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E377" s="3" t="s">
         <v>44</v>
@@ -11551,7 +11551,7 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="7" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B378" s="3">
         <v>1</v>
@@ -11560,7 +11560,7 @@
         <v>360</v>
       </c>
       <c r="D378" s="8" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="E378" s="3" t="s">
         <v>44</v>
@@ -11568,7 +11568,7 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" s="7" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B379" s="3">
         <v>1</v>
@@ -11577,7 +11577,7 @@
         <v>360</v>
       </c>
       <c r="D379" s="8" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="E379" s="3" t="s">
         <v>44</v>
@@ -11585,7 +11585,7 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="7" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B380" s="3">
         <v>1</v>
@@ -11594,7 +11594,7 @@
         <v>320</v>
       </c>
       <c r="D380" s="8" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="E380" s="3" t="s">
         <v>44</v>
@@ -11602,7 +11602,7 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="7" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B381" s="3">
         <v>3</v>
@@ -11611,7 +11611,7 @@
         <v>300</v>
       </c>
       <c r="D381" s="8" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="E381" s="3" t="s">
         <v>44</v>
@@ -11619,7 +11619,7 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="7" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B382" s="3">
         <v>3</v>
@@ -11628,7 +11628,7 @@
         <v>320</v>
       </c>
       <c r="D382" s="8" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="E382" s="3" t="s">
         <v>44</v>
@@ -11636,7 +11636,7 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="7" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B383" s="3">
         <v>3</v>
@@ -11645,7 +11645,7 @@
         <v>320</v>
       </c>
       <c r="D383" s="8" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="E383" s="3" t="s">
         <v>44</v>
@@ -11662,7 +11662,7 @@
         <v>260</v>
       </c>
       <c r="D384" s="8" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="E384" s="3" t="s">
         <v>100</v>
@@ -11772,7 +11772,7 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B391" s="3">
         <v>2</v>
@@ -11781,7 +11781,7 @@
         <v>260</v>
       </c>
       <c r="D391" s="8" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E391" s="3" t="s">
         <v>100</v>
@@ -11789,7 +11789,7 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B392" s="3">
         <v>2</v>
@@ -11798,7 +11798,7 @@
         <v>260</v>
       </c>
       <c r="D392" s="8" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E392" s="3" t="s">
         <v>100</v>
@@ -11976,7 +11976,7 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="7" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B403" s="3">
         <v>1</v>
@@ -11985,7 +11985,7 @@
         <v>500</v>
       </c>
       <c r="D403" s="8" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E403" s="3" t="s">
         <v>100</v>
@@ -12010,7 +12010,7 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B405" s="3">
         <v>0</v>
@@ -12138,7 +12138,7 @@
         <v>260</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="E412" s="3" t="s">
         <v>100</v>
@@ -12189,7 +12189,7 @@
         <v>260</v>
       </c>
       <c r="D415" s="8" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="E415" s="3" t="s">
         <v>100</v>
@@ -12333,7 +12333,7 @@
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" s="7" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B424" s="3">
         <v>0</v>
@@ -12350,7 +12350,7 @@
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" s="7" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B425" s="3">
         <v>1</v>
@@ -12367,7 +12367,7 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B426" s="3">
         <v>1</v>
@@ -12384,7 +12384,7 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" s="7" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B427" s="3">
         <v>1</v>
@@ -12401,7 +12401,7 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" s="7" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B428" s="3">
         <v>0</v>
@@ -12418,7 +12418,7 @@
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" s="7" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B429" s="3">
         <v>1</v>
@@ -12767,7 +12767,7 @@
         <v>260</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="E449" s="3" t="s">
         <v>116</v>
@@ -12775,7 +12775,7 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="7" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B450" s="3">
         <v>1</v>
@@ -12784,7 +12784,7 @@
         <v>260</v>
       </c>
       <c r="D450" s="8" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="E450" s="3" t="s">
         <v>116</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="7" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B451" s="3">
         <v>1</v>
@@ -12801,7 +12801,7 @@
         <v>260</v>
       </c>
       <c r="D451" s="8" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E451" s="3" t="s">
         <v>116</v>
@@ -12852,7 +12852,7 @@
         <v>240</v>
       </c>
       <c r="D454" s="8" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E454" s="3" t="s">
         <v>116</v>
@@ -13132,7 +13132,7 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="7" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B471" s="3">
         <v>1</v>
@@ -13141,7 +13141,7 @@
         <v>300</v>
       </c>
       <c r="D471" s="8" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="E471" s="3" t="s">
         <v>116</v>
@@ -13149,7 +13149,7 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="7" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B472" s="3">
         <v>3</v>
@@ -13158,7 +13158,7 @@
         <v>300</v>
       </c>
       <c r="D472" s="8" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="E472" s="3" t="s">
         <v>116</v>
@@ -13166,7 +13166,7 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B473" s="3">
         <v>3</v>
@@ -13175,7 +13175,7 @@
         <v>280</v>
       </c>
       <c r="D473" s="8" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E473" s="3" t="s">
         <v>116</v>
@@ -13183,7 +13183,7 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B474" s="3">
         <v>2</v>
@@ -13192,7 +13192,7 @@
         <v>280</v>
       </c>
       <c r="D474" s="8" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E474" s="3" t="s">
         <v>116</v>
@@ -13200,7 +13200,7 @@
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B475" s="3">
         <v>1</v>
@@ -13209,7 +13209,7 @@
         <v>280</v>
       </c>
       <c r="D475" s="8" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E475" s="3" t="s">
         <v>116</v>
@@ -13217,7 +13217,7 @@
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B476" s="3">
         <v>1</v>
@@ -13226,7 +13226,7 @@
         <v>280</v>
       </c>
       <c r="D476" s="8" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E476" s="3" t="s">
         <v>116</v>
@@ -13234,7 +13234,7 @@
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B477" s="3">
         <v>1</v>
@@ -13243,7 +13243,7 @@
         <v>280</v>
       </c>
       <c r="D477" s="8" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="E477" s="3" t="s">
         <v>116</v>
@@ -13251,7 +13251,7 @@
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B478" s="3">
         <v>1</v>
@@ -13260,7 +13260,7 @@
         <v>280</v>
       </c>
       <c r="D478" s="8" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="E478" s="3" t="s">
         <v>116</v>
@@ -13268,7 +13268,7 @@
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B479" s="3">
         <v>1</v>
@@ -13277,7 +13277,7 @@
         <v>280</v>
       </c>
       <c r="D479" s="8" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="E479" s="3" t="s">
         <v>116</v>
@@ -13285,7 +13285,7 @@
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="B480" s="3">
         <v>2</v>
@@ -13294,7 +13294,7 @@
         <v>320</v>
       </c>
       <c r="D480" s="8" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="E480" s="3" t="s">
         <v>116</v>
@@ -13302,7 +13302,7 @@
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B481" s="3">
         <v>1</v>
@@ -13311,7 +13311,7 @@
         <v>320</v>
       </c>
       <c r="D481" s="8" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="E481" s="3" t="s">
         <v>116</v>
@@ -13319,7 +13319,7 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B482" s="3">
         <v>2</v>
@@ -13328,7 +13328,7 @@
         <v>320</v>
       </c>
       <c r="D482" s="8" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="E482" s="3" t="s">
         <v>116</v>
@@ -13489,7 +13489,7 @@
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" s="7" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B492" s="3">
         <v>1</v>
@@ -13498,7 +13498,7 @@
         <v>270</v>
       </c>
       <c r="D492" s="8" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="E492" s="3" t="s">
         <v>120</v>
@@ -13608,7 +13608,7 @@
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B499" s="3">
         <v>3</v>
@@ -13617,7 +13617,7 @@
         <v>270</v>
       </c>
       <c r="D499" s="8" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E499" s="3" t="s">
         <v>120</v>
@@ -13625,7 +13625,7 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B500" s="3">
         <v>2</v>
@@ -13634,7 +13634,7 @@
         <v>270</v>
       </c>
       <c r="D500" s="8" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E500" s="3" t="s">
         <v>120</v>
@@ -13642,7 +13642,7 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B501" s="3">
         <v>1</v>
@@ -13651,7 +13651,7 @@
         <v>270</v>
       </c>
       <c r="D501" s="8" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E501" s="3" t="s">
         <v>120</v>
@@ -13659,7 +13659,7 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B502" s="3">
         <v>2</v>
@@ -13668,7 +13668,7 @@
         <v>360</v>
       </c>
       <c r="D502" s="8" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E502" s="3" t="s">
         <v>120</v>
@@ -13676,7 +13676,7 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B503" s="3">
         <v>2</v>
@@ -13685,7 +13685,7 @@
         <v>360</v>
       </c>
       <c r="D503" s="8" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E503" s="3" t="s">
         <v>120</v>
@@ -13693,7 +13693,7 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B504" s="3">
         <v>3</v>
@@ -13702,7 +13702,7 @@
         <v>360</v>
       </c>
       <c r="D504" s="8" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E504" s="3" t="s">
         <v>120</v>
@@ -13710,7 +13710,7 @@
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B505" s="3">
         <v>1</v>
@@ -13719,7 +13719,7 @@
         <v>360</v>
       </c>
       <c r="D505" s="8" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E505" s="3" t="s">
         <v>120</v>
@@ -13727,7 +13727,7 @@
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B506" s="3">
         <v>1</v>
@@ -13736,7 +13736,7 @@
         <v>360</v>
       </c>
       <c r="D506" s="8" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E506" s="3" t="s">
         <v>120</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B507" s="3">
         <v>2</v>
@@ -13753,7 +13753,7 @@
         <v>360</v>
       </c>
       <c r="D507" s="8" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E507" s="3" t="s">
         <v>120</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B508" s="3">
         <v>2</v>
@@ -13770,7 +13770,7 @@
         <v>360</v>
       </c>
       <c r="D508" s="8" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E508" s="3" t="s">
         <v>120</v>
@@ -13778,7 +13778,7 @@
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" s="7" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B509" s="3">
         <v>2</v>
@@ -13787,7 +13787,7 @@
         <v>360</v>
       </c>
       <c r="D509" s="8" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E509" s="3" t="s">
         <v>120</v>
@@ -13795,7 +13795,7 @@
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B510" s="3">
         <v>0</v>
@@ -13804,7 +13804,7 @@
         <v>360</v>
       </c>
       <c r="D510" s="8" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E510" s="3" t="s">
         <v>120</v>
@@ -13812,7 +13812,7 @@
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B511" s="3">
         <v>3</v>
@@ -13821,7 +13821,7 @@
         <v>360</v>
       </c>
       <c r="D511" s="8" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E511" s="3" t="s">
         <v>120</v>
@@ -13829,7 +13829,7 @@
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B512" s="3">
         <v>4</v>
@@ -13838,7 +13838,7 @@
         <v>360</v>
       </c>
       <c r="D512" s="8" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="E512" s="3" t="s">
         <v>120</v>
@@ -13846,7 +13846,7 @@
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B513" s="3">
         <v>1</v>
@@ -13855,7 +13855,7 @@
         <v>270</v>
       </c>
       <c r="D513" s="8" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E513" s="3" t="s">
         <v>120</v>
@@ -13863,7 +13863,7 @@
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B514" s="3">
         <v>1</v>
@@ -13872,7 +13872,7 @@
         <v>270</v>
       </c>
       <c r="D514" s="8" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="E514" s="3" t="s">
         <v>120</v>
@@ -13880,7 +13880,7 @@
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B515" s="3">
         <v>1</v>
@@ -13889,7 +13889,7 @@
         <v>270</v>
       </c>
       <c r="D515" s="8" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="E515" s="3" t="s">
         <v>120</v>
@@ -14220,16 +14220,16 @@
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535" s="7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B535" s="3">
+        <v>1</v>
+      </c>
+      <c r="C535" s="3">
+        <v>260</v>
+      </c>
+      <c r="D535" s="8" t="s">
         <v>1080</v>
-      </c>
-      <c r="B535" s="3">
-        <v>1</v>
-      </c>
-      <c r="C535" s="3">
-        <v>260</v>
-      </c>
-      <c r="D535" s="8" t="s">
-        <v>1081</v>
       </c>
       <c r="E535" s="6" t="s">
         <v>412</v>
@@ -14237,7 +14237,7 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536" s="7" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B536" s="3">
         <v>1</v>
@@ -14246,7 +14246,7 @@
         <v>220</v>
       </c>
       <c r="D536" s="8" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E536" s="6" t="s">
         <v>412</v>
@@ -14254,7 +14254,7 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537" s="7" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B537" s="3">
         <v>1</v>
@@ -14263,7 +14263,7 @@
         <v>220</v>
       </c>
       <c r="D537" s="8" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E537" s="6" t="s">
         <v>412</v>
@@ -14271,7 +14271,7 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538" s="7" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B538" s="3">
         <v>1</v>
@@ -14280,7 +14280,7 @@
         <v>220</v>
       </c>
       <c r="D538" s="8" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E538" s="6" t="s">
         <v>412</v>
@@ -14288,7 +14288,7 @@
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539" s="7" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B539" s="3">
         <v>0</v>
@@ -14297,7 +14297,7 @@
         <v>220</v>
       </c>
       <c r="D539" s="8" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E539" s="6" t="s">
         <v>412</v>
@@ -14305,7 +14305,7 @@
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540" s="7" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B540" s="3">
         <v>2</v>
@@ -14314,7 +14314,7 @@
         <v>260</v>
       </c>
       <c r="D540" s="8" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E540" s="6" t="s">
         <v>412</v>
@@ -14322,7 +14322,7 @@
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541" s="7" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B541" s="3">
         <v>1</v>
@@ -14331,7 +14331,7 @@
         <v>260</v>
       </c>
       <c r="D541" s="8" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E541" s="6" t="s">
         <v>412</v>
@@ -14339,7 +14339,7 @@
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542" s="7" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B542" s="3">
         <v>0</v>
@@ -14348,7 +14348,7 @@
         <v>260</v>
       </c>
       <c r="D542" s="8" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="E542" s="6" t="s">
         <v>412</v>
@@ -14356,7 +14356,7 @@
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543" s="7" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B543" s="3">
         <v>1</v>
@@ -14365,7 +14365,7 @@
         <v>260</v>
       </c>
       <c r="D543" s="8" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="E543" s="6" t="s">
         <v>412</v>
@@ -14373,7 +14373,7 @@
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544" s="7" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B544" s="3">
         <v>0</v>
@@ -14382,7 +14382,7 @@
         <v>260</v>
       </c>
       <c r="D544" s="8" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="E544" s="6" t="s">
         <v>412</v>
@@ -14390,7 +14390,7 @@
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545" s="7" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B545" s="3">
         <v>5</v>
@@ -14399,7 +14399,7 @@
         <v>220</v>
       </c>
       <c r="D545" s="8" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="E545" s="6" t="s">
         <v>412</v>
@@ -14419,7 +14419,7 @@
         <v>220</v>
       </c>
       <c r="E546" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
@@ -14436,7 +14436,7 @@
         <v>277</v>
       </c>
       <c r="E547" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
@@ -14450,7 +14450,7 @@
         <v>260</v>
       </c>
       <c r="D548" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="E548" s="6" t="s">
         <v>359</v>
@@ -14458,7 +14458,7 @@
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B549" s="5">
         <v>4</v>
@@ -14467,7 +14467,7 @@
         <v>280</v>
       </c>
       <c r="D549" s="8" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="E549" s="6" t="s">
         <v>359</v>
@@ -14475,7 +14475,7 @@
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B550" s="5">
         <v>3</v>
@@ -14484,7 +14484,7 @@
         <v>260</v>
       </c>
       <c r="D550" s="8" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E550" s="6" t="s">
         <v>359</v>
@@ -14492,7 +14492,7 @@
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B551" s="5">
         <v>3</v>
@@ -14501,7 +14501,7 @@
         <v>280</v>
       </c>
       <c r="D551" s="8" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="E551" s="6" t="s">
         <v>359</v>
@@ -14645,7 +14645,7 @@
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B560" s="5">
         <v>2</v>
@@ -14654,7 +14654,7 @@
         <v>260</v>
       </c>
       <c r="D560" s="8" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E560" s="6" t="s">
         <v>359</v>
@@ -14662,7 +14662,7 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B561" s="5">
         <v>1</v>
@@ -14671,7 +14671,7 @@
         <v>260</v>
       </c>
       <c r="D561" s="8" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="E561" s="6" t="s">
         <v>359</v>
@@ -14679,7 +14679,7 @@
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B562" s="5">
         <v>1</v>
@@ -14688,7 +14688,7 @@
         <v>260</v>
       </c>
       <c r="D562" s="8" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="E562" s="6" t="s">
         <v>359</v>
@@ -14696,7 +14696,7 @@
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B563" s="5">
         <v>2</v>
@@ -14705,7 +14705,7 @@
         <v>260</v>
       </c>
       <c r="D563" s="8" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="E563" s="6" t="s">
         <v>359</v>
@@ -14713,7 +14713,7 @@
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B564" s="5">
         <v>2</v>
@@ -14722,7 +14722,7 @@
         <v>260</v>
       </c>
       <c r="D564" s="8" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E564" s="6" t="s">
         <v>359</v>
@@ -14730,7 +14730,7 @@
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B565" s="5">
         <v>1</v>
@@ -14739,7 +14739,7 @@
         <v>320</v>
       </c>
       <c r="D565" s="8" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="E565" s="6" t="s">
         <v>359</v>
@@ -14747,7 +14747,7 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B566" s="5">
         <v>1</v>
@@ -14756,7 +14756,7 @@
         <v>320</v>
       </c>
       <c r="D566" s="8" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="E566" s="6" t="s">
         <v>359</v>
@@ -14764,7 +14764,7 @@
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B567" s="5">
         <v>1</v>
@@ -14773,7 +14773,7 @@
         <v>320</v>
       </c>
       <c r="D567" s="8" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="E567" s="6" t="s">
         <v>359</v>
@@ -14784,7 +14784,7 @@
         <v>173</v>
       </c>
       <c r="B568" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C568" s="6">
         <v>360</v>
@@ -14793,7 +14793,7 @@
         <v>221</v>
       </c>
       <c r="E568" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
@@ -15351,7 +15351,7 @@
         <v>300</v>
       </c>
       <c r="D601" s="8" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="E601" s="6" t="s">
         <v>308</v>
@@ -15359,7 +15359,7 @@
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B602" s="5">
         <v>1</v>
@@ -15368,7 +15368,7 @@
         <v>300</v>
       </c>
       <c r="D602" s="8" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E602" s="6" t="s">
         <v>308</v>
@@ -15376,7 +15376,7 @@
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B603" s="5">
         <v>0</v>
@@ -15385,7 +15385,7 @@
         <v>320</v>
       </c>
       <c r="D603" s="8" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E603" s="6" t="s">
         <v>308</v>
@@ -15393,7 +15393,7 @@
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="B604" s="5">
         <v>11</v>
@@ -15988,7 +15988,7 @@
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B639" s="5">
         <v>1</v>
@@ -15997,15 +15997,15 @@
         <v>200</v>
       </c>
       <c r="D639" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="E639" s="6" t="s">
         <v>787</v>
-      </c>
-      <c r="E639" s="6" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B640" s="5">
         <v>0</v>
@@ -16014,15 +16014,15 @@
         <v>200</v>
       </c>
       <c r="D640" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E640" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B641" s="5">
         <v>0</v>
@@ -16031,15 +16031,15 @@
         <v>200</v>
       </c>
       <c r="D641" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E641" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B642" s="5">
         <v>1</v>
@@ -16048,32 +16048,32 @@
         <v>200</v>
       </c>
       <c r="D642" s="4" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E642" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B643" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C643" s="6">
         <v>200</v>
       </c>
       <c r="D643" s="4" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E643" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B644" s="5">
         <v>0</v>
@@ -16082,15 +16082,15 @@
         <v>200</v>
       </c>
       <c r="D644" s="4" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E644" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B645" s="5">
         <v>1</v>
@@ -16099,15 +16099,15 @@
         <v>200</v>
       </c>
       <c r="D645" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E645" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B646" s="5">
         <v>1</v>
@@ -16116,15 +16116,15 @@
         <v>200</v>
       </c>
       <c r="D646" s="4" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E646" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B647" s="5">
         <v>2</v>
@@ -16133,15 +16133,15 @@
         <v>200</v>
       </c>
       <c r="D647" s="4" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E647" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B648" s="5">
         <v>2</v>
@@ -16150,15 +16150,15 @@
         <v>200</v>
       </c>
       <c r="D648" s="4" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E648" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B649" s="5">
         <v>2</v>
@@ -16167,15 +16167,15 @@
         <v>200</v>
       </c>
       <c r="D649" s="4" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E649" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B650" s="5">
         <v>1</v>
@@ -16184,15 +16184,15 @@
         <v>200</v>
       </c>
       <c r="D650" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E650" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B651" s="5">
         <v>1</v>
@@ -16201,15 +16201,15 @@
         <v>200</v>
       </c>
       <c r="D651" s="4" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E651" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B652" s="5">
         <v>1</v>
@@ -16218,15 +16218,15 @@
         <v>200</v>
       </c>
       <c r="D652" s="4" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E652" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B653" s="5">
         <v>2</v>
@@ -16235,15 +16235,15 @@
         <v>200</v>
       </c>
       <c r="D653" s="4" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E653" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B654" s="5">
         <v>2</v>
@@ -16252,15 +16252,15 @@
         <v>200</v>
       </c>
       <c r="D654" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E654" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B655" s="5">
         <v>2</v>
@@ -16269,15 +16269,15 @@
         <v>200</v>
       </c>
       <c r="D655" s="4" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E655" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B656" s="5">
         <v>2</v>
@@ -16286,15 +16286,15 @@
         <v>200</v>
       </c>
       <c r="D656" s="4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E656" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B657" s="5">
         <v>2</v>
@@ -16303,15 +16303,15 @@
         <v>200</v>
       </c>
       <c r="D657" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E657" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B658" s="5">
         <v>1</v>
@@ -16320,15 +16320,15 @@
         <v>200</v>
       </c>
       <c r="D658" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E658" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B659" s="5">
         <v>2</v>
@@ -16337,15 +16337,15 @@
         <v>200</v>
       </c>
       <c r="D659" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E659" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B660" s="5">
         <v>2</v>
@@ -16354,15 +16354,15 @@
         <v>200</v>
       </c>
       <c r="D660" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E660" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B661" s="5">
         <v>1</v>
@@ -16371,15 +16371,15 @@
         <v>200</v>
       </c>
       <c r="D661" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E661" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B662" s="5">
         <v>1</v>
@@ -16388,15 +16388,15 @@
         <v>200</v>
       </c>
       <c r="D662" s="4" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E662" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B663" s="5">
         <v>1</v>
@@ -16405,15 +16405,15 @@
         <v>200</v>
       </c>
       <c r="D663" s="4" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E663" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B664" s="5">
         <v>1</v>
@@ -16422,15 +16422,15 @@
         <v>200</v>
       </c>
       <c r="D664" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E664" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B665" s="5">
         <v>1</v>
@@ -16439,15 +16439,15 @@
         <v>200</v>
       </c>
       <c r="D665" s="4" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E665" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B666" s="5">
         <v>1</v>
@@ -16456,7 +16456,7 @@
         <v>200</v>
       </c>
       <c r="D666" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E666" s="6" t="s">
         <v>327</v>
@@ -16464,7 +16464,7 @@
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B667" s="5">
         <v>1</v>
@@ -16473,7 +16473,7 @@
         <v>200</v>
       </c>
       <c r="D667" s="4" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E667" s="6" t="s">
         <v>327</v>
@@ -16481,7 +16481,7 @@
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B668" s="5">
         <v>3</v>
@@ -16490,7 +16490,7 @@
         <v>200</v>
       </c>
       <c r="D668" s="4" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E668" s="6" t="s">
         <v>327</v>
@@ -16498,7 +16498,7 @@
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B669" s="5">
         <v>3</v>
@@ -16507,7 +16507,7 @@
         <v>200</v>
       </c>
       <c r="D669" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E669" s="6" t="s">
         <v>327</v>
@@ -16515,7 +16515,7 @@
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B670" s="5">
         <v>1</v>
@@ -16524,7 +16524,7 @@
         <v>160</v>
       </c>
       <c r="D670" s="4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E670" s="6" t="s">
         <v>327</v>
@@ -16532,7 +16532,7 @@
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B671" s="5">
         <v>4</v>
@@ -16541,7 +16541,7 @@
         <v>160</v>
       </c>
       <c r="D671" s="4" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E671" s="6" t="s">
         <v>327</v>
@@ -16549,7 +16549,7 @@
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B672" s="5">
         <v>2</v>
@@ -16558,7 +16558,7 @@
         <v>160</v>
       </c>
       <c r="D672" s="4" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E672" s="6" t="s">
         <v>327</v>
@@ -16566,7 +16566,7 @@
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B673" s="5">
         <v>2</v>
@@ -16575,15 +16575,15 @@
         <v>260</v>
       </c>
       <c r="D673" s="8" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E673" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B674" s="5">
         <v>2</v>
@@ -16592,15 +16592,15 @@
         <v>260</v>
       </c>
       <c r="D674" s="8" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E674" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B675" s="5">
         <v>0</v>
@@ -16609,15 +16609,15 @@
         <v>260</v>
       </c>
       <c r="D675" s="8" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E675" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B676" s="5">
         <v>0</v>
@@ -16626,15 +16626,15 @@
         <v>260</v>
       </c>
       <c r="D676" s="8" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E676" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="677" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B677" s="5">
         <v>2</v>
@@ -16643,15 +16643,15 @@
         <v>260</v>
       </c>
       <c r="D677" s="8" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="E677" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B678" s="5">
         <v>2</v>
@@ -16660,15 +16660,15 @@
         <v>260</v>
       </c>
       <c r="D678" s="8" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E678" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B679" s="5">
         <v>1</v>
@@ -16677,15 +16677,15 @@
         <v>260</v>
       </c>
       <c r="D679" s="8" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E679" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B680" s="5">
         <v>0</v>
@@ -16694,7 +16694,7 @@
         <v>260</v>
       </c>
       <c r="D680" s="8" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="E680" s="6" t="s">
         <v>174</v>
@@ -16702,7 +16702,7 @@
     </row>
     <row r="681" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B681" s="5">
         <v>0</v>
@@ -16711,7 +16711,7 @@
         <v>260</v>
       </c>
       <c r="D681" s="8" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E681" s="6" t="s">
         <v>174</v>
@@ -16719,7 +16719,7 @@
     </row>
     <row r="682" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B682" s="5">
         <v>3</v>
@@ -16728,15 +16728,15 @@
         <v>300</v>
       </c>
       <c r="D682" s="8" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="E682" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="683" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B683" s="5">
         <v>1</v>
@@ -16745,15 +16745,15 @@
         <v>300</v>
       </c>
       <c r="D683" s="8" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="E683" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="684" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B684" s="5">
         <v>1</v>
@@ -16762,15 +16762,15 @@
         <v>300</v>
       </c>
       <c r="D684" s="8" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E684" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="685" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B685" s="5">
         <v>3</v>
@@ -16779,15 +16779,15 @@
         <v>300</v>
       </c>
       <c r="D685" s="8" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="E685" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B686" s="5">
         <v>1</v>
@@ -16796,15 +16796,15 @@
         <v>300</v>
       </c>
       <c r="D686" s="8" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E686" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B687" s="5">
         <v>2</v>
@@ -16813,15 +16813,15 @@
         <v>260</v>
       </c>
       <c r="D687" s="8" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="E687" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="688" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B688" s="5">
         <v>1</v>
@@ -16830,15 +16830,15 @@
         <v>260</v>
       </c>
       <c r="D688" s="8" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="E688" s="6" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B689" s="5">
         <v>20</v>
@@ -16847,7 +16847,7 @@
         <v>100</v>
       </c>
       <c r="D689" s="8" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="E689" s="6" t="s">
         <v>174</v>
@@ -16855,7 +16855,7 @@
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B690" s="5">
         <v>40</v>
@@ -16864,7 +16864,7 @@
         <v>200</v>
       </c>
       <c r="D690" s="8" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="E690" s="6" t="s">
         <v>174</v>
@@ -16872,7 +16872,7 @@
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B691" s="5">
         <v>1</v>
@@ -16881,49 +16881,49 @@
         <v>260</v>
       </c>
       <c r="D691" s="8" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="E691" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B692" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C692" s="5">
         <v>260</v>
       </c>
       <c r="D692" s="8" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E692" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B693" s="5">
+        <v>1</v>
+      </c>
+      <c r="C693" s="5">
+        <v>260</v>
+      </c>
+      <c r="D693" s="8" t="s">
         <v>1076</v>
       </c>
-      <c r="B693" s="5">
-        <v>1</v>
-      </c>
-      <c r="C693" s="5">
-        <v>260</v>
-      </c>
-      <c r="D693" s="8" t="s">
-        <v>1077</v>
-      </c>
       <c r="E693" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B694" s="5">
         <v>1</v>
@@ -16932,15 +16932,15 @@
         <v>260</v>
       </c>
       <c r="D694" s="8" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="E694" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B695" s="5">
         <v>5</v>
@@ -16949,15 +16949,15 @@
         <v>280</v>
       </c>
       <c r="D695" s="4" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="E695" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B696" s="5">
         <v>0</v>
@@ -16966,15 +16966,15 @@
         <v>1300</v>
       </c>
       <c r="D696" s="4" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E696" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B697" s="5">
         <v>1</v>
@@ -16983,15 +16983,15 @@
         <v>560</v>
       </c>
       <c r="D697" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E697" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="698" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="B698" s="5">
         <v>1</v>
@@ -17000,15 +17000,15 @@
         <v>280</v>
       </c>
       <c r="D698" s="4" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E698" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="699" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="B699" s="5">
         <v>1</v>
@@ -17017,15 +17017,15 @@
         <v>350</v>
       </c>
       <c r="D699" s="4" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="E699" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="700" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="B700" s="5">
         <v>5</v>
@@ -17034,15 +17034,15 @@
         <v>280</v>
       </c>
       <c r="D700" s="4" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="E700" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="701" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B701" s="5">
         <v>2</v>
@@ -17051,15 +17051,15 @@
         <v>280</v>
       </c>
       <c r="D701" s="4" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="E701" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="702" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B702" s="5">
         <v>0</v>
@@ -17068,15 +17068,15 @@
         <v>280</v>
       </c>
       <c r="D702" s="4" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="E702" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="703" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B703" s="5">
         <v>1</v>
@@ -17085,15 +17085,15 @@
         <v>280</v>
       </c>
       <c r="D703" s="4" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="E703" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="704" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="B704" s="5">
         <v>1</v>
@@ -17102,15 +17102,15 @@
         <v>260</v>
       </c>
       <c r="D704" s="4" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="E704" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B705" s="5">
         <v>1</v>
@@ -17119,15 +17119,15 @@
         <v>260</v>
       </c>
       <c r="D705" s="4" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E705" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B706" s="5">
         <v>1</v>
@@ -17136,15 +17136,15 @@
         <v>260</v>
       </c>
       <c r="D706" s="4" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="E706" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="707" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="B707" s="5">
         <v>0</v>
@@ -17156,12 +17156,12 @@
         <v>134</v>
       </c>
       <c r="E707" s="6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="708" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="B708" s="5">
         <v>1</v>
@@ -17170,15 +17170,15 @@
         <v>460</v>
       </c>
       <c r="D708" s="4" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="E708" s="6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="709" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B709" s="5">
         <v>1</v>
@@ -17187,15 +17187,15 @@
         <v>400</v>
       </c>
       <c r="D709" s="4" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="E709" s="6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="710" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="B710" s="5">
         <v>1</v>
@@ -17204,15 +17204,15 @@
         <v>460</v>
       </c>
       <c r="D710" s="4" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="E710" s="6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="711" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B711" s="5">
         <v>2</v>
@@ -17221,15 +17221,15 @@
         <v>460</v>
       </c>
       <c r="D711" s="4" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E711" s="6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="712" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B712" s="5">
         <v>0</v>
@@ -17241,12 +17241,12 @@
         <v>134</v>
       </c>
       <c r="E712" s="6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="713" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B713" s="5">
         <v>0</v>
@@ -17255,15 +17255,15 @@
         <v>460</v>
       </c>
       <c r="D713" s="4" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="E713" s="6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="714" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B714" s="5">
         <v>0</v>
@@ -17272,15 +17272,15 @@
         <v>460</v>
       </c>
       <c r="D714" s="4" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="E714" s="6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="715" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B715" s="5">
         <v>0</v>
@@ -17292,12 +17292,12 @@
         <v>134</v>
       </c>
       <c r="E715" s="6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="716" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B716" s="5">
         <v>1</v>
@@ -17306,15 +17306,15 @@
         <v>460</v>
       </c>
       <c r="D716" s="4" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E716" s="6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="717" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B717" s="5">
         <v>1</v>
@@ -17323,15 +17323,15 @@
         <v>420</v>
       </c>
       <c r="D717" s="4" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="E717" s="6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="718" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B718" s="5">
         <v>1</v>
@@ -17340,15 +17340,15 @@
         <v>420</v>
       </c>
       <c r="D718" s="4" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="E718" s="6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="719" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="B719" s="5">
         <v>1</v>
@@ -17357,15 +17357,15 @@
         <v>420</v>
       </c>
       <c r="D719" s="4" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="E719" s="6" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="720" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B720" s="5">
         <v>0</v>
@@ -17374,15 +17374,15 @@
         <v>420</v>
       </c>
       <c r="D720" s="4" t="s">
+        <v>1267</v>
+      </c>
+      <c r="E720" s="6" t="s">
         <v>1268</v>
-      </c>
-      <c r="E720" s="6" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="721" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="B721" s="5">
         <v>1</v>
@@ -17391,7 +17391,7 @@
         <v>1600</v>
       </c>
       <c r="D721" s="4" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="E721" s="6" t="s">
         <v>174</v>
@@ -17399,7 +17399,7 @@
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B722" s="5">
         <v>1</v>
@@ -17408,15 +17408,15 @@
         <v>260</v>
       </c>
       <c r="D722" s="4" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E722" s="6" t="s">
         <v>1323</v>
-      </c>
-      <c r="E722" s="6" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="723" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B723" s="5">
         <v>1</v>
@@ -17425,32 +17425,32 @@
         <v>260</v>
       </c>
       <c r="D723" s="4" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="E723" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="724" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B724" s="5">
+        <v>1</v>
+      </c>
+      <c r="C724" s="5">
+        <v>260</v>
+      </c>
+      <c r="D724" s="4" t="s">
         <v>1320</v>
       </c>
-      <c r="B724" s="5">
-        <v>1</v>
-      </c>
-      <c r="C724" s="5">
-        <v>260</v>
-      </c>
-      <c r="D724" s="4" t="s">
-        <v>1321</v>
-      </c>
       <c r="E724" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="725" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="B725" s="5">
         <v>2</v>
@@ -17459,15 +17459,15 @@
         <v>280</v>
       </c>
       <c r="D725" s="4" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="E725" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="726" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B726" s="5">
         <v>3</v>
@@ -17476,15 +17476,15 @@
         <v>300</v>
       </c>
       <c r="D726" s="4" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="E726" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="727" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B727" s="5">
         <v>1</v>
@@ -17493,15 +17493,15 @@
         <v>260</v>
       </c>
       <c r="D727" s="4" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="E727" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="B728" s="5">
         <v>1</v>
@@ -17510,15 +17510,15 @@
         <v>260</v>
       </c>
       <c r="D728" s="4" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="E728" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="729" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="B729" s="5">
         <v>1</v>
@@ -17527,15 +17527,15 @@
         <v>260</v>
       </c>
       <c r="D729" s="4" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="E729" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="730" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="B730" s="5">
         <v>1</v>
@@ -17544,32 +17544,32 @@
         <v>260</v>
       </c>
       <c r="D730" s="4" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="E730" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="731" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B731" s="5">
+        <v>1</v>
+      </c>
+      <c r="C731" s="5">
+        <v>260</v>
+      </c>
+      <c r="D731" s="4" t="s">
         <v>1405</v>
       </c>
-      <c r="B731" s="5">
-        <v>1</v>
-      </c>
-      <c r="C731" s="5">
-        <v>260</v>
-      </c>
-      <c r="D731" s="4" t="s">
-        <v>1406</v>
-      </c>
       <c r="E731" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="732" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B732" s="5">
         <v>1</v>
@@ -17578,15 +17578,15 @@
         <v>260</v>
       </c>
       <c r="D732" s="4" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="E732" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B733" s="5">
         <v>1</v>
@@ -17595,15 +17595,15 @@
         <v>260</v>
       </c>
       <c r="D733" s="4" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="E733" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="734" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B734" s="5">
         <v>1</v>
@@ -17612,24 +17612,24 @@
         <v>260</v>
       </c>
       <c r="D734" s="4" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="E734" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B735" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C735" s="5">
         <v>250</v>
       </c>
       <c r="D735" s="4" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="E735" s="6" t="s">
         <v>174</v>
@@ -17637,7 +17637,7 @@
     </row>
     <row r="736" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="B736" s="5">
         <v>1</v>
@@ -17646,7 +17646,7 @@
         <v>280</v>
       </c>
       <c r="D736" s="4" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="E736" s="6" t="s">
         <v>327</v>
@@ -17654,7 +17654,7 @@
     </row>
     <row r="737" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="B737" s="5">
         <v>1</v>
@@ -17663,7 +17663,7 @@
         <v>280</v>
       </c>
       <c r="D737" s="4" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="E737" s="6" t="s">
         <v>327</v>
@@ -17671,7 +17671,7 @@
     </row>
     <row r="738" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="B738" s="5">
         <v>1</v>
@@ -17680,7 +17680,7 @@
         <v>280</v>
       </c>
       <c r="D738" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="E738" s="6" t="s">
         <v>327</v>
@@ -17688,7 +17688,7 @@
     </row>
     <row r="739" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B739" s="5">
         <v>1</v>
@@ -17697,7 +17697,7 @@
         <v>280</v>
       </c>
       <c r="D739" s="4" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="E739" s="6" t="s">
         <v>327</v>
@@ -17705,7 +17705,7 @@
     </row>
     <row r="740" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="B740" s="5">
         <v>1</v>
@@ -17714,7 +17714,7 @@
         <v>280</v>
       </c>
       <c r="D740" s="4" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="E740" s="6" t="s">
         <v>327</v>
@@ -17722,7 +17722,7 @@
     </row>
     <row r="741" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="B741" s="5">
         <v>1</v>
@@ -17731,7 +17731,7 @@
         <v>280</v>
       </c>
       <c r="D741" s="4" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E741" s="6" t="s">
         <v>327</v>
@@ -17739,7 +17739,7 @@
     </row>
     <row r="742" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B742" s="5">
         <v>1</v>
@@ -17748,7 +17748,7 @@
         <v>280</v>
       </c>
       <c r="D742" s="4" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="E742" s="6" t="s">
         <v>327</v>
@@ -17756,7 +17756,7 @@
     </row>
     <row r="743" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="B743" s="5">
         <v>3</v>
@@ -17765,15 +17765,15 @@
         <v>280</v>
       </c>
       <c r="D743" s="4" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="E743" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="744" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B744" s="5">
         <v>1</v>
@@ -17782,15 +17782,15 @@
         <v>280</v>
       </c>
       <c r="D744" s="4" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="E744" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="745" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B745" s="5">
         <v>3</v>
@@ -17799,15 +17799,15 @@
         <v>280</v>
       </c>
       <c r="D745" s="4" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="E745" s="6" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="746" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B746" s="5">
         <v>1</v>
@@ -17816,15 +17816,15 @@
         <v>960</v>
       </c>
       <c r="D746" s="4" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="E746" s="6" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="747" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B747" s="5">
         <v>1</v>
@@ -17833,7 +17833,7 @@
         <v>580</v>
       </c>
       <c r="D747" s="4" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="E747" s="6" t="s">
         <v>174</v>
@@ -17841,7 +17841,7 @@
     </row>
     <row r="748" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B748" s="5">
         <v>1</v>
@@ -17850,7 +17850,7 @@
         <v>580</v>
       </c>
       <c r="D748" s="4" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="E748" s="6" t="s">
         <v>174</v>
@@ -17858,7 +17858,7 @@
     </row>
     <row r="749" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B749" s="5">
         <v>2</v>
@@ -17867,7 +17867,7 @@
         <v>180</v>
       </c>
       <c r="D749" s="4" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="E749" s="6" t="s">
         <v>174</v>
@@ -17875,7 +17875,7 @@
     </row>
     <row r="750" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B750" s="5">
         <v>1</v>
@@ -17884,7 +17884,7 @@
         <v>200</v>
       </c>
       <c r="D750" s="4" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="E750" s="6" t="s">
         <v>174</v>
@@ -17892,7 +17892,7 @@
     </row>
     <row r="751" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B751" s="5">
         <v>2</v>
@@ -17901,7 +17901,7 @@
         <v>160</v>
       </c>
       <c r="D751" s="4" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="E751" s="6" t="s">
         <v>174</v>
@@ -17909,7 +17909,7 @@
     </row>
     <row r="752" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B752" s="5">
         <v>2</v>
@@ -17918,7 +17918,7 @@
         <v>160</v>
       </c>
       <c r="D752" s="4" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="E752" s="6" t="s">
         <v>174</v>
@@ -17926,7 +17926,7 @@
     </row>
     <row r="753" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B753" s="5">
         <v>2</v>
@@ -17935,7 +17935,7 @@
         <v>200</v>
       </c>
       <c r="D753" s="4" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="E753" s="6" t="s">
         <v>174</v>
@@ -17943,7 +17943,7 @@
     </row>
     <row r="754" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B754" s="5">
         <v>2</v>
@@ -17952,7 +17952,7 @@
         <v>120</v>
       </c>
       <c r="D754" s="4" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="E754" s="6" t="s">
         <v>174</v>
@@ -17960,7 +17960,7 @@
     </row>
     <row r="755" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="B755" s="5">
         <v>2</v>
@@ -17969,7 +17969,7 @@
         <v>120</v>
       </c>
       <c r="D755" s="4" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="E755" s="6" t="s">
         <v>174</v>
@@ -17977,7 +17977,7 @@
     </row>
     <row r="756" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B756" s="5">
         <v>2</v>
@@ -17986,7 +17986,7 @@
         <v>120</v>
       </c>
       <c r="D756" s="4" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="E756" s="6" t="s">
         <v>174</v>
@@ -17994,7 +17994,7 @@
     </row>
     <row r="757" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B757" s="5">
         <v>8</v>
@@ -18003,7 +18003,7 @@
         <v>120</v>
       </c>
       <c r="D757" s="4" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="E757" s="6" t="s">
         <v>174</v>
@@ -18011,7 +18011,7 @@
     </row>
     <row r="758" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B758" s="5">
         <v>2</v>
@@ -18020,7 +18020,7 @@
         <v>120</v>
       </c>
       <c r="D758" s="4" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="E758" s="6" t="s">
         <v>174</v>

--- a/data/stock.xlsx
+++ b/data/stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\blocks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82323FC-7A40-45F1-A0A5-E9070AF9B191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695C3B0E-104F-4D46-A8F2-34AC07A83852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4320" yWindow="2340" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
   </bookViews>
@@ -7440,7 +7440,7 @@
         <v>873</v>
       </c>
       <c r="B136" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C136" s="3">
         <v>150</v>
@@ -11758,7 +11758,7 @@
         <v>594</v>
       </c>
       <c r="B390" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C390" s="3">
         <v>260</v>
@@ -12047,7 +12047,7 @@
         <v>102</v>
       </c>
       <c r="B407" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C407" s="3">
         <v>260</v>
@@ -12132,7 +12132,7 @@
         <v>237</v>
       </c>
       <c r="B412" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C412" s="3">
         <v>260</v>
@@ -12149,7 +12149,7 @@
         <v>238</v>
       </c>
       <c r="B413" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C413" s="3">
         <v>260</v>
@@ -12166,7 +12166,7 @@
         <v>106</v>
       </c>
       <c r="B414" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C414" s="3">
         <v>260</v>
@@ -12625,7 +12625,7 @@
         <v>427</v>
       </c>
       <c r="B441" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C441" s="3">
         <v>260</v>

--- a/data/stock.xlsx
+++ b/data/stock.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\blocks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695C3B0E-104F-4D46-A8F2-34AC07A83852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C4317C-990D-42EC-B0D2-DCA7E0BA5AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="2340" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
+    <workbookView xWindow="540" yWindow="915" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5230,7 +5230,7 @@
         <v>1306</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3">
         <v>300</v>
@@ -5383,7 +5383,7 @@
         <v>1513</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" s="3">
         <v>260</v>
@@ -5995,7 +5995,7 @@
         <v>243</v>
       </c>
       <c r="B51" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" s="3">
         <v>260</v>
@@ -6284,7 +6284,7 @@
         <v>21</v>
       </c>
       <c r="B68" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C68" s="3">
         <v>180</v>
@@ -6352,7 +6352,7 @@
         <v>493</v>
       </c>
       <c r="B72" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72" s="3">
         <v>180</v>
@@ -6369,7 +6369,7 @@
         <v>494</v>
       </c>
       <c r="B73" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73" s="3">
         <v>180</v>
@@ -6488,7 +6488,7 @@
         <v>25</v>
       </c>
       <c r="B80" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80" s="3">
         <v>460</v>
@@ -6726,7 +6726,7 @@
         <v>33</v>
       </c>
       <c r="B94" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C94" s="3">
         <v>260</v>
@@ -6828,7 +6828,7 @@
         <v>200</v>
       </c>
       <c r="B100" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C100" s="3">
         <v>200</v>
@@ -7814,7 +7814,7 @@
         <v>889</v>
       </c>
       <c r="B158" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C158" s="3">
         <v>260</v>
@@ -8137,7 +8137,7 @@
         <v>1136</v>
       </c>
       <c r="B177" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C177" s="3">
         <v>280</v>
@@ -8205,7 +8205,7 @@
         <v>1140</v>
       </c>
       <c r="B181" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C181" s="3">
         <v>280</v>
@@ -8273,7 +8273,7 @@
         <v>1144</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C185" s="3">
         <v>260</v>
@@ -8647,7 +8647,7 @@
         <v>1460</v>
       </c>
       <c r="B207" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C207" s="3">
         <v>160</v>
@@ -9446,7 +9446,7 @@
         <v>710</v>
       </c>
       <c r="B254" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C254" s="3">
         <v>270</v>
@@ -10687,7 +10687,7 @@
         <v>73</v>
       </c>
       <c r="B327" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C327" s="3">
         <v>320</v>
@@ -10772,7 +10772,7 @@
         <v>77</v>
       </c>
       <c r="B332" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C332" s="3">
         <v>300</v>
@@ -10789,7 +10789,7 @@
         <v>78</v>
       </c>
       <c r="B333" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C333" s="3">
         <v>300</v>
@@ -10857,7 +10857,7 @@
         <v>81</v>
       </c>
       <c r="B337" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C337" s="3">
         <v>300</v>
@@ -10925,7 +10925,7 @@
         <v>84</v>
       </c>
       <c r="B341" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C341" s="3">
         <v>300</v>
@@ -11061,7 +11061,7 @@
         <v>91</v>
       </c>
       <c r="B349" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C349" s="3">
         <v>300</v>
@@ -11180,7 +11180,7 @@
         <v>569</v>
       </c>
       <c r="B356" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C356" s="3">
         <v>300</v>
@@ -11605,7 +11605,7 @@
         <v>1445</v>
       </c>
       <c r="B381" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C381" s="3">
         <v>300</v>

--- a/data/stock.xlsx
+++ b/data/stock.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\blocks\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C4317C-990D-42EC-B0D2-DCA7E0BA5AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05DAB21-A810-49A9-B891-A8EF269541D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="915" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
+    <workbookView xWindow="3150" yWindow="1410" windowWidth="21600" windowHeight="11250" xr2:uid="{FC0CBB84-858B-49F6-BA69-44D83C89F7C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5162,7 +5162,7 @@
         <v>1301</v>
       </c>
       <c r="B2" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3">
         <v>260</v>
@@ -5366,7 +5366,7 @@
         <v>1457</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="3">
         <v>260</v>
@@ -5757,7 +5757,7 @@
         <v>784</v>
       </c>
       <c r="B37" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C37" s="3">
         <v>220</v>
@@ -5995,7 +5995,7 @@
         <v>243</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" s="3">
         <v>260</v>
@@ -6046,7 +6046,7 @@
         <v>245</v>
       </c>
       <c r="B54" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C54" s="3">
         <v>260</v>
@@ -6080,7 +6080,7 @@
         <v>584</v>
       </c>
       <c r="B56" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C56" s="3">
         <v>260</v>
@@ -6148,7 +6148,7 @@
         <v>12</v>
       </c>
       <c r="B60" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60" s="3">
         <v>220</v>
@@ -6318,7 +6318,7 @@
         <v>23</v>
       </c>
       <c r="B70" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70" s="3">
         <v>180</v>
@@ -6947,7 +6947,7 @@
         <v>380</v>
       </c>
       <c r="B107" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C107" s="3">
         <v>260</v>
@@ -6964,7 +6964,7 @@
         <v>518</v>
       </c>
       <c r="B108" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C108" s="3">
         <v>260</v>
@@ -6981,7 +6981,7 @@
         <v>381</v>
       </c>
       <c r="B109" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C109" s="3">
         <v>260</v>
@@ -6998,7 +6998,7 @@
         <v>517</v>
       </c>
       <c r="B110" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110" s="3">
         <v>260</v>
@@ -7219,7 +7219,7 @@
         <v>861</v>
       </c>
       <c r="B123" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C123" s="3">
         <v>260</v>
@@ -7797,7 +7797,7 @@
         <v>888</v>
       </c>
       <c r="B157" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C157" s="3">
         <v>260</v>
@@ -7814,7 +7814,7 @@
         <v>889</v>
       </c>
       <c r="B158" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C158" s="3">
         <v>260</v>
@@ -8171,7 +8171,7 @@
         <v>1138</v>
       </c>
       <c r="B179" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C179" s="3">
         <v>280</v>
@@ -8188,7 +8188,7 @@
         <v>1139</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C180" s="3">
         <v>280</v>
@@ -8222,7 +8222,7 @@
         <v>1141</v>
       </c>
       <c r="B182" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C182" s="3">
         <v>280</v>
@@ -8698,7 +8698,7 @@
         <v>1463</v>
       </c>
       <c r="B210" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C210" s="3">
         <v>160</v>
@@ -8851,7 +8851,7 @@
         <v>369</v>
       </c>
       <c r="B219" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C219" s="3">
         <v>260</v>
@@ -8970,7 +8970,7 @@
         <v>734</v>
       </c>
       <c r="B226" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C226" s="3">
         <v>400</v>
@@ -9055,7 +9055,7 @@
         <v>1107</v>
       </c>
       <c r="B231" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C231" s="3">
         <v>360</v>
@@ -9548,7 +9548,7 @@
         <v>913</v>
       </c>
       <c r="B260" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C260" s="3">
         <v>220</v>
@@ -9752,7 +9752,7 @@
         <v>1177</v>
       </c>
       <c r="B272" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C272" s="3">
         <v>260</v>
@@ -10449,7 +10449,7 @@
         <v>240</v>
       </c>
       <c r="B313" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C313" s="3">
         <v>360</v>
@@ -10466,7 +10466,7 @@
         <v>60</v>
       </c>
       <c r="B314" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C314" s="3">
         <v>360</v>
@@ -10755,7 +10755,7 @@
         <v>297</v>
       </c>
       <c r="B331" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C331" s="3">
         <v>320</v>
@@ -11146,7 +11146,7 @@
         <v>568</v>
       </c>
       <c r="B354" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C354" s="3">
         <v>300</v>
@@ -11197,7 +11197,7 @@
         <v>92</v>
       </c>
       <c r="B357" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C357" s="3">
         <v>300</v>
@@ -11214,7 +11214,7 @@
         <v>93</v>
       </c>
       <c r="B358" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C358" s="3">
         <v>300</v>
@@ -11231,7 +11231,7 @@
         <v>94</v>
       </c>
       <c r="B359" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C359" s="3">
         <v>300</v>
@@ -11248,7 +11248,7 @@
         <v>95</v>
       </c>
       <c r="B360" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C360" s="3">
         <v>300</v>
@@ -11605,7 +11605,7 @@
         <v>1445</v>
       </c>
       <c r="B381" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C381" s="3">
         <v>300</v>
@@ -11979,7 +11979,7 @@
         <v>1188</v>
       </c>
       <c r="B403" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C403" s="3">
         <v>500</v>
@@ -12098,7 +12098,7 @@
         <v>105</v>
       </c>
       <c r="B410" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C410" s="3">
         <v>260</v>
@@ -12183,7 +12183,7 @@
         <v>616</v>
       </c>
       <c r="B415" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C415" s="3">
         <v>260</v>
@@ -12965,7 +12965,7 @@
         <v>444</v>
       </c>
       <c r="B461" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C461" s="3">
         <v>400</v>
@@ -16586,7 +16586,7 @@
         <v>947</v>
       </c>
       <c r="B674" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C674" s="5">
         <v>260</v>
@@ -16671,7 +16671,7 @@
         <v>950</v>
       </c>
       <c r="B679" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C679" s="5">
         <v>260</v>
@@ -16926,7 +16926,7 @@
         <v>959</v>
       </c>
       <c r="B694" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C694" s="5">
         <v>260</v>
@@ -16943,7 +16943,7 @@
         <v>1217</v>
       </c>
       <c r="B695" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C695" s="5">
         <v>280</v>
@@ -17079,7 +17079,7 @@
         <v>1225</v>
       </c>
       <c r="B703" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C703" s="5">
         <v>280</v>
@@ -17453,7 +17453,7 @@
         <v>1386</v>
       </c>
       <c r="B725" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C725" s="5">
         <v>280</v>
@@ -17470,7 +17470,7 @@
         <v>1388</v>
       </c>
       <c r="B726" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C726" s="5">
         <v>300</v>
@@ -17606,7 +17606,7 @@
         <v>1392</v>
       </c>
       <c r="B734" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C734" s="5">
         <v>260</v>
@@ -17776,7 +17776,7 @@
         <v>1508</v>
       </c>
       <c r="B744" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C744" s="5">
         <v>280</v>
@@ -17827,7 +17827,7 @@
         <v>1469</v>
       </c>
       <c r="B747" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C747" s="5">
         <v>580</v>
